--- a/DMC-ICE13/reproduction/seidler_dmc13_recalculation/comparison_workbook.xlsx
+++ b/DMC-ICE13/reproduction/seidler_dmc13_recalculation/comparison_workbook.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re6d9a6786ab844ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch statistics" sheetId="2" r:id="R6913f97e34384634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative energies" sheetId="3" r:id="Ra856d74dcc4f452e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch differences" sheetId="4" r:id="R4235f91fa8824f87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absolute parity" sheetId="5" r:id="R1aa348fac95d4862"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Native meshes" sheetId="6" r:id="Rf5db574199884949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mstore absolute" sheetId="7" r:id="R4f05b190878a4340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="8" r:id="Rb1915db522b3414e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Reabe28064c9f4899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch statistics" sheetId="2" r:id="R19074c89ad274ecd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative energies" sheetId="3" r:id="R28b99a65c7c64fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch differences" sheetId="4" r:id="Rc54c27faba284aae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absolute parity" sheetId="5" r:id="Rf7071fc64d1445b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Native meshes" sheetId="6" r:id="R4de1317794b244e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mstore absolute" sheetId="7" r:id="R4b23f8a383e84758"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="8" r:id="Re9f51ea73f9f442b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -524,7 +524,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb0076e67bc6e4ea6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R228f9dcc45974e94"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1061,7 +1061,7 @@
     <x:mergeCell ref="A24:E24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84c7269c97fd4b89"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fb42972e9f043d0"/>
 </x:worksheet>
 </file>
 
@@ -3513,25 +3513,25 @@
     </x:row>
     <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="36" t="str">
-        <x:v>author pbc CLI</x:v>
+        <x:v>CP2K-native pbc provider</x:v>
       </x:c>
       <x:c r="B81" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C81" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D81" s="42" t="str">
-        <x:v>-40.056162616318</x:v>
+        <x:v>0.090455358961</x:v>
       </x:c>
       <x:c r="E81" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F81" s="42" t="str">
-        <x:v>-40.366162616318</x:v>
+        <x:v>-1.609544641039</x:v>
       </x:c>
       <x:c r="G81" s="42" t="str">
-        <x:v>40.366162616318</x:v>
+        <x:v>1.609544641039</x:v>
       </x:c>
       <x:c r="H81" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3545,19 +3545,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C82" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D82" s="42" t="str">
-        <x:v>-21.728016057439</x:v>
+        <x:v>-40.056162616318</x:v>
       </x:c>
       <x:c r="E82" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F82" s="42" t="str">
-        <x:v>-22.978016057439</x:v>
+        <x:v>-40.366162616318</x:v>
       </x:c>
       <x:c r="G82" s="42" t="str">
-        <x:v>22.978016057439</x:v>
+        <x:v>40.366162616318</x:v>
       </x:c>
       <x:c r="H82" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3571,19 +3571,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C83" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D83" s="42" t="str">
-        <x:v>14.909575775296</x:v>
+        <x:v>-21.728016057439</x:v>
       </x:c>
       <x:c r="E83" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F83" s="42" t="str">
-        <x:v>11.079575775296</x:v>
+        <x:v>-22.978016057439</x:v>
       </x:c>
       <x:c r="G83" s="42" t="str">
-        <x:v>11.079575775296</x:v>
+        <x:v>22.978016057439</x:v>
       </x:c>
       <x:c r="H83" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3597,19 +3597,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C84" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D84" s="42" t="str">
-        <x:v>-57.502753280215</x:v>
+        <x:v>14.909575775296</x:v>
       </x:c>
       <x:c r="E84" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F84" s="42" t="str">
-        <x:v>-59.282753280215</x:v>
+        <x:v>11.079575775296</x:v>
       </x:c>
       <x:c r="G84" s="42" t="str">
-        <x:v>59.282753280215</x:v>
+        <x:v>11.079575775296</x:v>
       </x:c>
       <x:c r="H84" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3623,19 +3623,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C85" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D85" s="42" t="str">
-        <x:v>-300.067320161804</x:v>
+        <x:v>-57.502753280215</x:v>
       </x:c>
       <x:c r="E85" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F85" s="42" t="str">
-        <x:v>-305.057320161804</x:v>
+        <x:v>-59.282753280215</x:v>
       </x:c>
       <x:c r="G85" s="42" t="str">
-        <x:v>305.057320161804</x:v>
+        <x:v>59.282753280215</x:v>
       </x:c>
       <x:c r="H85" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3649,19 +3649,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C86" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D86" s="42" t="str">
-        <x:v>-121.498882525679</x:v>
+        <x:v>-300.067320161804</x:v>
       </x:c>
       <x:c r="E86" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F86" s="42" t="str">
-        <x:v>-125.728882525679</x:v>
+        <x:v>-305.057320161804</x:v>
       </x:c>
       <x:c r="G86" s="42" t="str">
-        <x:v>125.728882525679</x:v>
+        <x:v>305.057320161804</x:v>
       </x:c>
       <x:c r="H86" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3675,19 +3675,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C87" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D87" s="42" t="str">
-        <x:v>-14.812836787859</x:v>
+        <x:v>-121.498882525679</x:v>
       </x:c>
       <x:c r="E87" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F87" s="42" t="str">
-        <x:v>-15.412836787859</x:v>
+        <x:v>-125.728882525679</x:v>
       </x:c>
       <x:c r="G87" s="42" t="str">
-        <x:v>15.412836787859</x:v>
+        <x:v>125.728882525679</x:v>
       </x:c>
       <x:c r="H87" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3701,19 +3701,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C88" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D88" s="42" t="str">
-        <x:v>-165.257377908596</x:v>
+        <x:v>-14.812836787859</x:v>
       </x:c>
       <x:c r="E88" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F88" s="42" t="str">
-        <x:v>-165.417377908596</x:v>
+        <x:v>-15.412836787859</x:v>
       </x:c>
       <x:c r="G88" s="42" t="str">
-        <x:v>165.417377908596</x:v>
+        <x:v>15.412836787859</x:v>
       </x:c>
       <x:c r="H88" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3727,19 +3727,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C89" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D89" s="42" t="str">
-        <x:v>6.868364020212</x:v>
+        <x:v>-165.257377908596</x:v>
       </x:c>
       <x:c r="E89" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F89" s="42" t="str">
-        <x:v>4.748364020212</x:v>
+        <x:v>-165.417377908596</x:v>
       </x:c>
       <x:c r="G89" s="42" t="str">
-        <x:v>4.748364020212</x:v>
+        <x:v>165.417377908596</x:v>
       </x:c>
       <x:c r="H89" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3753,19 +3753,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C90" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D90" s="42" t="str">
-        <x:v>-199.611684777200</x:v>
+        <x:v>6.868364020212</x:v>
       </x:c>
       <x:c r="E90" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F90" s="42" t="str">
-        <x:v>-201.311684777200</x:v>
+        <x:v>4.748364020212</x:v>
       </x:c>
       <x:c r="G90" s="42" t="str">
-        <x:v>201.311684777200</x:v>
+        <x:v>4.748364020212</x:v>
       </x:c>
       <x:c r="H90" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3779,19 +3779,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C91" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D91" s="42" t="str">
-        <x:v>-58.050293332028</x:v>
+        <x:v>-199.611684777200</x:v>
       </x:c>
       <x:c r="E91" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F91" s="42" t="str">
-        <x:v>-59.790293332028</x:v>
+        <x:v>-201.311684777200</x:v>
       </x:c>
       <x:c r="G91" s="42" t="str">
-        <x:v>59.790293332028</x:v>
+        <x:v>201.311684777200</x:v>
       </x:c>
       <x:c r="H91" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3805,19 +3805,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C92" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D92" s="42" t="str">
-        <x:v>-51.559121420866</x:v>
+        <x:v>-58.050293332028</x:v>
       </x:c>
       <x:c r="E92" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F92" s="42" t="str">
-        <x:v>-53.309121420866</x:v>
+        <x:v>-59.790293332028</x:v>
       </x:c>
       <x:c r="G92" s="42" t="str">
-        <x:v>53.309121420866</x:v>
+        <x:v>59.790293332028</x:v>
       </x:c>
       <x:c r="H92" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3828,22 +3828,22 @@
         <x:v>author pbc CLI</x:v>
       </x:c>
       <x:c r="B93" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C93" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D93" s="42" t="str">
-        <x:v>-9.054674468559</x:v>
+        <x:v>-51.559121420866</x:v>
       </x:c>
       <x:c r="E93" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F93" s="42" t="str">
-        <x:v>-9.364674468559</x:v>
+        <x:v>-53.309121420866</x:v>
       </x:c>
       <x:c r="G93" s="42" t="str">
-        <x:v>9.364674468559</x:v>
+        <x:v>53.309121420866</x:v>
       </x:c>
       <x:c r="H93" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3857,19 +3857,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C94" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D94" s="42" t="str">
-        <x:v>-2.341718734421</x:v>
+        <x:v>-9.054674468559</x:v>
       </x:c>
       <x:c r="E94" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F94" s="42" t="str">
-        <x:v>-3.591718734421</x:v>
+        <x:v>-9.364674468559</x:v>
       </x:c>
       <x:c r="G94" s="42" t="str">
-        <x:v>3.591718734421</x:v>
+        <x:v>9.364674468559</x:v>
       </x:c>
       <x:c r="H94" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3883,19 +3883,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C95" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D95" s="42" t="str">
-        <x:v>2.892295286943</x:v>
+        <x:v>-2.341718734421</x:v>
       </x:c>
       <x:c r="E95" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F95" s="42" t="str">
-        <x:v>-0.937704713057</x:v>
+        <x:v>-3.591718734421</x:v>
       </x:c>
       <x:c r="G95" s="42" t="str">
-        <x:v>0.937704713057</x:v>
+        <x:v>3.591718734421</x:v>
       </x:c>
       <x:c r="H95" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3909,19 +3909,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C96" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D96" s="42" t="str">
-        <x:v>-12.421511801622</x:v>
+        <x:v>2.892295286943</x:v>
       </x:c>
       <x:c r="E96" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F96" s="42" t="str">
-        <x:v>-14.201511801622</x:v>
+        <x:v>-0.937704713057</x:v>
       </x:c>
       <x:c r="G96" s="42" t="str">
-        <x:v>14.201511801622</x:v>
+        <x:v>0.937704713057</x:v>
       </x:c>
       <x:c r="H96" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3935,19 +3935,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C97" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D97" s="42" t="str">
-        <x:v>-153.975297576434</x:v>
+        <x:v>-12.421511801622</x:v>
       </x:c>
       <x:c r="E97" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F97" s="42" t="str">
-        <x:v>-158.965297576434</x:v>
+        <x:v>-14.201511801622</x:v>
       </x:c>
       <x:c r="G97" s="42" t="str">
-        <x:v>158.965297576434</x:v>
+        <x:v>14.201511801622</x:v>
       </x:c>
       <x:c r="H97" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3961,19 +3961,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C98" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D98" s="42" t="str">
-        <x:v>-38.490190110106</x:v>
+        <x:v>-153.975297576434</x:v>
       </x:c>
       <x:c r="E98" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F98" s="42" t="str">
-        <x:v>-42.720190110106</x:v>
+        <x:v>-158.965297576434</x:v>
       </x:c>
       <x:c r="G98" s="42" t="str">
-        <x:v>42.720190110106</x:v>
+        <x:v>158.965297576434</x:v>
       </x:c>
       <x:c r="H98" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3987,19 +3987,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C99" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D99" s="42" t="str">
-        <x:v>-2.462552657305</x:v>
+        <x:v>-38.490190110106</x:v>
       </x:c>
       <x:c r="E99" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F99" s="42" t="str">
-        <x:v>-3.062552657305</x:v>
+        <x:v>-42.720190110106</x:v>
       </x:c>
       <x:c r="G99" s="42" t="str">
-        <x:v>3.062552657305</x:v>
+        <x:v>42.720190110106</x:v>
       </x:c>
       <x:c r="H99" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4013,19 +4013,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C100" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D100" s="42" t="str">
-        <x:v>-62.538655042867</x:v>
+        <x:v>-2.462552657305</x:v>
       </x:c>
       <x:c r="E100" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F100" s="42" t="str">
-        <x:v>-62.698655042867</x:v>
+        <x:v>-3.062552657305</x:v>
       </x:c>
       <x:c r="G100" s="42" t="str">
-        <x:v>62.698655042867</x:v>
+        <x:v>3.062552657305</x:v>
       </x:c>
       <x:c r="H100" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4039,19 +4039,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C101" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D101" s="42" t="str">
-        <x:v>0.923689537732</x:v>
+        <x:v>-62.538655042867</x:v>
       </x:c>
       <x:c r="E101" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F101" s="42" t="str">
-        <x:v>-1.196310462268</x:v>
+        <x:v>-62.698655042867</x:v>
       </x:c>
       <x:c r="G101" s="42" t="str">
-        <x:v>1.196310462268</x:v>
+        <x:v>62.698655042867</x:v>
       </x:c>
       <x:c r="H101" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4065,19 +4065,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C102" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D102" s="42" t="str">
-        <x:v>-83.903026598902</x:v>
+        <x:v>0.923689537732</x:v>
       </x:c>
       <x:c r="E102" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F102" s="42" t="str">
-        <x:v>-85.603026598902</x:v>
+        <x:v>-1.196310462268</x:v>
       </x:c>
       <x:c r="G102" s="42" t="str">
-        <x:v>85.603026598902</x:v>
+        <x:v>1.196310462268</x:v>
       </x:c>
       <x:c r="H102" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4091,19 +4091,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C103" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D103" s="42" t="str">
-        <x:v>-12.548998010281</x:v>
+        <x:v>-83.903026598902</x:v>
       </x:c>
       <x:c r="E103" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F103" s="42" t="str">
-        <x:v>-14.288998010281</x:v>
+        <x:v>-85.603026598902</x:v>
       </x:c>
       <x:c r="G103" s="42" t="str">
-        <x:v>14.288998010281</x:v>
+        <x:v>85.603026598902</x:v>
       </x:c>
       <x:c r="H103" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4117,19 +4117,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C104" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D104" s="42" t="str">
-        <x:v>-10.466416914384</x:v>
+        <x:v>-12.548998010281</x:v>
       </x:c>
       <x:c r="E104" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F104" s="42" t="str">
-        <x:v>-12.216416914384</x:v>
+        <x:v>-14.288998010281</x:v>
       </x:c>
       <x:c r="G104" s="42" t="str">
-        <x:v>12.216416914384</x:v>
+        <x:v>14.288998010281</x:v>
       </x:c>
       <x:c r="H104" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4137,25 +4137,25 @@
     </x:row>
     <x:row r="105" ht="15" hidden="0" customHeight="1">
       <x:c r="A105" s="36" t="str">
-        <x:v>current pbc CLI</x:v>
+        <x:v>author pbc CLI</x:v>
       </x:c>
       <x:c r="B105" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C105" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D105" s="42" t="str">
-        <x:v>-85.402832480791</x:v>
+        <x:v>-10.466416914384</x:v>
       </x:c>
       <x:c r="E105" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F105" s="42" t="str">
-        <x:v>-85.712832480791</x:v>
+        <x:v>-12.216416914384</x:v>
       </x:c>
       <x:c r="G105" s="42" t="str">
-        <x:v>85.712832480791</x:v>
+        <x:v>12.216416914384</x:v>
       </x:c>
       <x:c r="H105" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4169,19 +4169,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C106" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D106" s="42" t="str">
-        <x:v>-52.784771448006</x:v>
+        <x:v>-85.402832480791</x:v>
       </x:c>
       <x:c r="E106" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F106" s="42" t="str">
-        <x:v>-54.034771448006</x:v>
+        <x:v>-85.712832480791</x:v>
       </x:c>
       <x:c r="G106" s="42" t="str">
-        <x:v>54.034771448006</x:v>
+        <x:v>85.712832480791</x:v>
       </x:c>
       <x:c r="H106" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4195,19 +4195,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C107" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D107" s="42" t="str">
-        <x:v>38.666296487481</x:v>
+        <x:v>-52.784771448006</x:v>
       </x:c>
       <x:c r="E107" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F107" s="42" t="str">
-        <x:v>34.836296487481</x:v>
+        <x:v>-54.034771448006</x:v>
       </x:c>
       <x:c r="G107" s="42" t="str">
-        <x:v>34.836296487481</x:v>
+        <x:v>54.034771448006</x:v>
       </x:c>
       <x:c r="H107" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4221,19 +4221,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C108" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D108" s="42" t="str">
-        <x:v>-119.951876462899</x:v>
+        <x:v>38.666296487481</x:v>
       </x:c>
       <x:c r="E108" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F108" s="42" t="str">
-        <x:v>-121.731876462899</x:v>
+        <x:v>34.836296487481</x:v>
       </x:c>
       <x:c r="G108" s="42" t="str">
-        <x:v>121.731876462899</x:v>
+        <x:v>34.836296487481</x:v>
       </x:c>
       <x:c r="H108" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4247,19 +4247,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C109" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D109" s="42" t="str">
-        <x:v>-491.873083815613</x:v>
+        <x:v>-119.951876462899</x:v>
       </x:c>
       <x:c r="E109" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F109" s="42" t="str">
-        <x:v>-496.863083815613</x:v>
+        <x:v>-121.731876462899</x:v>
       </x:c>
       <x:c r="G109" s="42" t="str">
-        <x:v>496.863083815613</x:v>
+        <x:v>121.731876462899</x:v>
       </x:c>
       <x:c r="H109" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4273,19 +4273,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C110" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D110" s="42" t="str">
-        <x:v>-227.181421040355</x:v>
+        <x:v>-491.873083815613</x:v>
       </x:c>
       <x:c r="E110" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F110" s="42" t="str">
-        <x:v>-231.411421040355</x:v>
+        <x:v>-496.863083815613</x:v>
       </x:c>
       <x:c r="G110" s="42" t="str">
-        <x:v>231.411421040355</x:v>
+        <x:v>496.863083815613</x:v>
       </x:c>
       <x:c r="H110" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4299,19 +4299,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C111" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D111" s="42" t="str">
-        <x:v>-36.269951925783</x:v>
+        <x:v>-227.181421040355</x:v>
       </x:c>
       <x:c r="E111" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F111" s="42" t="str">
-        <x:v>-36.869951925783</x:v>
+        <x:v>-231.411421040355</x:v>
       </x:c>
       <x:c r="G111" s="42" t="str">
-        <x:v>36.869951925783</x:v>
+        <x:v>231.411421040355</x:v>
       </x:c>
       <x:c r="H111" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4325,19 +4325,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C112" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D112" s="42" t="str">
-        <x:v>-299.258518836626</x:v>
+        <x:v>-36.269951925783</x:v>
       </x:c>
       <x:c r="E112" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F112" s="42" t="str">
-        <x:v>-299.418518836626</x:v>
+        <x:v>-36.869951925783</x:v>
       </x:c>
       <x:c r="G112" s="42" t="str">
-        <x:v>299.418518836626</x:v>
+        <x:v>36.869951925783</x:v>
       </x:c>
       <x:c r="H112" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4351,19 +4351,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C113" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D113" s="42" t="str">
-        <x:v>16.464730608559</x:v>
+        <x:v>-299.258518836626</x:v>
       </x:c>
       <x:c r="E113" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F113" s="42" t="str">
-        <x:v>14.344730608559</x:v>
+        <x:v>-299.418518836626</x:v>
       </x:c>
       <x:c r="G113" s="42" t="str">
-        <x:v>14.344730608559</x:v>
+        <x:v>299.418518836626</x:v>
       </x:c>
       <x:c r="H113" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4377,19 +4377,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C114" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D114" s="42" t="str">
-        <x:v>-351.956576532881</x:v>
+        <x:v>16.464730608559</x:v>
       </x:c>
       <x:c r="E114" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F114" s="42" t="str">
-        <x:v>-353.656576532881</x:v>
+        <x:v>14.344730608559</x:v>
       </x:c>
       <x:c r="G114" s="42" t="str">
-        <x:v>353.656576532881</x:v>
+        <x:v>14.344730608559</x:v>
       </x:c>
       <x:c r="H114" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4403,19 +4403,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C115" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D115" s="42" t="str">
-        <x:v>-121.156628176656</x:v>
+        <x:v>-351.956576532881</x:v>
       </x:c>
       <x:c r="E115" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F115" s="42" t="str">
-        <x:v>-122.896628176656</x:v>
+        <x:v>-353.656576532881</x:v>
       </x:c>
       <x:c r="G115" s="42" t="str">
-        <x:v>122.896628176656</x:v>
+        <x:v>353.656576532881</x:v>
       </x:c>
       <x:c r="H115" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4429,19 +4429,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C116" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D116" s="42" t="str">
-        <x:v>-112.486904450047</x:v>
+        <x:v>-121.156628176656</x:v>
       </x:c>
       <x:c r="E116" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F116" s="42" t="str">
-        <x:v>-114.236904450047</x:v>
+        <x:v>-122.896628176656</x:v>
       </x:c>
       <x:c r="G116" s="42" t="str">
-        <x:v>114.236904450047</x:v>
+        <x:v>122.896628176656</x:v>
       </x:c>
       <x:c r="H116" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4452,22 +4452,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B117" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C117" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D117" s="42" t="str">
-        <x:v>-40.052769548562</x:v>
+        <x:v>-112.486904450047</x:v>
       </x:c>
       <x:c r="E117" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F117" s="42" t="str">
-        <x:v>-40.362769548562</x:v>
+        <x:v>-114.236904450047</x:v>
       </x:c>
       <x:c r="G117" s="42" t="str">
-        <x:v>40.362769548562</x:v>
+        <x:v>114.236904450047</x:v>
       </x:c>
       <x:c r="H117" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4481,19 +4481,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C118" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D118" s="42" t="str">
-        <x:v>-21.669458368756</x:v>
+        <x:v>-40.052769548562</x:v>
       </x:c>
       <x:c r="E118" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F118" s="42" t="str">
-        <x:v>-22.919458368756</x:v>
+        <x:v>-40.362769548562</x:v>
       </x:c>
       <x:c r="G118" s="42" t="str">
-        <x:v>22.919458368756</x:v>
+        <x:v>40.362769548562</x:v>
       </x:c>
       <x:c r="H118" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4507,19 +4507,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C119" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D119" s="42" t="str">
-        <x:v>14.926647908813</x:v>
+        <x:v>-21.669458368756</x:v>
       </x:c>
       <x:c r="E119" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F119" s="42" t="str">
-        <x:v>11.096647908813</x:v>
+        <x:v>-22.919458368756</x:v>
       </x:c>
       <x:c r="G119" s="42" t="str">
-        <x:v>11.096647908813</x:v>
+        <x:v>22.919458368756</x:v>
       </x:c>
       <x:c r="H119" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4533,19 +4533,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C120" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D120" s="42" t="str">
-        <x:v>-57.367276074495</x:v>
+        <x:v>14.926647908813</x:v>
       </x:c>
       <x:c r="E120" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F120" s="42" t="str">
-        <x:v>-59.147276074495</x:v>
+        <x:v>11.096647908813</x:v>
       </x:c>
       <x:c r="G120" s="42" t="str">
-        <x:v>59.147276074495</x:v>
+        <x:v>11.096647908813</x:v>
       </x:c>
       <x:c r="H120" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4559,19 +4559,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C121" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D121" s="42" t="str">
-        <x:v>-299.975204903283</x:v>
+        <x:v>-57.367276074495</x:v>
       </x:c>
       <x:c r="E121" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F121" s="42" t="str">
-        <x:v>-304.965204903283</x:v>
+        <x:v>-59.147276074495</x:v>
       </x:c>
       <x:c r="G121" s="42" t="str">
-        <x:v>304.965204903283</x:v>
+        <x:v>59.147276074495</x:v>
       </x:c>
       <x:c r="H121" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4585,19 +4585,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C122" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D122" s="42" t="str">
-        <x:v>-121.493623038083</x:v>
+        <x:v>-299.975204903283</x:v>
       </x:c>
       <x:c r="E122" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F122" s="42" t="str">
-        <x:v>-125.723623038083</x:v>
+        <x:v>-304.965204903283</x:v>
       </x:c>
       <x:c r="G122" s="42" t="str">
-        <x:v>125.723623038083</x:v>
+        <x:v>304.965204903283</x:v>
       </x:c>
       <x:c r="H122" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4611,19 +4611,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C123" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D123" s="42" t="str">
-        <x:v>-14.811033266160</x:v>
+        <x:v>-121.493623038083</x:v>
       </x:c>
       <x:c r="E123" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F123" s="42" t="str">
-        <x:v>-15.411033266160</x:v>
+        <x:v>-125.723623038083</x:v>
       </x:c>
       <x:c r="G123" s="42" t="str">
-        <x:v>15.411033266160</x:v>
+        <x:v>125.723623038083</x:v>
       </x:c>
       <x:c r="H123" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4637,19 +4637,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C124" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D124" s="42" t="str">
-        <x:v>-165.236809268426</x:v>
+        <x:v>-14.811033266160</x:v>
       </x:c>
       <x:c r="E124" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F124" s="42" t="str">
-        <x:v>-165.396809268426</x:v>
+        <x:v>-15.411033266160</x:v>
       </x:c>
       <x:c r="G124" s="42" t="str">
-        <x:v>165.396809268426</x:v>
+        <x:v>15.411033266160</x:v>
       </x:c>
       <x:c r="H124" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4663,19 +4663,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C125" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D125" s="42" t="str">
-        <x:v>6.872357662713</x:v>
+        <x:v>-165.236809268426</x:v>
       </x:c>
       <x:c r="E125" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F125" s="42" t="str">
-        <x:v>4.752357662713</x:v>
+        <x:v>-165.396809268426</x:v>
       </x:c>
       <x:c r="G125" s="42" t="str">
-        <x:v>4.752357662713</x:v>
+        <x:v>165.396809268426</x:v>
       </x:c>
       <x:c r="H125" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4689,19 +4689,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C126" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D126" s="42" t="str">
-        <x:v>-199.607041791688</x:v>
+        <x:v>6.872357662713</x:v>
       </x:c>
       <x:c r="E126" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F126" s="42" t="str">
-        <x:v>-201.307041791688</x:v>
+        <x:v>4.752357662713</x:v>
       </x:c>
       <x:c r="G126" s="42" t="str">
-        <x:v>201.307041791688</x:v>
+        <x:v>4.752357662713</x:v>
       </x:c>
       <x:c r="H126" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4715,19 +4715,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C127" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D127" s="42" t="str">
-        <x:v>-58.045564075785</x:v>
+        <x:v>-199.607041791688</x:v>
       </x:c>
       <x:c r="E127" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F127" s="42" t="str">
-        <x:v>-59.785564075785</x:v>
+        <x:v>-201.307041791688</x:v>
       </x:c>
       <x:c r="G127" s="42" t="str">
-        <x:v>59.785564075785</x:v>
+        <x:v>201.307041791688</x:v>
       </x:c>
       <x:c r="H127" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4741,19 +4741,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C128" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D128" s="42" t="str">
-        <x:v>-51.558720983607</x:v>
+        <x:v>-58.045564075785</x:v>
       </x:c>
       <x:c r="E128" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F128" s="42" t="str">
-        <x:v>-53.308720983607</x:v>
+        <x:v>-59.785564075785</x:v>
       </x:c>
       <x:c r="G128" s="42" t="str">
-        <x:v>53.308720983607</x:v>
+        <x:v>59.785564075785</x:v>
       </x:c>
       <x:c r="H128" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4764,22 +4764,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B129" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C129" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D129" s="42" t="str">
-        <x:v>-9.052128552229</x:v>
+        <x:v>-51.558720983607</x:v>
       </x:c>
       <x:c r="E129" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F129" s="42" t="str">
-        <x:v>-9.362128552229</x:v>
+        <x:v>-53.308720983607</x:v>
       </x:c>
       <x:c r="G129" s="42" t="str">
-        <x:v>9.362128552229</x:v>
+        <x:v>53.308720983607</x:v>
       </x:c>
       <x:c r="H129" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4793,19 +4793,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C130" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D130" s="42" t="str">
-        <x:v>-2.299617048110</x:v>
+        <x:v>-9.052128552229</x:v>
       </x:c>
       <x:c r="E130" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F130" s="42" t="str">
-        <x:v>-3.549617048110</x:v>
+        <x:v>-9.362128552229</x:v>
       </x:c>
       <x:c r="G130" s="42" t="str">
-        <x:v>3.549617048110</x:v>
+        <x:v>9.362128552229</x:v>
       </x:c>
       <x:c r="H130" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4819,19 +4819,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C131" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D131" s="42" t="str">
-        <x:v>2.904340310370</x:v>
+        <x:v>-2.299617048110</x:v>
       </x:c>
       <x:c r="E131" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F131" s="42" t="str">
-        <x:v>-0.925659689630</x:v>
+        <x:v>-3.549617048110</x:v>
       </x:c>
       <x:c r="G131" s="42" t="str">
-        <x:v>0.925659689630</x:v>
+        <x:v>3.549617048110</x:v>
       </x:c>
       <x:c r="H131" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4845,19 +4845,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C132" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D132" s="42" t="str">
-        <x:v>-12.321031303355</x:v>
+        <x:v>2.904340310370</x:v>
       </x:c>
       <x:c r="E132" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F132" s="42" t="str">
-        <x:v>-14.101031303355</x:v>
+        <x:v>-0.925659689630</x:v>
       </x:c>
       <x:c r="G132" s="42" t="str">
-        <x:v>14.101031303355</x:v>
+        <x:v>0.925659689630</x:v>
       </x:c>
       <x:c r="H132" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4871,19 +4871,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C133" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D133" s="42" t="str">
-        <x:v>-153.898129900577</x:v>
+        <x:v>-12.321031303355</x:v>
       </x:c>
       <x:c r="E133" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F133" s="42" t="str">
-        <x:v>-158.888129900577</x:v>
+        <x:v>-14.101031303355</x:v>
       </x:c>
       <x:c r="G133" s="42" t="str">
-        <x:v>158.888129900577</x:v>
+        <x:v>14.101031303355</x:v>
       </x:c>
       <x:c r="H133" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4897,19 +4897,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C134" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D134" s="42" t="str">
-        <x:v>-38.486266197120</x:v>
+        <x:v>-153.898129900577</x:v>
       </x:c>
       <x:c r="E134" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F134" s="42" t="str">
-        <x:v>-42.716266197120</x:v>
+        <x:v>-158.888129900577</x:v>
       </x:c>
       <x:c r="G134" s="42" t="str">
-        <x:v>42.716266197120</x:v>
+        <x:v>158.888129900577</x:v>
       </x:c>
       <x:c r="H134" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4923,19 +4923,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C135" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D135" s="42" t="str">
-        <x:v>-2.461004071112</x:v>
+        <x:v>-38.486266197120</x:v>
       </x:c>
       <x:c r="E135" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F135" s="42" t="str">
-        <x:v>-3.061004071112</x:v>
+        <x:v>-42.716266197120</x:v>
       </x:c>
       <x:c r="G135" s="42" t="str">
-        <x:v>3.061004071112</x:v>
+        <x:v>42.716266197120</x:v>
       </x:c>
       <x:c r="H135" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4949,19 +4949,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C136" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D136" s="42" t="str">
-        <x:v>-62.523175264048</x:v>
+        <x:v>-2.461004071112</x:v>
       </x:c>
       <x:c r="E136" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F136" s="42" t="str">
-        <x:v>-62.683175264048</x:v>
+        <x:v>-3.061004071112</x:v>
       </x:c>
       <x:c r="G136" s="42" t="str">
-        <x:v>62.683175264048</x:v>
+        <x:v>3.061004071112</x:v>
       </x:c>
       <x:c r="H136" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4975,19 +4975,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C137" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D137" s="42" t="str">
-        <x:v>0.926723486584</x:v>
+        <x:v>-62.523175264048</x:v>
       </x:c>
       <x:c r="E137" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F137" s="42" t="str">
-        <x:v>-1.193276513416</x:v>
+        <x:v>-62.683175264048</x:v>
       </x:c>
       <x:c r="G137" s="42" t="str">
-        <x:v>1.193276513416</x:v>
+        <x:v>62.683175264048</x:v>
       </x:c>
       <x:c r="H137" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5001,19 +5001,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C138" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D138" s="42" t="str">
-        <x:v>-83.899718986935</x:v>
+        <x:v>0.926723486584</x:v>
       </x:c>
       <x:c r="E138" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F138" s="42" t="str">
-        <x:v>-85.599718986935</x:v>
+        <x:v>-1.193276513416</x:v>
       </x:c>
       <x:c r="G138" s="42" t="str">
-        <x:v>85.599718986935</x:v>
+        <x:v>1.193276513416</x:v>
       </x:c>
       <x:c r="H138" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5027,19 +5027,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C139" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D139" s="42" t="str">
-        <x:v>-12.545503073689</x:v>
+        <x:v>-83.899718986935</x:v>
       </x:c>
       <x:c r="E139" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F139" s="42" t="str">
-        <x:v>-14.285503073689</x:v>
+        <x:v>-85.599718986935</x:v>
       </x:c>
       <x:c r="G139" s="42" t="str">
-        <x:v>14.285503073689</x:v>
+        <x:v>85.599718986935</x:v>
       </x:c>
       <x:c r="H139" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5053,19 +5053,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C140" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D140" s="42" t="str">
-        <x:v>-10.466391957817</x:v>
+        <x:v>-12.545503073689</x:v>
       </x:c>
       <x:c r="E140" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F140" s="42" t="str">
-        <x:v>-12.216391957817</x:v>
+        <x:v>-14.285503073689</x:v>
       </x:c>
       <x:c r="G140" s="42" t="str">
-        <x:v>12.216391957817</x:v>
+        <x:v>14.285503073689</x:v>
       </x:c>
       <x:c r="H140" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5076,22 +5076,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B141" s="36" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C141" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D141" s="42" t="str">
-        <x:v>-2.513150603252</x:v>
+        <x:v>-10.466391957817</x:v>
       </x:c>
       <x:c r="E141" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F141" s="42" t="str">
-        <x:v>-2.823150603252</x:v>
+        <x:v>-12.216391957817</x:v>
       </x:c>
       <x:c r="G141" s="42" t="str">
-        <x:v>2.823150603252</x:v>
+        <x:v>12.216391957817</x:v>
       </x:c>
       <x:c r="H141" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5105,19 +5105,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C142" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D142" s="42" t="str">
-        <x:v>1.264029937698</x:v>
+        <x:v>-2.513150603252</x:v>
       </x:c>
       <x:c r="E142" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F142" s="42" t="str">
-        <x:v>0.014029937698</x:v>
+        <x:v>-2.823150603252</x:v>
       </x:c>
       <x:c r="G142" s="42" t="str">
-        <x:v>0.014029937698</x:v>
+        <x:v>2.823150603252</x:v>
       </x:c>
       <x:c r="H142" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5131,19 +5131,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C143" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D143" s="42" t="str">
-        <x:v>1.405712159485</x:v>
+        <x:v>1.264029937698</x:v>
       </x:c>
       <x:c r="E143" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F143" s="42" t="str">
-        <x:v>-2.424287840515</x:v>
+        <x:v>0.014029937698</x:v>
       </x:c>
       <x:c r="G143" s="42" t="str">
-        <x:v>2.424287840515</x:v>
+        <x:v>0.014029937698</x:v>
       </x:c>
       <x:c r="H143" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5157,19 +5157,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C144" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D144" s="42" t="str">
-        <x:v>-1.048061577331</x:v>
+        <x:v>1.405712159485</x:v>
       </x:c>
       <x:c r="E144" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F144" s="42" t="str">
-        <x:v>-2.828061577331</x:v>
+        <x:v>-2.424287840515</x:v>
       </x:c>
       <x:c r="G144" s="42" t="str">
-        <x:v>2.828061577331</x:v>
+        <x:v>2.424287840515</x:v>
       </x:c>
       <x:c r="H144" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5183,19 +5183,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C145" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D145" s="42" t="str">
-        <x:v>-63.955235096392</x:v>
+        <x:v>-1.048061577331</x:v>
       </x:c>
       <x:c r="E145" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F145" s="42" t="str">
-        <x:v>-68.945235096392</x:v>
+        <x:v>-2.828061577331</x:v>
       </x:c>
       <x:c r="G145" s="42" t="str">
-        <x:v>68.945235096392</x:v>
+        <x:v>2.828061577331</x:v>
       </x:c>
       <x:c r="H145" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5209,19 +5209,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C146" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D146" s="42" t="str">
-        <x:v>-6.163484047291</x:v>
+        <x:v>-63.955235096392</x:v>
       </x:c>
       <x:c r="E146" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F146" s="42" t="str">
-        <x:v>-10.393484047291</x:v>
+        <x:v>-68.945235096392</x:v>
       </x:c>
       <x:c r="G146" s="42" t="str">
-        <x:v>10.393484047291</x:v>
+        <x:v>68.945235096392</x:v>
       </x:c>
       <x:c r="H146" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5235,19 +5235,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C147" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D147" s="42" t="str">
-        <x:v>-0.372876272237</x:v>
+        <x:v>-6.163484047291</x:v>
       </x:c>
       <x:c r="E147" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F147" s="42" t="str">
-        <x:v>-0.972876272237</x:v>
+        <x:v>-10.393484047291</x:v>
       </x:c>
       <x:c r="G147" s="42" t="str">
-        <x:v>0.972876272237</x:v>
+        <x:v>10.393484047291</x:v>
       </x:c>
       <x:c r="H147" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5261,19 +5261,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C148" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D148" s="42" t="str">
-        <x:v>-14.875013200229</x:v>
+        <x:v>-0.372876272237</x:v>
       </x:c>
       <x:c r="E148" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F148" s="42" t="str">
-        <x:v>-15.035013200229</x:v>
+        <x:v>-0.972876272237</x:v>
       </x:c>
       <x:c r="G148" s="42" t="str">
-        <x:v>15.035013200229</x:v>
+        <x:v>0.972876272237</x:v>
       </x:c>
       <x:c r="H148" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5287,19 +5287,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C149" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D149" s="42" t="str">
-        <x:v>0.123061371006</x:v>
+        <x:v>-14.875013200229</x:v>
       </x:c>
       <x:c r="E149" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F149" s="42" t="str">
-        <x:v>-1.996938628994</x:v>
+        <x:v>-15.035013200229</x:v>
       </x:c>
       <x:c r="G149" s="42" t="str">
-        <x:v>1.996938628994</x:v>
+        <x:v>15.035013200229</x:v>
       </x:c>
       <x:c r="H149" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5313,19 +5313,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C150" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D150" s="42" t="str">
-        <x:v>-23.938106879109</x:v>
+        <x:v>0.123061371006</x:v>
       </x:c>
       <x:c r="E150" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F150" s="42" t="str">
-        <x:v>-25.638106879109</x:v>
+        <x:v>-1.996938628994</x:v>
       </x:c>
       <x:c r="G150" s="42" t="str">
-        <x:v>25.638106879109</x:v>
+        <x:v>1.996938628994</x:v>
       </x:c>
       <x:c r="H150" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5339,19 +5339,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C151" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D151" s="42" t="str">
-        <x:v>-1.097393985422</x:v>
+        <x:v>-23.938106879109</x:v>
       </x:c>
       <x:c r="E151" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F151" s="42" t="str">
-        <x:v>-2.837393985422</x:v>
+        <x:v>-25.638106879109</x:v>
       </x:c>
       <x:c r="G151" s="42" t="str">
-        <x:v>2.837393985422</x:v>
+        <x:v>25.638106879109</x:v>
       </x:c>
       <x:c r="H151" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5365,19 +5365,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C152" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D152" s="42" t="str">
-        <x:v>-0.727230275074</x:v>
+        <x:v>-1.097393985422</x:v>
       </x:c>
       <x:c r="E152" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F152" s="42" t="str">
-        <x:v>-2.477230275074</x:v>
+        <x:v>-2.837393985422</x:v>
       </x:c>
       <x:c r="G152" s="42" t="str">
-        <x:v>2.477230275074</x:v>
+        <x:v>2.837393985422</x:v>
       </x:c>
       <x:c r="H152" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5385,25 +5385,25 @@
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
       <x:c r="A153" s="36" t="str">
-        <x:v>historical mstore-inorganic CLI</x:v>
+        <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B153" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C153" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D153" s="42" t="str">
-        <x:v>11.549596417487</x:v>
+        <x:v>-0.727230275074</x:v>
       </x:c>
       <x:c r="E153" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F153" s="42" t="str">
-        <x:v>11.239596417487</x:v>
+        <x:v>-2.477230275074</x:v>
       </x:c>
       <x:c r="G153" s="42" t="str">
-        <x:v>11.239596417487</x:v>
+        <x:v>2.477230275074</x:v>
       </x:c>
       <x:c r="H153" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5417,19 +5417,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C154" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D154" s="42" t="str">
-        <x:v>-29.811523391510</x:v>
+        <x:v>11.549596417487</x:v>
       </x:c>
       <x:c r="E154" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F154" s="42" t="str">
-        <x:v>-31.061523391510</x:v>
+        <x:v>11.239596417487</x:v>
       </x:c>
       <x:c r="G154" s="42" t="str">
-        <x:v>31.061523391510</x:v>
+        <x:v>11.239596417487</x:v>
       </x:c>
       <x:c r="H154" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5443,19 +5443,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C155" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D155" s="42" t="str">
-        <x:v>0.256599145141</x:v>
+        <x:v>-29.811523391510</x:v>
       </x:c>
       <x:c r="E155" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F155" s="42" t="str">
-        <x:v>-3.573400854859</x:v>
+        <x:v>-31.061523391510</x:v>
       </x:c>
       <x:c r="G155" s="42" t="str">
-        <x:v>3.573400854859</x:v>
+        <x:v>31.061523391510</x:v>
       </x:c>
       <x:c r="H155" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5469,19 +5469,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C156" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D156" s="42" t="str">
-        <x:v>-28.460677817350</x:v>
+        <x:v>0.256599145141</x:v>
       </x:c>
       <x:c r="E156" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F156" s="42" t="str">
-        <x:v>-30.240677817350</x:v>
+        <x:v>-3.573400854859</x:v>
       </x:c>
       <x:c r="G156" s="42" t="str">
-        <x:v>30.240677817350</x:v>
+        <x:v>3.573400854859</x:v>
       </x:c>
       <x:c r="H156" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5495,19 +5495,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C157" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D157" s="42" t="str">
-        <x:v>-151.947965741842</x:v>
+        <x:v>-28.460677817350</x:v>
       </x:c>
       <x:c r="E157" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F157" s="42" t="str">
-        <x:v>-156.937965741842</x:v>
+        <x:v>-30.240677817350</x:v>
       </x:c>
       <x:c r="G157" s="42" t="str">
-        <x:v>156.937965741842</x:v>
+        <x:v>30.240677817350</x:v>
       </x:c>
       <x:c r="H157" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5521,19 +5521,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C158" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D158" s="42" t="str">
-        <x:v>-77.417542603032</x:v>
+        <x:v>-151.947965741842</x:v>
       </x:c>
       <x:c r="E158" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F158" s="42" t="str">
-        <x:v>-81.647542603032</x:v>
+        <x:v>-156.937965741842</x:v>
       </x:c>
       <x:c r="G158" s="42" t="str">
-        <x:v>81.647542603032</x:v>
+        <x:v>156.937965741842</x:v>
       </x:c>
       <x:c r="H158" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5547,19 +5547,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C159" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D159" s="42" t="str">
-        <x:v>-24.470250890265</x:v>
+        <x:v>-77.417542603032</x:v>
       </x:c>
       <x:c r="E159" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F159" s="42" t="str">
-        <x:v>-25.070250890265</x:v>
+        <x:v>-81.647542603032</x:v>
       </x:c>
       <x:c r="G159" s="42" t="str">
-        <x:v>25.070250890265</x:v>
+        <x:v>81.647542603032</x:v>
       </x:c>
       <x:c r="H159" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5573,19 +5573,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C160" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D160" s="42" t="str">
-        <x:v>-84.549975905731</x:v>
+        <x:v>-24.470250890265</x:v>
       </x:c>
       <x:c r="E160" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F160" s="42" t="str">
-        <x:v>-84.709975905731</x:v>
+        <x:v>-25.070250890265</x:v>
       </x:c>
       <x:c r="G160" s="42" t="str">
-        <x:v>84.709975905731</x:v>
+        <x:v>25.070250890265</x:v>
       </x:c>
       <x:c r="H160" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5599,19 +5599,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C161" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D161" s="42" t="str">
-        <x:v>0.922244833924</x:v>
+        <x:v>-84.549975905731</x:v>
       </x:c>
       <x:c r="E161" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F161" s="42" t="str">
-        <x:v>-1.197755166076</x:v>
+        <x:v>-84.709975905731</x:v>
       </x:c>
       <x:c r="G161" s="42" t="str">
-        <x:v>1.197755166076</x:v>
+        <x:v>84.709975905731</x:v>
       </x:c>
       <x:c r="H161" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5625,19 +5625,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C162" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D162" s="42" t="str">
-        <x:v>-99.557194036284</x:v>
+        <x:v>0.922244833924</x:v>
       </x:c>
       <x:c r="E162" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F162" s="42" t="str">
-        <x:v>-101.257194036284</x:v>
+        <x:v>-1.197755166076</x:v>
       </x:c>
       <x:c r="G162" s="42" t="str">
-        <x:v>101.257194036284</x:v>
+        <x:v>1.197755166076</x:v>
       </x:c>
       <x:c r="H162" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5651,19 +5651,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C163" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D163" s="42" t="str">
-        <x:v>-28.664951204286</x:v>
+        <x:v>-99.557194036284</x:v>
       </x:c>
       <x:c r="E163" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F163" s="42" t="str">
-        <x:v>-30.404951204286</x:v>
+        <x:v>-101.257194036284</x:v>
       </x:c>
       <x:c r="G163" s="42" t="str">
-        <x:v>30.404951204286</x:v>
+        <x:v>101.257194036284</x:v>
       </x:c>
       <x:c r="H163" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5677,19 +5677,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C164" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D164" s="42" t="str">
-        <x:v>-25.438330429983</x:v>
+        <x:v>-28.664951204286</x:v>
       </x:c>
       <x:c r="E164" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F164" s="42" t="str">
-        <x:v>-27.188330429983</x:v>
+        <x:v>-30.404951204286</x:v>
       </x:c>
       <x:c r="G164" s="42" t="str">
-        <x:v>27.188330429983</x:v>
+        <x:v>30.404951204286</x:v>
       </x:c>
       <x:c r="H164" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5700,22 +5700,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B165" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C165" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D165" s="42" t="str">
-        <x:v>-0.279988209907</x:v>
+        <x:v>-25.438330429983</x:v>
       </x:c>
       <x:c r="E165" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F165" s="42" t="str">
-        <x:v>-0.589988209907</x:v>
+        <x:v>-27.188330429983</x:v>
       </x:c>
       <x:c r="G165" s="42" t="str">
-        <x:v>0.589988209907</x:v>
+        <x:v>27.188330429983</x:v>
       </x:c>
       <x:c r="H165" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5729,19 +5729,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C166" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D166" s="42" t="str">
-        <x:v>-1.720202220170</x:v>
+        <x:v>-0.279988209907</x:v>
       </x:c>
       <x:c r="E166" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F166" s="42" t="str">
-        <x:v>-2.970202220170</x:v>
+        <x:v>-0.589988209907</x:v>
       </x:c>
       <x:c r="G166" s="42" t="str">
-        <x:v>2.970202220170</x:v>
+        <x:v>0.589988209907</x:v>
       </x:c>
       <x:c r="H166" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5755,19 +5755,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C167" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D167" s="42" t="str">
-        <x:v>1.653583137544</x:v>
+        <x:v>-1.720202220170</x:v>
       </x:c>
       <x:c r="E167" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F167" s="42" t="str">
-        <x:v>-2.176416862456</x:v>
+        <x:v>-2.970202220170</x:v>
       </x:c>
       <x:c r="G167" s="42" t="str">
-        <x:v>2.176416862456</x:v>
+        <x:v>2.970202220170</x:v>
       </x:c>
       <x:c r="H167" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5781,19 +5781,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C168" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D168" s="42" t="str">
-        <x:v>-5.912105883998</x:v>
+        <x:v>1.653583137544</x:v>
       </x:c>
       <x:c r="E168" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F168" s="42" t="str">
-        <x:v>-7.692105883998</x:v>
+        <x:v>-2.176416862456</x:v>
       </x:c>
       <x:c r="G168" s="42" t="str">
-        <x:v>7.692105883998</x:v>
+        <x:v>2.176416862456</x:v>
       </x:c>
       <x:c r="H168" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5807,19 +5807,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C169" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D169" s="42" t="str">
-        <x:v>-77.446667006181</x:v>
+        <x:v>-5.912105883998</x:v>
       </x:c>
       <x:c r="E169" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F169" s="42" t="str">
-        <x:v>-82.436667006181</x:v>
+        <x:v>-7.692105883998</x:v>
       </x:c>
       <x:c r="G169" s="42" t="str">
-        <x:v>82.436667006181</x:v>
+        <x:v>7.692105883998</x:v>
       </x:c>
       <x:c r="H169" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5833,19 +5833,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C170" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D170" s="42" t="str">
-        <x:v>-19.706722185486</x:v>
+        <x:v>-77.446667006181</x:v>
       </x:c>
       <x:c r="E170" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F170" s="42" t="str">
-        <x:v>-23.936722185486</x:v>
+        <x:v>-82.436667006181</x:v>
       </x:c>
       <x:c r="G170" s="42" t="str">
-        <x:v>23.936722185486</x:v>
+        <x:v>82.436667006181</x:v>
       </x:c>
       <x:c r="H170" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5859,19 +5859,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C171" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D171" s="42" t="str">
-        <x:v>-2.774771626398</x:v>
+        <x:v>-19.706722185486</x:v>
       </x:c>
       <x:c r="E171" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F171" s="42" t="str">
-        <x:v>-3.374771626398</x:v>
+        <x:v>-23.936722185486</x:v>
       </x:c>
       <x:c r="G171" s="42" t="str">
-        <x:v>3.374771626398</x:v>
+        <x:v>23.936722185486</x:v>
       </x:c>
       <x:c r="H171" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5885,19 +5885,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C172" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D172" s="42" t="str">
-        <x:v>-31.168750655955</x:v>
+        <x:v>-2.774771626398</x:v>
       </x:c>
       <x:c r="E172" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F172" s="42" t="str">
-        <x:v>-31.328750655955</x:v>
+        <x:v>-3.374771626398</x:v>
       </x:c>
       <x:c r="G172" s="42" t="str">
-        <x:v>31.328750655955</x:v>
+        <x:v>3.374771626398</x:v>
       </x:c>
       <x:c r="H172" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5911,19 +5911,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C173" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D173" s="42" t="str">
-        <x:v>0.442953962487</x:v>
+        <x:v>-31.168750655955</x:v>
       </x:c>
       <x:c r="E173" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F173" s="42" t="str">
-        <x:v>-1.677046037513</x:v>
+        <x:v>-31.328750655955</x:v>
       </x:c>
       <x:c r="G173" s="42" t="str">
-        <x:v>1.677046037513</x:v>
+        <x:v>31.328750655955</x:v>
       </x:c>
       <x:c r="H173" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5937,19 +5937,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C174" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D174" s="42" t="str">
-        <x:v>-41.779791859131</x:v>
+        <x:v>0.442953962487</x:v>
       </x:c>
       <x:c r="E174" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F174" s="42" t="str">
-        <x:v>-43.479791859131</x:v>
+        <x:v>-1.677046037513</x:v>
       </x:c>
       <x:c r="G174" s="42" t="str">
-        <x:v>43.479791859131</x:v>
+        <x:v>1.677046037513</x:v>
       </x:c>
       <x:c r="H174" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5963,19 +5963,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C175" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D175" s="42" t="str">
-        <x:v>-5.934441749535</x:v>
+        <x:v>-41.779791859131</x:v>
       </x:c>
       <x:c r="E175" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F175" s="42" t="str">
-        <x:v>-7.674441749535</x:v>
+        <x:v>-43.479791859131</x:v>
       </x:c>
       <x:c r="G175" s="42" t="str">
-        <x:v>7.674441749535</x:v>
+        <x:v>43.479791859131</x:v>
       </x:c>
       <x:c r="H175" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5989,21 +5989,47 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C176" s="36" t="str">
+        <x:v>XV</x:v>
+      </x:c>
+      <x:c r="D176" s="42" t="str">
+        <x:v>-5.934441749535</x:v>
+      </x:c>
+      <x:c r="E176" s="42" t="str">
+        <x:v>1.740000</x:v>
+      </x:c>
+      <x:c r="F176" s="42" t="str">
+        <x:v>-7.674441749535</x:v>
+      </x:c>
+      <x:c r="G176" s="42" t="str">
+        <x:v>7.674441749535</x:v>
+      </x:c>
+      <x:c r="H176" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="15" hidden="0" customHeight="1">
+      <x:c r="A177" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B177" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C177" s="36" t="str">
         <x:v>XVII</x:v>
       </x:c>
-      <x:c r="D176" s="42" t="str">
+      <x:c r="D177" s="42" t="str">
         <x:v>-4.880577524129</x:v>
       </x:c>
-      <x:c r="E176" s="42" t="str">
+      <x:c r="E177" s="42" t="str">
         <x:v>1.750000</x:v>
       </x:c>
-      <x:c r="F176" s="42" t="str">
+      <x:c r="F177" s="42" t="str">
         <x:v>-6.630577524129</x:v>
       </x:c>
-      <x:c r="G176" s="42" t="str">
+      <x:c r="G177" s="42" t="str">
         <x:v>6.630577524129</x:v>
       </x:c>
-      <x:c r="H176" s="36" t="str">
+      <x:c r="H177" s="36" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
@@ -10892,6 +10918,32 @@
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
+      <x:c r="A81" s="36" t="str">
+        <x:v>CP2K-native pbc provider</x:v>
+      </x:c>
+      <x:c r="B81" s="36" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C81" s="36" t="str">
+        <x:v>XIV</x:v>
+      </x:c>
+      <x:c r="D81" s="42" t="str">
+        <x:v>0.090455358961</x:v>
+      </x:c>
+      <x:c r="E81" s="42" t="str">
+        <x:v>1.700000</x:v>
+      </x:c>
+      <x:c r="F81" s="42" t="str">
+        <x:v>-1.609544641039</x:v>
+      </x:c>
+      <x:c r="G81" s="42" t="str">
+        <x:v>1.609544641039</x:v>
+      </x:c>
+      <x:c r="H81" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/DMC-ICE13/reproduction/seidler_dmc13_recalculation/comparison_workbook.xlsx
+++ b/DMC-ICE13/reproduction/seidler_dmc13_recalculation/comparison_workbook.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Reabe28064c9f4899"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch statistics" sheetId="2" r:id="R19074c89ad274ecd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative energies" sheetId="3" r:id="R28b99a65c7c64fed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch differences" sheetId="4" r:id="Rc54c27faba284aae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absolute parity" sheetId="5" r:id="Rf7071fc64d1445b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Native meshes" sheetId="6" r:id="R4de1317794b244e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mstore absolute" sheetId="7" r:id="R4b23f8a383e84758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="8" r:id="Re9f51ea73f9f442b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R143bfb9c0f194c1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch statistics" sheetId="2" r:id="Red175082568a434f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative energies" sheetId="3" r:id="R42a0f59b0a554140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch differences" sheetId="4" r:id="Rfef6cab5e87149a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absolute parity" sheetId="5" r:id="Rda6b4d1b66c04a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Native meshes" sheetId="6" r:id="Rdfee209259314721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mstore absolute" sheetId="7" r:id="R2a51f1bdebd24f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="8" r:id="R76beba646cb74d32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -305,7 +305,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Summary'!$A$13:$A$14</c:f>
+              <c:f>'Summary'!$A$13:$A$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -313,7 +313,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Summary'!$B$13:$B$14</c:f>
+              <c:f>'Summary'!$B$13:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="0"/>
@@ -332,7 +332,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Summary'!$A$13:$A$14</c:f>
+              <c:f>'Summary'!$A$13:$A$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -340,7 +340,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Summary'!$C$13:$C$14</c:f>
+              <c:f>'Summary'!$C$13:$C$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="0"/>
@@ -359,7 +359,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Summary'!$A$13:$A$14</c:f>
+              <c:f>'Summary'!$A$13:$A$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -367,7 +367,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Summary'!$D$13:$D$14</c:f>
+              <c:f>'Summary'!$D$13:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="0"/>
@@ -386,7 +386,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Summary'!$A$13:$A$14</c:f>
+              <c:f>'Summary'!$A$13:$A$15</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -394,7 +394,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Summary'!$E$13:$E$14</c:f>
+              <c:f>'Summary'!$E$13:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="0"/>
@@ -524,7 +524,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R228f9dcc45974e94"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0d786a217f1641c7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -853,43 +853,61 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B13" s="17" t="str">
+        <x:f>'Branch statistics'!E2</x:f>
+        <x:v>163.834465429086</x:v>
+      </x:c>
+      <x:c r="C13" s="17" t="str">
+        <x:f>'Branch statistics'!E9</x:f>
+        <x:v>163.834466022141</x:v>
+      </x:c>
+      <x:c r="D13" s="17"/>
+      <x:c r="E13" s="17" t="str">
+        <x:f>'Branch statistics'!E13</x:f>
+        <x:v>130.899820154311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="str">
+      <x:c r="B14" s="17" t="str">
         <x:f>'Branch statistics'!E3</x:f>
         <x:v>88.681375103720</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="str">
+      <x:c r="C14" s="17" t="str">
         <x:f>'Branch statistics'!E10</x:f>
         <x:v>88.681375574198</x:v>
       </x:c>
-      <x:c r="D13" s="17" t="str">
+      <x:c r="D14" s="17" t="str">
         <x:f>'Branch statistics'!E7</x:f>
         <x:v>88.706865721959</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="str">
-        <x:f>'Branch statistics'!E13</x:f>
+      <x:c r="E14" s="17" t="str">
+        <x:f>'Branch statistics'!E14</x:f>
         <x:v>48.710763704892</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="11" t="n">
+    <x:row r="15">
+      <x:c r="A15" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="str">
+      <x:c r="B15" s="17" t="str">
         <x:f>'Branch statistics'!E4</x:f>
         <x:v>34.048487494128</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="str">
+      <x:c r="C15" s="17" t="str">
         <x:f>'Branch statistics'!E11</x:f>
         <x:v>34.048491879836</x:v>
       </x:c>
-      <x:c r="D14" s="17" t="str">
+      <x:c r="D15" s="17" t="str">
         <x:f>'Branch statistics'!E8</x:f>
         <x:v>34.070588090850</x:v>
       </x:c>
-      <x:c r="E14" s="17" t="str">
-        <x:f>'Branch statistics'!E14</x:f>
+      <x:c r="E15" s="17" t="str">
+        <x:f>'Branch statistics'!E15</x:f>
         <x:v>17.830623485072</x:v>
       </x:c>
     </x:row>
@@ -1061,7 +1079,7 @@
     <x:mergeCell ref="A24:E24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fb42972e9f043d0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1baf0f69a85426e"/>
 </x:worksheet>
 </file>
 
@@ -1359,22 +1377,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B13" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C13" s="36" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D13" s="41" t="str">
-        <x:v>-46.837497635311</x:v>
+        <x:v>-127.290755088539</x:v>
       </x:c>
       <x:c r="E13" s="41" t="str">
-        <x:v>48.710763704892</x:v>
+        <x:v>130.899820154311</x:v>
       </x:c>
       <x:c r="F13" s="41" t="str">
-        <x:v>66.480998967341</x:v>
+        <x:v>155.257907693709</x:v>
       </x:c>
       <x:c r="G13" s="41" t="str">
-        <x:v>156.937965741842</x:v>
+        <x:v>264.186245399110</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -1382,26 +1400,49 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B14" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="36" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D14" s="41" t="str">
+        <x:v>-46.837497635311</x:v>
+      </x:c>
+      <x:c r="E14" s="41" t="str">
+        <x:v>48.710763704892</x:v>
+      </x:c>
+      <x:c r="F14" s="41" t="str">
+        <x:v>66.480998967341</x:v>
+      </x:c>
+      <x:c r="G14" s="41" t="str">
+        <x:v>156.937965741842</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B15" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C15" s="36" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D15" s="41" t="str">
         <x:v>-17.830623485072</x:v>
       </x:c>
-      <x:c r="E14" s="41" t="str">
+      <x:c r="E15" s="41" t="str">
         <x:v>17.830623485072</x:v>
       </x:c>
-      <x:c r="F14" s="41" t="str">
+      <x:c r="F15" s="41" t="str">
         <x:v>29.482893777393</x:v>
       </x:c>
-      <x:c r="G14" s="41" t="str">
+      <x:c r="G15" s="41" t="str">
         <x:v>82.436667006181</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="E2:E14">
+  <x:conditionalFormatting sqref="E2:E15">
     <x:cfRule type="colorScale" priority="1">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -3389,19 +3430,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C76" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D76" s="42" t="str">
-        <x:v>-0.111024864121</x:v>
+        <x:v>0.420415546280</x:v>
       </x:c>
       <x:c r="E76" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F76" s="42" t="str">
-        <x:v>-1.811024864121</x:v>
+        <x:v>0.260415546280</x:v>
       </x:c>
       <x:c r="G76" s="42" t="str">
-        <x:v>1.811024864121</x:v>
+        <x:v>0.260415546280</x:v>
       </x:c>
       <x:c r="H76" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3415,19 +3456,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C77" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D77" s="42" t="str">
-        <x:v>0.635864765327</x:v>
+        <x:v>-0.111024864121</x:v>
       </x:c>
       <x:c r="E77" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F77" s="42" t="str">
-        <x:v>-1.104135234673</x:v>
+        <x:v>-1.811024864121</x:v>
       </x:c>
       <x:c r="G77" s="42" t="str">
-        <x:v>1.104135234673</x:v>
+        <x:v>1.811024864121</x:v>
       </x:c>
       <x:c r="H77" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3441,19 +3482,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C78" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D78" s="42" t="str">
-        <x:v>0.672285685199</x:v>
+        <x:v>0.635864765327</x:v>
       </x:c>
       <x:c r="E78" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F78" s="42" t="str">
-        <x:v>-1.077714314801</x:v>
+        <x:v>-1.104135234673</x:v>
       </x:c>
       <x:c r="G78" s="42" t="str">
-        <x:v>1.077714314801</x:v>
+        <x:v>1.104135234673</x:v>
       </x:c>
       <x:c r="H78" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3464,22 +3505,22 @@
         <x:v>CP2K-native pbc provider</x:v>
       </x:c>
       <x:c r="B79" s="36" t="str">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C79" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D79" s="42" t="str">
-        <x:v>-0.441453685894</x:v>
+        <x:v>0.672285685199</x:v>
       </x:c>
       <x:c r="E79" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F79" s="42" t="str">
-        <x:v>-5.431453685894</x:v>
+        <x:v>-1.077714314801</x:v>
       </x:c>
       <x:c r="G79" s="42" t="str">
-        <x:v>5.431453685894</x:v>
+        <x:v>1.077714314801</x:v>
       </x:c>
       <x:c r="H79" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3493,19 +3534,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C80" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D80" s="42" t="str">
-        <x:v>1.810235969010</x:v>
+        <x:v>-0.441453685894</x:v>
       </x:c>
       <x:c r="E80" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F80" s="42" t="str">
-        <x:v>-2.419764030990</x:v>
+        <x:v>-5.431453685894</x:v>
       </x:c>
       <x:c r="G80" s="42" t="str">
-        <x:v>2.419764030990</x:v>
+        <x:v>5.431453685894</x:v>
       </x:c>
       <x:c r="H80" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3519,19 +3560,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C81" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D81" s="42" t="str">
-        <x:v>0.090455358961</x:v>
+        <x:v>1.810235969010</x:v>
       </x:c>
       <x:c r="E81" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F81" s="42" t="str">
-        <x:v>-1.609544641039</x:v>
+        <x:v>-2.419764030990</x:v>
       </x:c>
       <x:c r="G81" s="42" t="str">
-        <x:v>1.609544641039</x:v>
+        <x:v>2.419764030990</x:v>
       </x:c>
       <x:c r="H81" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3539,25 +3580,25 @@
     </x:row>
     <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="36" t="str">
-        <x:v>author pbc CLI</x:v>
+        <x:v>CP2K-native pbc provider</x:v>
       </x:c>
       <x:c r="B82" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C82" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D82" s="42" t="str">
-        <x:v>-40.056162616318</x:v>
+        <x:v>0.090455358961</x:v>
       </x:c>
       <x:c r="E82" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F82" s="42" t="str">
-        <x:v>-40.366162616318</x:v>
+        <x:v>-1.609544641039</x:v>
       </x:c>
       <x:c r="G82" s="42" t="str">
-        <x:v>40.366162616318</x:v>
+        <x:v>1.609544641039</x:v>
       </x:c>
       <x:c r="H82" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3571,19 +3612,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C83" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D83" s="42" t="str">
-        <x:v>-21.728016057439</x:v>
+        <x:v>-40.056162616318</x:v>
       </x:c>
       <x:c r="E83" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F83" s="42" t="str">
-        <x:v>-22.978016057439</x:v>
+        <x:v>-40.366162616318</x:v>
       </x:c>
       <x:c r="G83" s="42" t="str">
-        <x:v>22.978016057439</x:v>
+        <x:v>40.366162616318</x:v>
       </x:c>
       <x:c r="H83" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3597,19 +3638,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C84" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D84" s="42" t="str">
-        <x:v>14.909575775296</x:v>
+        <x:v>-21.728016057439</x:v>
       </x:c>
       <x:c r="E84" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F84" s="42" t="str">
-        <x:v>11.079575775296</x:v>
+        <x:v>-22.978016057439</x:v>
       </x:c>
       <x:c r="G84" s="42" t="str">
-        <x:v>11.079575775296</x:v>
+        <x:v>22.978016057439</x:v>
       </x:c>
       <x:c r="H84" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3623,19 +3664,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C85" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D85" s="42" t="str">
-        <x:v>-57.502753280215</x:v>
+        <x:v>14.909575775296</x:v>
       </x:c>
       <x:c r="E85" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F85" s="42" t="str">
-        <x:v>-59.282753280215</x:v>
+        <x:v>11.079575775296</x:v>
       </x:c>
       <x:c r="G85" s="42" t="str">
-        <x:v>59.282753280215</x:v>
+        <x:v>11.079575775296</x:v>
       </x:c>
       <x:c r="H85" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3649,19 +3690,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C86" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D86" s="42" t="str">
-        <x:v>-300.067320161804</x:v>
+        <x:v>-57.502753280215</x:v>
       </x:c>
       <x:c r="E86" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F86" s="42" t="str">
-        <x:v>-305.057320161804</x:v>
+        <x:v>-59.282753280215</x:v>
       </x:c>
       <x:c r="G86" s="42" t="str">
-        <x:v>305.057320161804</x:v>
+        <x:v>59.282753280215</x:v>
       </x:c>
       <x:c r="H86" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3675,19 +3716,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C87" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D87" s="42" t="str">
-        <x:v>-121.498882525679</x:v>
+        <x:v>-300.067320161804</x:v>
       </x:c>
       <x:c r="E87" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F87" s="42" t="str">
-        <x:v>-125.728882525679</x:v>
+        <x:v>-305.057320161804</x:v>
       </x:c>
       <x:c r="G87" s="42" t="str">
-        <x:v>125.728882525679</x:v>
+        <x:v>305.057320161804</x:v>
       </x:c>
       <x:c r="H87" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3701,19 +3742,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C88" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D88" s="42" t="str">
-        <x:v>-14.812836787859</x:v>
+        <x:v>-121.498882525679</x:v>
       </x:c>
       <x:c r="E88" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F88" s="42" t="str">
-        <x:v>-15.412836787859</x:v>
+        <x:v>-125.728882525679</x:v>
       </x:c>
       <x:c r="G88" s="42" t="str">
-        <x:v>15.412836787859</x:v>
+        <x:v>125.728882525679</x:v>
       </x:c>
       <x:c r="H88" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3727,19 +3768,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C89" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D89" s="42" t="str">
-        <x:v>-165.257377908596</x:v>
+        <x:v>-14.812836787859</x:v>
       </x:c>
       <x:c r="E89" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F89" s="42" t="str">
-        <x:v>-165.417377908596</x:v>
+        <x:v>-15.412836787859</x:v>
       </x:c>
       <x:c r="G89" s="42" t="str">
-        <x:v>165.417377908596</x:v>
+        <x:v>15.412836787859</x:v>
       </x:c>
       <x:c r="H89" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3753,19 +3794,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C90" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D90" s="42" t="str">
-        <x:v>6.868364020212</x:v>
+        <x:v>-165.257377908596</x:v>
       </x:c>
       <x:c r="E90" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F90" s="42" t="str">
-        <x:v>4.748364020212</x:v>
+        <x:v>-165.417377908596</x:v>
       </x:c>
       <x:c r="G90" s="42" t="str">
-        <x:v>4.748364020212</x:v>
+        <x:v>165.417377908596</x:v>
       </x:c>
       <x:c r="H90" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3779,19 +3820,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C91" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D91" s="42" t="str">
-        <x:v>-199.611684777200</x:v>
+        <x:v>6.868364020212</x:v>
       </x:c>
       <x:c r="E91" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F91" s="42" t="str">
-        <x:v>-201.311684777200</x:v>
+        <x:v>4.748364020212</x:v>
       </x:c>
       <x:c r="G91" s="42" t="str">
-        <x:v>201.311684777200</x:v>
+        <x:v>4.748364020212</x:v>
       </x:c>
       <x:c r="H91" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3805,19 +3846,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C92" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D92" s="42" t="str">
-        <x:v>-58.050293332028</x:v>
+        <x:v>-199.611684777200</x:v>
       </x:c>
       <x:c r="E92" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F92" s="42" t="str">
-        <x:v>-59.790293332028</x:v>
+        <x:v>-201.311684777200</x:v>
       </x:c>
       <x:c r="G92" s="42" t="str">
-        <x:v>59.790293332028</x:v>
+        <x:v>201.311684777200</x:v>
       </x:c>
       <x:c r="H92" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3831,19 +3872,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C93" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D93" s="42" t="str">
-        <x:v>-51.559121420866</x:v>
+        <x:v>-58.050293332028</x:v>
       </x:c>
       <x:c r="E93" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F93" s="42" t="str">
-        <x:v>-53.309121420866</x:v>
+        <x:v>-59.790293332028</x:v>
       </x:c>
       <x:c r="G93" s="42" t="str">
-        <x:v>53.309121420866</x:v>
+        <x:v>59.790293332028</x:v>
       </x:c>
       <x:c r="H93" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3854,22 +3895,22 @@
         <x:v>author pbc CLI</x:v>
       </x:c>
       <x:c r="B94" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C94" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D94" s="42" t="str">
-        <x:v>-9.054674468559</x:v>
+        <x:v>-51.559121420866</x:v>
       </x:c>
       <x:c r="E94" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F94" s="42" t="str">
-        <x:v>-9.364674468559</x:v>
+        <x:v>-53.309121420866</x:v>
       </x:c>
       <x:c r="G94" s="42" t="str">
-        <x:v>9.364674468559</x:v>
+        <x:v>53.309121420866</x:v>
       </x:c>
       <x:c r="H94" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3883,19 +3924,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C95" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D95" s="42" t="str">
-        <x:v>-2.341718734421</x:v>
+        <x:v>-9.054674468559</x:v>
       </x:c>
       <x:c r="E95" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F95" s="42" t="str">
-        <x:v>-3.591718734421</x:v>
+        <x:v>-9.364674468559</x:v>
       </x:c>
       <x:c r="G95" s="42" t="str">
-        <x:v>3.591718734421</x:v>
+        <x:v>9.364674468559</x:v>
       </x:c>
       <x:c r="H95" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3909,19 +3950,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C96" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D96" s="42" t="str">
-        <x:v>2.892295286943</x:v>
+        <x:v>-2.341718734421</x:v>
       </x:c>
       <x:c r="E96" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F96" s="42" t="str">
-        <x:v>-0.937704713057</x:v>
+        <x:v>-3.591718734421</x:v>
       </x:c>
       <x:c r="G96" s="42" t="str">
-        <x:v>0.937704713057</x:v>
+        <x:v>3.591718734421</x:v>
       </x:c>
       <x:c r="H96" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3935,19 +3976,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C97" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D97" s="42" t="str">
-        <x:v>-12.421511801622</x:v>
+        <x:v>2.892295286943</x:v>
       </x:c>
       <x:c r="E97" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F97" s="42" t="str">
-        <x:v>-14.201511801622</x:v>
+        <x:v>-0.937704713057</x:v>
       </x:c>
       <x:c r="G97" s="42" t="str">
-        <x:v>14.201511801622</x:v>
+        <x:v>0.937704713057</x:v>
       </x:c>
       <x:c r="H97" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3961,19 +4002,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C98" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D98" s="42" t="str">
-        <x:v>-153.975297576434</x:v>
+        <x:v>-12.421511801622</x:v>
       </x:c>
       <x:c r="E98" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F98" s="42" t="str">
-        <x:v>-158.965297576434</x:v>
+        <x:v>-14.201511801622</x:v>
       </x:c>
       <x:c r="G98" s="42" t="str">
-        <x:v>158.965297576434</x:v>
+        <x:v>14.201511801622</x:v>
       </x:c>
       <x:c r="H98" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3987,19 +4028,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C99" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D99" s="42" t="str">
-        <x:v>-38.490190110106</x:v>
+        <x:v>-153.975297576434</x:v>
       </x:c>
       <x:c r="E99" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F99" s="42" t="str">
-        <x:v>-42.720190110106</x:v>
+        <x:v>-158.965297576434</x:v>
       </x:c>
       <x:c r="G99" s="42" t="str">
-        <x:v>42.720190110106</x:v>
+        <x:v>158.965297576434</x:v>
       </x:c>
       <x:c r="H99" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4013,19 +4054,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C100" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D100" s="42" t="str">
-        <x:v>-2.462552657305</x:v>
+        <x:v>-38.490190110106</x:v>
       </x:c>
       <x:c r="E100" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F100" s="42" t="str">
-        <x:v>-3.062552657305</x:v>
+        <x:v>-42.720190110106</x:v>
       </x:c>
       <x:c r="G100" s="42" t="str">
-        <x:v>3.062552657305</x:v>
+        <x:v>42.720190110106</x:v>
       </x:c>
       <x:c r="H100" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4039,19 +4080,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C101" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D101" s="42" t="str">
-        <x:v>-62.538655042867</x:v>
+        <x:v>-2.462552657305</x:v>
       </x:c>
       <x:c r="E101" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F101" s="42" t="str">
-        <x:v>-62.698655042867</x:v>
+        <x:v>-3.062552657305</x:v>
       </x:c>
       <x:c r="G101" s="42" t="str">
-        <x:v>62.698655042867</x:v>
+        <x:v>3.062552657305</x:v>
       </x:c>
       <x:c r="H101" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4065,19 +4106,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C102" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D102" s="42" t="str">
-        <x:v>0.923689537732</x:v>
+        <x:v>-62.538655042867</x:v>
       </x:c>
       <x:c r="E102" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F102" s="42" t="str">
-        <x:v>-1.196310462268</x:v>
+        <x:v>-62.698655042867</x:v>
       </x:c>
       <x:c r="G102" s="42" t="str">
-        <x:v>1.196310462268</x:v>
+        <x:v>62.698655042867</x:v>
       </x:c>
       <x:c r="H102" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4091,19 +4132,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C103" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D103" s="42" t="str">
-        <x:v>-83.903026598902</x:v>
+        <x:v>0.923689537732</x:v>
       </x:c>
       <x:c r="E103" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F103" s="42" t="str">
-        <x:v>-85.603026598902</x:v>
+        <x:v>-1.196310462268</x:v>
       </x:c>
       <x:c r="G103" s="42" t="str">
-        <x:v>85.603026598902</x:v>
+        <x:v>1.196310462268</x:v>
       </x:c>
       <x:c r="H103" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4117,19 +4158,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C104" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D104" s="42" t="str">
-        <x:v>-12.548998010281</x:v>
+        <x:v>-83.903026598902</x:v>
       </x:c>
       <x:c r="E104" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F104" s="42" t="str">
-        <x:v>-14.288998010281</x:v>
+        <x:v>-85.603026598902</x:v>
       </x:c>
       <x:c r="G104" s="42" t="str">
-        <x:v>14.288998010281</x:v>
+        <x:v>85.603026598902</x:v>
       </x:c>
       <x:c r="H104" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4143,19 +4184,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C105" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D105" s="42" t="str">
-        <x:v>-10.466416914384</x:v>
+        <x:v>-12.548998010281</x:v>
       </x:c>
       <x:c r="E105" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F105" s="42" t="str">
-        <x:v>-12.216416914384</x:v>
+        <x:v>-14.288998010281</x:v>
       </x:c>
       <x:c r="G105" s="42" t="str">
-        <x:v>12.216416914384</x:v>
+        <x:v>14.288998010281</x:v>
       </x:c>
       <x:c r="H105" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4163,25 +4204,25 @@
     </x:row>
     <x:row r="106" ht="15" hidden="0" customHeight="1">
       <x:c r="A106" s="36" t="str">
-        <x:v>current pbc CLI</x:v>
+        <x:v>author pbc CLI</x:v>
       </x:c>
       <x:c r="B106" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C106" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D106" s="42" t="str">
-        <x:v>-85.402832480791</x:v>
+        <x:v>-10.466416914384</x:v>
       </x:c>
       <x:c r="E106" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F106" s="42" t="str">
-        <x:v>-85.712832480791</x:v>
+        <x:v>-12.216416914384</x:v>
       </x:c>
       <x:c r="G106" s="42" t="str">
-        <x:v>85.712832480791</x:v>
+        <x:v>12.216416914384</x:v>
       </x:c>
       <x:c r="H106" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4195,19 +4236,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C107" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D107" s="42" t="str">
-        <x:v>-52.784771448006</x:v>
+        <x:v>-85.402832480791</x:v>
       </x:c>
       <x:c r="E107" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F107" s="42" t="str">
-        <x:v>-54.034771448006</x:v>
+        <x:v>-85.712832480791</x:v>
       </x:c>
       <x:c r="G107" s="42" t="str">
-        <x:v>54.034771448006</x:v>
+        <x:v>85.712832480791</x:v>
       </x:c>
       <x:c r="H107" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4221,19 +4262,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C108" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D108" s="42" t="str">
-        <x:v>38.666296487481</x:v>
+        <x:v>-52.784771448006</x:v>
       </x:c>
       <x:c r="E108" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F108" s="42" t="str">
-        <x:v>34.836296487481</x:v>
+        <x:v>-54.034771448006</x:v>
       </x:c>
       <x:c r="G108" s="42" t="str">
-        <x:v>34.836296487481</x:v>
+        <x:v>54.034771448006</x:v>
       </x:c>
       <x:c r="H108" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4247,19 +4288,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C109" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D109" s="42" t="str">
-        <x:v>-119.951876462899</x:v>
+        <x:v>38.666296487481</x:v>
       </x:c>
       <x:c r="E109" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F109" s="42" t="str">
-        <x:v>-121.731876462899</x:v>
+        <x:v>34.836296487481</x:v>
       </x:c>
       <x:c r="G109" s="42" t="str">
-        <x:v>121.731876462899</x:v>
+        <x:v>34.836296487481</x:v>
       </x:c>
       <x:c r="H109" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4273,19 +4314,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C110" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D110" s="42" t="str">
-        <x:v>-491.873083815613</x:v>
+        <x:v>-119.951876462899</x:v>
       </x:c>
       <x:c r="E110" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F110" s="42" t="str">
-        <x:v>-496.863083815613</x:v>
+        <x:v>-121.731876462899</x:v>
       </x:c>
       <x:c r="G110" s="42" t="str">
-        <x:v>496.863083815613</x:v>
+        <x:v>121.731876462899</x:v>
       </x:c>
       <x:c r="H110" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4299,19 +4340,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C111" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D111" s="42" t="str">
-        <x:v>-227.181421040355</x:v>
+        <x:v>-491.873083815613</x:v>
       </x:c>
       <x:c r="E111" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F111" s="42" t="str">
-        <x:v>-231.411421040355</x:v>
+        <x:v>-496.863083815613</x:v>
       </x:c>
       <x:c r="G111" s="42" t="str">
-        <x:v>231.411421040355</x:v>
+        <x:v>496.863083815613</x:v>
       </x:c>
       <x:c r="H111" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4325,19 +4366,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C112" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D112" s="42" t="str">
-        <x:v>-36.269951925783</x:v>
+        <x:v>-227.181421040355</x:v>
       </x:c>
       <x:c r="E112" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F112" s="42" t="str">
-        <x:v>-36.869951925783</x:v>
+        <x:v>-231.411421040355</x:v>
       </x:c>
       <x:c r="G112" s="42" t="str">
-        <x:v>36.869951925783</x:v>
+        <x:v>231.411421040355</x:v>
       </x:c>
       <x:c r="H112" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4351,19 +4392,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C113" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D113" s="42" t="str">
-        <x:v>-299.258518836626</x:v>
+        <x:v>-36.269951925783</x:v>
       </x:c>
       <x:c r="E113" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F113" s="42" t="str">
-        <x:v>-299.418518836626</x:v>
+        <x:v>-36.869951925783</x:v>
       </x:c>
       <x:c r="G113" s="42" t="str">
-        <x:v>299.418518836626</x:v>
+        <x:v>36.869951925783</x:v>
       </x:c>
       <x:c r="H113" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4377,19 +4418,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C114" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D114" s="42" t="str">
-        <x:v>16.464730608559</x:v>
+        <x:v>-299.258518836626</x:v>
       </x:c>
       <x:c r="E114" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F114" s="42" t="str">
-        <x:v>14.344730608559</x:v>
+        <x:v>-299.418518836626</x:v>
       </x:c>
       <x:c r="G114" s="42" t="str">
-        <x:v>14.344730608559</x:v>
+        <x:v>299.418518836626</x:v>
       </x:c>
       <x:c r="H114" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4403,19 +4444,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C115" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D115" s="42" t="str">
-        <x:v>-351.956576532881</x:v>
+        <x:v>16.464730608559</x:v>
       </x:c>
       <x:c r="E115" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F115" s="42" t="str">
-        <x:v>-353.656576532881</x:v>
+        <x:v>14.344730608559</x:v>
       </x:c>
       <x:c r="G115" s="42" t="str">
-        <x:v>353.656576532881</x:v>
+        <x:v>14.344730608559</x:v>
       </x:c>
       <x:c r="H115" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4429,19 +4470,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C116" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D116" s="42" t="str">
-        <x:v>-121.156628176656</x:v>
+        <x:v>-351.956576532881</x:v>
       </x:c>
       <x:c r="E116" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F116" s="42" t="str">
-        <x:v>-122.896628176656</x:v>
+        <x:v>-353.656576532881</x:v>
       </x:c>
       <x:c r="G116" s="42" t="str">
-        <x:v>122.896628176656</x:v>
+        <x:v>353.656576532881</x:v>
       </x:c>
       <x:c r="H116" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4455,19 +4496,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C117" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D117" s="42" t="str">
-        <x:v>-112.486904450047</x:v>
+        <x:v>-121.156628176656</x:v>
       </x:c>
       <x:c r="E117" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F117" s="42" t="str">
-        <x:v>-114.236904450047</x:v>
+        <x:v>-122.896628176656</x:v>
       </x:c>
       <x:c r="G117" s="42" t="str">
-        <x:v>114.236904450047</x:v>
+        <x:v>122.896628176656</x:v>
       </x:c>
       <x:c r="H117" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4478,22 +4519,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B118" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C118" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D118" s="42" t="str">
-        <x:v>-40.052769548562</x:v>
+        <x:v>-112.486904450047</x:v>
       </x:c>
       <x:c r="E118" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F118" s="42" t="str">
-        <x:v>-40.362769548562</x:v>
+        <x:v>-114.236904450047</x:v>
       </x:c>
       <x:c r="G118" s="42" t="str">
-        <x:v>40.362769548562</x:v>
+        <x:v>114.236904450047</x:v>
       </x:c>
       <x:c r="H118" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4507,19 +4548,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C119" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D119" s="42" t="str">
-        <x:v>-21.669458368756</x:v>
+        <x:v>-40.052769548562</x:v>
       </x:c>
       <x:c r="E119" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F119" s="42" t="str">
-        <x:v>-22.919458368756</x:v>
+        <x:v>-40.362769548562</x:v>
       </x:c>
       <x:c r="G119" s="42" t="str">
-        <x:v>22.919458368756</x:v>
+        <x:v>40.362769548562</x:v>
       </x:c>
       <x:c r="H119" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4533,19 +4574,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C120" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D120" s="42" t="str">
-        <x:v>14.926647908813</x:v>
+        <x:v>-21.669458368756</x:v>
       </x:c>
       <x:c r="E120" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F120" s="42" t="str">
-        <x:v>11.096647908813</x:v>
+        <x:v>-22.919458368756</x:v>
       </x:c>
       <x:c r="G120" s="42" t="str">
-        <x:v>11.096647908813</x:v>
+        <x:v>22.919458368756</x:v>
       </x:c>
       <x:c r="H120" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4559,19 +4600,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C121" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D121" s="42" t="str">
-        <x:v>-57.367276074495</x:v>
+        <x:v>14.926647908813</x:v>
       </x:c>
       <x:c r="E121" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F121" s="42" t="str">
-        <x:v>-59.147276074495</x:v>
+        <x:v>11.096647908813</x:v>
       </x:c>
       <x:c r="G121" s="42" t="str">
-        <x:v>59.147276074495</x:v>
+        <x:v>11.096647908813</x:v>
       </x:c>
       <x:c r="H121" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4585,19 +4626,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C122" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D122" s="42" t="str">
-        <x:v>-299.975204903283</x:v>
+        <x:v>-57.367276074495</x:v>
       </x:c>
       <x:c r="E122" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F122" s="42" t="str">
-        <x:v>-304.965204903283</x:v>
+        <x:v>-59.147276074495</x:v>
       </x:c>
       <x:c r="G122" s="42" t="str">
-        <x:v>304.965204903283</x:v>
+        <x:v>59.147276074495</x:v>
       </x:c>
       <x:c r="H122" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4611,19 +4652,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C123" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D123" s="42" t="str">
-        <x:v>-121.493623038083</x:v>
+        <x:v>-299.975204903283</x:v>
       </x:c>
       <x:c r="E123" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F123" s="42" t="str">
-        <x:v>-125.723623038083</x:v>
+        <x:v>-304.965204903283</x:v>
       </x:c>
       <x:c r="G123" s="42" t="str">
-        <x:v>125.723623038083</x:v>
+        <x:v>304.965204903283</x:v>
       </x:c>
       <x:c r="H123" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4637,19 +4678,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C124" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D124" s="42" t="str">
-        <x:v>-14.811033266160</x:v>
+        <x:v>-121.493623038083</x:v>
       </x:c>
       <x:c r="E124" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F124" s="42" t="str">
-        <x:v>-15.411033266160</x:v>
+        <x:v>-125.723623038083</x:v>
       </x:c>
       <x:c r="G124" s="42" t="str">
-        <x:v>15.411033266160</x:v>
+        <x:v>125.723623038083</x:v>
       </x:c>
       <x:c r="H124" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4663,19 +4704,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C125" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D125" s="42" t="str">
-        <x:v>-165.236809268426</x:v>
+        <x:v>-14.811033266160</x:v>
       </x:c>
       <x:c r="E125" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F125" s="42" t="str">
-        <x:v>-165.396809268426</x:v>
+        <x:v>-15.411033266160</x:v>
       </x:c>
       <x:c r="G125" s="42" t="str">
-        <x:v>165.396809268426</x:v>
+        <x:v>15.411033266160</x:v>
       </x:c>
       <x:c r="H125" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4689,19 +4730,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C126" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D126" s="42" t="str">
-        <x:v>6.872357662713</x:v>
+        <x:v>-165.236809268426</x:v>
       </x:c>
       <x:c r="E126" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F126" s="42" t="str">
-        <x:v>4.752357662713</x:v>
+        <x:v>-165.396809268426</x:v>
       </x:c>
       <x:c r="G126" s="42" t="str">
-        <x:v>4.752357662713</x:v>
+        <x:v>165.396809268426</x:v>
       </x:c>
       <x:c r="H126" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4715,19 +4756,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C127" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D127" s="42" t="str">
-        <x:v>-199.607041791688</x:v>
+        <x:v>6.872357662713</x:v>
       </x:c>
       <x:c r="E127" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F127" s="42" t="str">
-        <x:v>-201.307041791688</x:v>
+        <x:v>4.752357662713</x:v>
       </x:c>
       <x:c r="G127" s="42" t="str">
-        <x:v>201.307041791688</x:v>
+        <x:v>4.752357662713</x:v>
       </x:c>
       <x:c r="H127" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4741,19 +4782,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C128" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D128" s="42" t="str">
-        <x:v>-58.045564075785</x:v>
+        <x:v>-199.607041791688</x:v>
       </x:c>
       <x:c r="E128" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F128" s="42" t="str">
-        <x:v>-59.785564075785</x:v>
+        <x:v>-201.307041791688</x:v>
       </x:c>
       <x:c r="G128" s="42" t="str">
-        <x:v>59.785564075785</x:v>
+        <x:v>201.307041791688</x:v>
       </x:c>
       <x:c r="H128" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4767,19 +4808,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C129" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D129" s="42" t="str">
-        <x:v>-51.558720983607</x:v>
+        <x:v>-58.045564075785</x:v>
       </x:c>
       <x:c r="E129" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F129" s="42" t="str">
-        <x:v>-53.308720983607</x:v>
+        <x:v>-59.785564075785</x:v>
       </x:c>
       <x:c r="G129" s="42" t="str">
-        <x:v>53.308720983607</x:v>
+        <x:v>59.785564075785</x:v>
       </x:c>
       <x:c r="H129" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4790,22 +4831,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B130" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C130" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D130" s="42" t="str">
-        <x:v>-9.052128552229</x:v>
+        <x:v>-51.558720983607</x:v>
       </x:c>
       <x:c r="E130" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F130" s="42" t="str">
-        <x:v>-9.362128552229</x:v>
+        <x:v>-53.308720983607</x:v>
       </x:c>
       <x:c r="G130" s="42" t="str">
-        <x:v>9.362128552229</x:v>
+        <x:v>53.308720983607</x:v>
       </x:c>
       <x:c r="H130" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4819,19 +4860,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C131" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D131" s="42" t="str">
-        <x:v>-2.299617048110</x:v>
+        <x:v>-9.052128552229</x:v>
       </x:c>
       <x:c r="E131" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F131" s="42" t="str">
-        <x:v>-3.549617048110</x:v>
+        <x:v>-9.362128552229</x:v>
       </x:c>
       <x:c r="G131" s="42" t="str">
-        <x:v>3.549617048110</x:v>
+        <x:v>9.362128552229</x:v>
       </x:c>
       <x:c r="H131" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4845,19 +4886,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C132" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D132" s="42" t="str">
-        <x:v>2.904340310370</x:v>
+        <x:v>-2.299617048110</x:v>
       </x:c>
       <x:c r="E132" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F132" s="42" t="str">
-        <x:v>-0.925659689630</x:v>
+        <x:v>-3.549617048110</x:v>
       </x:c>
       <x:c r="G132" s="42" t="str">
-        <x:v>0.925659689630</x:v>
+        <x:v>3.549617048110</x:v>
       </x:c>
       <x:c r="H132" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4871,19 +4912,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C133" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D133" s="42" t="str">
-        <x:v>-12.321031303355</x:v>
+        <x:v>2.904340310370</x:v>
       </x:c>
       <x:c r="E133" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F133" s="42" t="str">
-        <x:v>-14.101031303355</x:v>
+        <x:v>-0.925659689630</x:v>
       </x:c>
       <x:c r="G133" s="42" t="str">
-        <x:v>14.101031303355</x:v>
+        <x:v>0.925659689630</x:v>
       </x:c>
       <x:c r="H133" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4897,19 +4938,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C134" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D134" s="42" t="str">
-        <x:v>-153.898129900577</x:v>
+        <x:v>-12.321031303355</x:v>
       </x:c>
       <x:c r="E134" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F134" s="42" t="str">
-        <x:v>-158.888129900577</x:v>
+        <x:v>-14.101031303355</x:v>
       </x:c>
       <x:c r="G134" s="42" t="str">
-        <x:v>158.888129900577</x:v>
+        <x:v>14.101031303355</x:v>
       </x:c>
       <x:c r="H134" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4923,19 +4964,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C135" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D135" s="42" t="str">
-        <x:v>-38.486266197120</x:v>
+        <x:v>-153.898129900577</x:v>
       </x:c>
       <x:c r="E135" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F135" s="42" t="str">
-        <x:v>-42.716266197120</x:v>
+        <x:v>-158.888129900577</x:v>
       </x:c>
       <x:c r="G135" s="42" t="str">
-        <x:v>42.716266197120</x:v>
+        <x:v>158.888129900577</x:v>
       </x:c>
       <x:c r="H135" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4949,19 +4990,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C136" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D136" s="42" t="str">
-        <x:v>-2.461004071112</x:v>
+        <x:v>-38.486266197120</x:v>
       </x:c>
       <x:c r="E136" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F136" s="42" t="str">
-        <x:v>-3.061004071112</x:v>
+        <x:v>-42.716266197120</x:v>
       </x:c>
       <x:c r="G136" s="42" t="str">
-        <x:v>3.061004071112</x:v>
+        <x:v>42.716266197120</x:v>
       </x:c>
       <x:c r="H136" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4975,19 +5016,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C137" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D137" s="42" t="str">
-        <x:v>-62.523175264048</x:v>
+        <x:v>-2.461004071112</x:v>
       </x:c>
       <x:c r="E137" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F137" s="42" t="str">
-        <x:v>-62.683175264048</x:v>
+        <x:v>-3.061004071112</x:v>
       </x:c>
       <x:c r="G137" s="42" t="str">
-        <x:v>62.683175264048</x:v>
+        <x:v>3.061004071112</x:v>
       </x:c>
       <x:c r="H137" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5001,19 +5042,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C138" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D138" s="42" t="str">
-        <x:v>0.926723486584</x:v>
+        <x:v>-62.523175264048</x:v>
       </x:c>
       <x:c r="E138" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F138" s="42" t="str">
-        <x:v>-1.193276513416</x:v>
+        <x:v>-62.683175264048</x:v>
       </x:c>
       <x:c r="G138" s="42" t="str">
-        <x:v>1.193276513416</x:v>
+        <x:v>62.683175264048</x:v>
       </x:c>
       <x:c r="H138" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5027,19 +5068,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C139" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D139" s="42" t="str">
-        <x:v>-83.899718986935</x:v>
+        <x:v>0.926723486584</x:v>
       </x:c>
       <x:c r="E139" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F139" s="42" t="str">
-        <x:v>-85.599718986935</x:v>
+        <x:v>-1.193276513416</x:v>
       </x:c>
       <x:c r="G139" s="42" t="str">
-        <x:v>85.599718986935</x:v>
+        <x:v>1.193276513416</x:v>
       </x:c>
       <x:c r="H139" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5053,19 +5094,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C140" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D140" s="42" t="str">
-        <x:v>-12.545503073689</x:v>
+        <x:v>-83.899718986935</x:v>
       </x:c>
       <x:c r="E140" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F140" s="42" t="str">
-        <x:v>-14.285503073689</x:v>
+        <x:v>-85.599718986935</x:v>
       </x:c>
       <x:c r="G140" s="42" t="str">
-        <x:v>14.285503073689</x:v>
+        <x:v>85.599718986935</x:v>
       </x:c>
       <x:c r="H140" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5079,19 +5120,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C141" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D141" s="42" t="str">
-        <x:v>-10.466391957817</x:v>
+        <x:v>-12.545503073689</x:v>
       </x:c>
       <x:c r="E141" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F141" s="42" t="str">
-        <x:v>-12.216391957817</x:v>
+        <x:v>-14.285503073689</x:v>
       </x:c>
       <x:c r="G141" s="42" t="str">
-        <x:v>12.216391957817</x:v>
+        <x:v>14.285503073689</x:v>
       </x:c>
       <x:c r="H141" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5102,22 +5143,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B142" s="36" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C142" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D142" s="42" t="str">
-        <x:v>-2.513150603252</x:v>
+        <x:v>-10.466391957817</x:v>
       </x:c>
       <x:c r="E142" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F142" s="42" t="str">
-        <x:v>-2.823150603252</x:v>
+        <x:v>-12.216391957817</x:v>
       </x:c>
       <x:c r="G142" s="42" t="str">
-        <x:v>2.823150603252</x:v>
+        <x:v>12.216391957817</x:v>
       </x:c>
       <x:c r="H142" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5131,19 +5172,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C143" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D143" s="42" t="str">
-        <x:v>1.264029937698</x:v>
+        <x:v>-2.513150603252</x:v>
       </x:c>
       <x:c r="E143" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F143" s="42" t="str">
-        <x:v>0.014029937698</x:v>
+        <x:v>-2.823150603252</x:v>
       </x:c>
       <x:c r="G143" s="42" t="str">
-        <x:v>0.014029937698</x:v>
+        <x:v>2.823150603252</x:v>
       </x:c>
       <x:c r="H143" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5157,19 +5198,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C144" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D144" s="42" t="str">
-        <x:v>1.405712159485</x:v>
+        <x:v>1.264029937698</x:v>
       </x:c>
       <x:c r="E144" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F144" s="42" t="str">
-        <x:v>-2.424287840515</x:v>
+        <x:v>0.014029937698</x:v>
       </x:c>
       <x:c r="G144" s="42" t="str">
-        <x:v>2.424287840515</x:v>
+        <x:v>0.014029937698</x:v>
       </x:c>
       <x:c r="H144" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5183,19 +5224,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C145" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D145" s="42" t="str">
-        <x:v>-1.048061577331</x:v>
+        <x:v>1.405712159485</x:v>
       </x:c>
       <x:c r="E145" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F145" s="42" t="str">
-        <x:v>-2.828061577331</x:v>
+        <x:v>-2.424287840515</x:v>
       </x:c>
       <x:c r="G145" s="42" t="str">
-        <x:v>2.828061577331</x:v>
+        <x:v>2.424287840515</x:v>
       </x:c>
       <x:c r="H145" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5209,19 +5250,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C146" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D146" s="42" t="str">
-        <x:v>-63.955235096392</x:v>
+        <x:v>-1.048061577331</x:v>
       </x:c>
       <x:c r="E146" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F146" s="42" t="str">
-        <x:v>-68.945235096392</x:v>
+        <x:v>-2.828061577331</x:v>
       </x:c>
       <x:c r="G146" s="42" t="str">
-        <x:v>68.945235096392</x:v>
+        <x:v>2.828061577331</x:v>
       </x:c>
       <x:c r="H146" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5235,19 +5276,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C147" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D147" s="42" t="str">
-        <x:v>-6.163484047291</x:v>
+        <x:v>-63.955235096392</x:v>
       </x:c>
       <x:c r="E147" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F147" s="42" t="str">
-        <x:v>-10.393484047291</x:v>
+        <x:v>-68.945235096392</x:v>
       </x:c>
       <x:c r="G147" s="42" t="str">
-        <x:v>10.393484047291</x:v>
+        <x:v>68.945235096392</x:v>
       </x:c>
       <x:c r="H147" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5261,19 +5302,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C148" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D148" s="42" t="str">
-        <x:v>-0.372876272237</x:v>
+        <x:v>-6.163484047291</x:v>
       </x:c>
       <x:c r="E148" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F148" s="42" t="str">
-        <x:v>-0.972876272237</x:v>
+        <x:v>-10.393484047291</x:v>
       </x:c>
       <x:c r="G148" s="42" t="str">
-        <x:v>0.972876272237</x:v>
+        <x:v>10.393484047291</x:v>
       </x:c>
       <x:c r="H148" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5287,19 +5328,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C149" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D149" s="42" t="str">
-        <x:v>-14.875013200229</x:v>
+        <x:v>-0.372876272237</x:v>
       </x:c>
       <x:c r="E149" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F149" s="42" t="str">
-        <x:v>-15.035013200229</x:v>
+        <x:v>-0.972876272237</x:v>
       </x:c>
       <x:c r="G149" s="42" t="str">
-        <x:v>15.035013200229</x:v>
+        <x:v>0.972876272237</x:v>
       </x:c>
       <x:c r="H149" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5313,19 +5354,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C150" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D150" s="42" t="str">
-        <x:v>0.123061371006</x:v>
+        <x:v>-14.875013200229</x:v>
       </x:c>
       <x:c r="E150" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F150" s="42" t="str">
-        <x:v>-1.996938628994</x:v>
+        <x:v>-15.035013200229</x:v>
       </x:c>
       <x:c r="G150" s="42" t="str">
-        <x:v>1.996938628994</x:v>
+        <x:v>15.035013200229</x:v>
       </x:c>
       <x:c r="H150" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5339,19 +5380,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C151" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D151" s="42" t="str">
-        <x:v>-23.938106879109</x:v>
+        <x:v>0.123061371006</x:v>
       </x:c>
       <x:c r="E151" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F151" s="42" t="str">
-        <x:v>-25.638106879109</x:v>
+        <x:v>-1.996938628994</x:v>
       </x:c>
       <x:c r="G151" s="42" t="str">
-        <x:v>25.638106879109</x:v>
+        <x:v>1.996938628994</x:v>
       </x:c>
       <x:c r="H151" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5365,19 +5406,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C152" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D152" s="42" t="str">
-        <x:v>-1.097393985422</x:v>
+        <x:v>-23.938106879109</x:v>
       </x:c>
       <x:c r="E152" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F152" s="42" t="str">
-        <x:v>-2.837393985422</x:v>
+        <x:v>-25.638106879109</x:v>
       </x:c>
       <x:c r="G152" s="42" t="str">
-        <x:v>2.837393985422</x:v>
+        <x:v>25.638106879109</x:v>
       </x:c>
       <x:c r="H152" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5391,19 +5432,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C153" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D153" s="42" t="str">
-        <x:v>-0.727230275074</x:v>
+        <x:v>-1.097393985422</x:v>
       </x:c>
       <x:c r="E153" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F153" s="42" t="str">
-        <x:v>-2.477230275074</x:v>
+        <x:v>-2.837393985422</x:v>
       </x:c>
       <x:c r="G153" s="42" t="str">
-        <x:v>2.477230275074</x:v>
+        <x:v>2.837393985422</x:v>
       </x:c>
       <x:c r="H153" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5411,25 +5452,25 @@
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
       <x:c r="A154" s="36" t="str">
-        <x:v>historical mstore-inorganic CLI</x:v>
+        <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B154" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C154" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D154" s="42" t="str">
-        <x:v>11.549596417487</x:v>
+        <x:v>-0.727230275074</x:v>
       </x:c>
       <x:c r="E154" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F154" s="42" t="str">
-        <x:v>11.239596417487</x:v>
+        <x:v>-2.477230275074</x:v>
       </x:c>
       <x:c r="G154" s="42" t="str">
-        <x:v>11.239596417487</x:v>
+        <x:v>2.477230275074</x:v>
       </x:c>
       <x:c r="H154" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5440,22 +5481,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B155" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C155" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D155" s="42" t="str">
-        <x:v>-29.811523391510</x:v>
+        <x:v>21.964390394634</x:v>
       </x:c>
       <x:c r="E155" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F155" s="42" t="str">
-        <x:v>-31.061523391510</x:v>
+        <x:v>21.654390394634</x:v>
       </x:c>
       <x:c r="G155" s="42" t="str">
-        <x:v>31.061523391510</x:v>
+        <x:v>21.654390394634</x:v>
       </x:c>
       <x:c r="H155" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5466,22 +5507,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B156" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C156" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D156" s="42" t="str">
-        <x:v>0.256599145141</x:v>
+        <x:v>-171.325848518761</x:v>
       </x:c>
       <x:c r="E156" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F156" s="42" t="str">
-        <x:v>-3.573400854859</x:v>
+        <x:v>-172.575848518761</x:v>
       </x:c>
       <x:c r="G156" s="42" t="str">
-        <x:v>3.573400854859</x:v>
+        <x:v>172.575848518761</x:v>
       </x:c>
       <x:c r="H156" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5492,22 +5533,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B157" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C157" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D157" s="42" t="str">
-        <x:v>-28.460677817350</x:v>
+        <x:v>-64.481456672543</x:v>
       </x:c>
       <x:c r="E157" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F157" s="42" t="str">
-        <x:v>-30.240677817350</x:v>
+        <x:v>-68.311456672543</x:v>
       </x:c>
       <x:c r="G157" s="42" t="str">
-        <x:v>30.240677817350</x:v>
+        <x:v>68.311456672543</x:v>
       </x:c>
       <x:c r="H157" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5518,22 +5559,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B158" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C158" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D158" s="42" t="str">
-        <x:v>-151.947965741842</x:v>
+        <x:v>-55.475838468692</x:v>
       </x:c>
       <x:c r="E158" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F158" s="42" t="str">
-        <x:v>-156.937965741842</x:v>
+        <x:v>-57.255838468692</x:v>
       </x:c>
       <x:c r="G158" s="42" t="str">
-        <x:v>156.937965741842</x:v>
+        <x:v>57.255838468692</x:v>
       </x:c>
       <x:c r="H158" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5544,22 +5585,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B159" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C159" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D159" s="42" t="str">
-        <x:v>-77.417542603032</x:v>
+        <x:v>-259.196245399110</x:v>
       </x:c>
       <x:c r="E159" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F159" s="42" t="str">
-        <x:v>-81.647542603032</x:v>
+        <x:v>-264.186245399110</x:v>
       </x:c>
       <x:c r="G159" s="42" t="str">
-        <x:v>81.647542603032</x:v>
+        <x:v>264.186245399110</x:v>
       </x:c>
       <x:c r="H159" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5570,22 +5611,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B160" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C160" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D160" s="42" t="str">
-        <x:v>-24.470250890265</x:v>
+        <x:v>-252.839445286494</x:v>
       </x:c>
       <x:c r="E160" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F160" s="42" t="str">
-        <x:v>-25.070250890265</x:v>
+        <x:v>-257.069445286494</x:v>
       </x:c>
       <x:c r="G160" s="42" t="str">
-        <x:v>25.070250890265</x:v>
+        <x:v>257.069445286494</x:v>
       </x:c>
       <x:c r="H160" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5596,22 +5637,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B161" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C161" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D161" s="42" t="str">
-        <x:v>-84.549975905731</x:v>
+        <x:v>-146.178117427308</x:v>
       </x:c>
       <x:c r="E161" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F161" s="42" t="str">
-        <x:v>-84.709975905731</x:v>
+        <x:v>-146.778117427308</x:v>
       </x:c>
       <x:c r="G161" s="42" t="str">
-        <x:v>84.709975905731</x:v>
+        <x:v>146.778117427308</x:v>
       </x:c>
       <x:c r="H161" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5622,22 +5663,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B162" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C162" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D162" s="42" t="str">
-        <x:v>0.922244833924</x:v>
+        <x:v>-224.393887966522</x:v>
       </x:c>
       <x:c r="E162" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F162" s="42" t="str">
-        <x:v>-1.197755166076</x:v>
+        <x:v>-224.553887966522</x:v>
       </x:c>
       <x:c r="G162" s="42" t="str">
-        <x:v>1.197755166076</x:v>
+        <x:v>224.553887966522</x:v>
       </x:c>
       <x:c r="H162" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5648,22 +5689,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B163" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C163" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D163" s="42" t="str">
-        <x:v>-99.557194036284</x:v>
+        <x:v>-64.059726187434</x:v>
       </x:c>
       <x:c r="E163" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F163" s="42" t="str">
-        <x:v>-101.257194036284</x:v>
+        <x:v>-66.179726187434</x:v>
       </x:c>
       <x:c r="G163" s="42" t="str">
-        <x:v>101.257194036284</x:v>
+        <x:v>66.179726187434</x:v>
       </x:c>
       <x:c r="H163" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5674,22 +5715,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B164" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C164" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D164" s="42" t="str">
-        <x:v>-28.664951204286</x:v>
+        <x:v>-178.832658863162</x:v>
       </x:c>
       <x:c r="E164" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F164" s="42" t="str">
-        <x:v>-30.404951204286</x:v>
+        <x:v>-180.532658863162</x:v>
       </x:c>
       <x:c r="G164" s="42" t="str">
-        <x:v>30.404951204286</x:v>
+        <x:v>180.532658863162</x:v>
       </x:c>
       <x:c r="H164" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5700,22 +5741,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B165" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C165" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D165" s="42" t="str">
-        <x:v>-25.438330429983</x:v>
+        <x:v>-55.925167433801</x:v>
       </x:c>
       <x:c r="E165" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F165" s="42" t="str">
-        <x:v>-27.188330429983</x:v>
+        <x:v>-57.665167433801</x:v>
       </x:c>
       <x:c r="G165" s="42" t="str">
-        <x:v>27.188330429983</x:v>
+        <x:v>57.665167433801</x:v>
       </x:c>
       <x:c r="H165" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5726,22 +5767,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B166" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C166" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D166" s="42" t="str">
-        <x:v>-0.279988209907</x:v>
+        <x:v>-52.285059233270</x:v>
       </x:c>
       <x:c r="E166" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F166" s="42" t="str">
-        <x:v>-0.589988209907</x:v>
+        <x:v>-54.035059233270</x:v>
       </x:c>
       <x:c r="G166" s="42" t="str">
-        <x:v>0.589988209907</x:v>
+        <x:v>54.035059233270</x:v>
       </x:c>
       <x:c r="H166" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5752,22 +5793,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B167" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C167" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D167" s="42" t="str">
-        <x:v>-1.720202220170</x:v>
+        <x:v>11.549596417487</x:v>
       </x:c>
       <x:c r="E167" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F167" s="42" t="str">
-        <x:v>-2.970202220170</x:v>
+        <x:v>11.239596417487</x:v>
       </x:c>
       <x:c r="G167" s="42" t="str">
-        <x:v>2.970202220170</x:v>
+        <x:v>11.239596417487</x:v>
       </x:c>
       <x:c r="H167" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5778,22 +5819,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B168" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C168" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D168" s="42" t="str">
-        <x:v>1.653583137544</x:v>
+        <x:v>-29.811523391510</x:v>
       </x:c>
       <x:c r="E168" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F168" s="42" t="str">
-        <x:v>-2.176416862456</x:v>
+        <x:v>-31.061523391510</x:v>
       </x:c>
       <x:c r="G168" s="42" t="str">
-        <x:v>2.176416862456</x:v>
+        <x:v>31.061523391510</x:v>
       </x:c>
       <x:c r="H168" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5804,22 +5845,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B169" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C169" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D169" s="42" t="str">
-        <x:v>-5.912105883998</x:v>
+        <x:v>0.256599145141</x:v>
       </x:c>
       <x:c r="E169" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F169" s="42" t="str">
-        <x:v>-7.692105883998</x:v>
+        <x:v>-3.573400854859</x:v>
       </x:c>
       <x:c r="G169" s="42" t="str">
-        <x:v>7.692105883998</x:v>
+        <x:v>3.573400854859</x:v>
       </x:c>
       <x:c r="H169" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5830,22 +5871,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B170" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C170" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D170" s="42" t="str">
-        <x:v>-77.446667006181</x:v>
+        <x:v>-28.460677817350</x:v>
       </x:c>
       <x:c r="E170" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F170" s="42" t="str">
-        <x:v>-82.436667006181</x:v>
+        <x:v>-30.240677817350</x:v>
       </x:c>
       <x:c r="G170" s="42" t="str">
-        <x:v>82.436667006181</x:v>
+        <x:v>30.240677817350</x:v>
       </x:c>
       <x:c r="H170" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5856,22 +5897,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B171" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C171" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D171" s="42" t="str">
-        <x:v>-19.706722185486</x:v>
+        <x:v>-151.947965741842</x:v>
       </x:c>
       <x:c r="E171" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F171" s="42" t="str">
-        <x:v>-23.936722185486</x:v>
+        <x:v>-156.937965741842</x:v>
       </x:c>
       <x:c r="G171" s="42" t="str">
-        <x:v>23.936722185486</x:v>
+        <x:v>156.937965741842</x:v>
       </x:c>
       <x:c r="H171" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5882,22 +5923,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B172" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C172" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D172" s="42" t="str">
-        <x:v>-2.774771626398</x:v>
+        <x:v>-77.417542603032</x:v>
       </x:c>
       <x:c r="E172" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F172" s="42" t="str">
-        <x:v>-3.374771626398</x:v>
+        <x:v>-81.647542603032</x:v>
       </x:c>
       <x:c r="G172" s="42" t="str">
-        <x:v>3.374771626398</x:v>
+        <x:v>81.647542603032</x:v>
       </x:c>
       <x:c r="H172" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5908,22 +5949,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B173" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C173" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D173" s="42" t="str">
-        <x:v>-31.168750655955</x:v>
+        <x:v>-24.470250890265</x:v>
       </x:c>
       <x:c r="E173" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F173" s="42" t="str">
-        <x:v>-31.328750655955</x:v>
+        <x:v>-25.070250890265</x:v>
       </x:c>
       <x:c r="G173" s="42" t="str">
-        <x:v>31.328750655955</x:v>
+        <x:v>25.070250890265</x:v>
       </x:c>
       <x:c r="H173" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5934,22 +5975,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B174" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C174" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D174" s="42" t="str">
-        <x:v>0.442953962487</x:v>
+        <x:v>-84.549975905731</x:v>
       </x:c>
       <x:c r="E174" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F174" s="42" t="str">
-        <x:v>-1.677046037513</x:v>
+        <x:v>-84.709975905731</x:v>
       </x:c>
       <x:c r="G174" s="42" t="str">
-        <x:v>1.677046037513</x:v>
+        <x:v>84.709975905731</x:v>
       </x:c>
       <x:c r="H174" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5960,22 +6001,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B175" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C175" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D175" s="42" t="str">
-        <x:v>-41.779791859131</x:v>
+        <x:v>0.922244833924</x:v>
       </x:c>
       <x:c r="E175" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F175" s="42" t="str">
-        <x:v>-43.479791859131</x:v>
+        <x:v>-1.197755166076</x:v>
       </x:c>
       <x:c r="G175" s="42" t="str">
-        <x:v>43.479791859131</x:v>
+        <x:v>1.197755166076</x:v>
       </x:c>
       <x:c r="H175" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5986,22 +6027,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B176" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C176" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D176" s="42" t="str">
-        <x:v>-5.934441749535</x:v>
+        <x:v>-99.557194036284</x:v>
       </x:c>
       <x:c r="E176" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F176" s="42" t="str">
-        <x:v>-7.674441749535</x:v>
+        <x:v>-101.257194036284</x:v>
       </x:c>
       <x:c r="G176" s="42" t="str">
-        <x:v>7.674441749535</x:v>
+        <x:v>101.257194036284</x:v>
       </x:c>
       <x:c r="H176" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6012,24 +6053,362 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B177" s="36" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C177" s="36" t="str">
+        <x:v>XV</x:v>
+      </x:c>
+      <x:c r="D177" s="42" t="str">
+        <x:v>-28.664951204286</x:v>
+      </x:c>
+      <x:c r="E177" s="42" t="str">
+        <x:v>1.740000</x:v>
+      </x:c>
+      <x:c r="F177" s="42" t="str">
+        <x:v>-30.404951204286</x:v>
+      </x:c>
+      <x:c r="G177" s="42" t="str">
+        <x:v>30.404951204286</x:v>
+      </x:c>
+      <x:c r="H177" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="15" hidden="0" customHeight="1">
+      <x:c r="A178" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B178" s="36" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C178" s="36" t="str">
+        <x:v>XVII</x:v>
+      </x:c>
+      <x:c r="D178" s="42" t="str">
+        <x:v>-25.438330429983</x:v>
+      </x:c>
+      <x:c r="E178" s="42" t="str">
+        <x:v>1.750000</x:v>
+      </x:c>
+      <x:c r="F178" s="42" t="str">
+        <x:v>-27.188330429983</x:v>
+      </x:c>
+      <x:c r="G178" s="42" t="str">
+        <x:v>27.188330429983</x:v>
+      </x:c>
+      <x:c r="H178" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="15" hidden="0" customHeight="1">
+      <x:c r="A179" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B179" s="36" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C177" s="36" t="str">
+      <x:c r="C179" s="36" t="str">
+        <x:v>II</x:v>
+      </x:c>
+      <x:c r="D179" s="42" t="str">
+        <x:v>-0.279988209907</x:v>
+      </x:c>
+      <x:c r="E179" s="42" t="str">
+        <x:v>0.310000</x:v>
+      </x:c>
+      <x:c r="F179" s="42" t="str">
+        <x:v>-0.589988209907</x:v>
+      </x:c>
+      <x:c r="G179" s="42" t="str">
+        <x:v>0.589988209907</x:v>
+      </x:c>
+      <x:c r="H179" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="15" hidden="0" customHeight="1">
+      <x:c r="A180" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B180" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C180" s="36" t="str">
+        <x:v>III</x:v>
+      </x:c>
+      <x:c r="D180" s="42" t="str">
+        <x:v>-1.720202220170</x:v>
+      </x:c>
+      <x:c r="E180" s="42" t="str">
+        <x:v>1.250000</x:v>
+      </x:c>
+      <x:c r="F180" s="42" t="str">
+        <x:v>-2.970202220170</x:v>
+      </x:c>
+      <x:c r="G180" s="42" t="str">
+        <x:v>2.970202220170</x:v>
+      </x:c>
+      <x:c r="H180" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="15" hidden="0" customHeight="1">
+      <x:c r="A181" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B181" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C181" s="36" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="D181" s="42" t="str">
+        <x:v>1.653583137544</x:v>
+      </x:c>
+      <x:c r="E181" s="42" t="str">
+        <x:v>3.830000</x:v>
+      </x:c>
+      <x:c r="F181" s="42" t="str">
+        <x:v>-2.176416862456</x:v>
+      </x:c>
+      <x:c r="G181" s="42" t="str">
+        <x:v>2.176416862456</x:v>
+      </x:c>
+      <x:c r="H181" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="15" hidden="0" customHeight="1">
+      <x:c r="A182" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B182" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C182" s="36" t="str">
+        <x:v>VI</x:v>
+      </x:c>
+      <x:c r="D182" s="42" t="str">
+        <x:v>-5.912105883998</x:v>
+      </x:c>
+      <x:c r="E182" s="42" t="str">
+        <x:v>1.780000</x:v>
+      </x:c>
+      <x:c r="F182" s="42" t="str">
+        <x:v>-7.692105883998</x:v>
+      </x:c>
+      <x:c r="G182" s="42" t="str">
+        <x:v>7.692105883998</x:v>
+      </x:c>
+      <x:c r="H182" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="15" hidden="0" customHeight="1">
+      <x:c r="A183" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B183" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C183" s="36" t="str">
+        <x:v>VII</x:v>
+      </x:c>
+      <x:c r="D183" s="42" t="str">
+        <x:v>-77.446667006181</x:v>
+      </x:c>
+      <x:c r="E183" s="42" t="str">
+        <x:v>4.990000</x:v>
+      </x:c>
+      <x:c r="F183" s="42" t="str">
+        <x:v>-82.436667006181</x:v>
+      </x:c>
+      <x:c r="G183" s="42" t="str">
+        <x:v>82.436667006181</x:v>
+      </x:c>
+      <x:c r="H183" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="15" hidden="0" customHeight="1">
+      <x:c r="A184" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B184" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C184" s="36" t="str">
+        <x:v>VIII</x:v>
+      </x:c>
+      <x:c r="D184" s="42" t="str">
+        <x:v>-19.706722185486</x:v>
+      </x:c>
+      <x:c r="E184" s="42" t="str">
+        <x:v>4.230000</x:v>
+      </x:c>
+      <x:c r="F184" s="42" t="str">
+        <x:v>-23.936722185486</x:v>
+      </x:c>
+      <x:c r="G184" s="42" t="str">
+        <x:v>23.936722185486</x:v>
+      </x:c>
+      <x:c r="H184" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" ht="15" hidden="0" customHeight="1">
+      <x:c r="A185" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B185" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C185" s="36" t="str">
+        <x:v>IX</x:v>
+      </x:c>
+      <x:c r="D185" s="42" t="str">
+        <x:v>-2.774771626398</x:v>
+      </x:c>
+      <x:c r="E185" s="42" t="str">
+        <x:v>0.600000</x:v>
+      </x:c>
+      <x:c r="F185" s="42" t="str">
+        <x:v>-3.374771626398</x:v>
+      </x:c>
+      <x:c r="G185" s="42" t="str">
+        <x:v>3.374771626398</x:v>
+      </x:c>
+      <x:c r="H185" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" ht="15" hidden="0" customHeight="1">
+      <x:c r="A186" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B186" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C186" s="36" t="str">
+        <x:v>XI</x:v>
+      </x:c>
+      <x:c r="D186" s="42" t="str">
+        <x:v>-31.168750655955</x:v>
+      </x:c>
+      <x:c r="E186" s="42" t="str">
+        <x:v>0.160000</x:v>
+      </x:c>
+      <x:c r="F186" s="42" t="str">
+        <x:v>-31.328750655955</x:v>
+      </x:c>
+      <x:c r="G186" s="42" t="str">
+        <x:v>31.328750655955</x:v>
+      </x:c>
+      <x:c r="H186" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="15" hidden="0" customHeight="1">
+      <x:c r="A187" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B187" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C187" s="36" t="str">
+        <x:v>XIII</x:v>
+      </x:c>
+      <x:c r="D187" s="42" t="str">
+        <x:v>0.442953962487</x:v>
+      </x:c>
+      <x:c r="E187" s="42" t="str">
+        <x:v>2.120000</x:v>
+      </x:c>
+      <x:c r="F187" s="42" t="str">
+        <x:v>-1.677046037513</x:v>
+      </x:c>
+      <x:c r="G187" s="42" t="str">
+        <x:v>1.677046037513</x:v>
+      </x:c>
+      <x:c r="H187" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" ht="15" hidden="0" customHeight="1">
+      <x:c r="A188" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B188" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C188" s="36" t="str">
+        <x:v>XIV</x:v>
+      </x:c>
+      <x:c r="D188" s="42" t="str">
+        <x:v>-41.779791859131</x:v>
+      </x:c>
+      <x:c r="E188" s="42" t="str">
+        <x:v>1.700000</x:v>
+      </x:c>
+      <x:c r="F188" s="42" t="str">
+        <x:v>-43.479791859131</x:v>
+      </x:c>
+      <x:c r="G188" s="42" t="str">
+        <x:v>43.479791859131</x:v>
+      </x:c>
+      <x:c r="H188" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" ht="15" hidden="0" customHeight="1">
+      <x:c r="A189" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B189" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C189" s="36" t="str">
+        <x:v>XV</x:v>
+      </x:c>
+      <x:c r="D189" s="42" t="str">
+        <x:v>-5.934441749535</x:v>
+      </x:c>
+      <x:c r="E189" s="42" t="str">
+        <x:v>1.740000</x:v>
+      </x:c>
+      <x:c r="F189" s="42" t="str">
+        <x:v>-7.674441749535</x:v>
+      </x:c>
+      <x:c r="G189" s="42" t="str">
+        <x:v>7.674441749535</x:v>
+      </x:c>
+      <x:c r="H189" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="15" hidden="0" customHeight="1">
+      <x:c r="A190" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B190" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C190" s="36" t="str">
         <x:v>XVII</x:v>
       </x:c>
-      <x:c r="D177" s="42" t="str">
+      <x:c r="D190" s="42" t="str">
         <x:v>-4.880577524129</x:v>
       </x:c>
-      <x:c r="E177" s="42" t="str">
+      <x:c r="E190" s="42" t="str">
         <x:v>1.750000</x:v>
       </x:c>
-      <x:c r="F177" s="42" t="str">
+      <x:c r="F190" s="42" t="str">
         <x:v>-6.630577524129</x:v>
       </x:c>
-      <x:c r="G177" s="42" t="str">
+      <x:c r="G190" s="42" t="str">
         <x:v>6.630577524129</x:v>
       </x:c>
-      <x:c r="H177" s="36" t="str">
+      <x:c r="H190" s="36" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
@@ -6092,7 +6471,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="36" t="str">
         <x:v>II</x:v>
@@ -6101,19 +6480,19 @@
         <x:v>0.310000</x:v>
       </x:c>
       <x:c r="D2" s="42" t="str">
-        <x:v>-40.052769548562</x:v>
+        <x:v>-85.402832480791</x:v>
       </x:c>
       <x:c r="E2" s="42" t="str">
-        <x:v>11.549596417487</x:v>
+        <x:v>21.964390394634</x:v>
       </x:c>
       <x:c r="F2" s="42" t="str">
-        <x:v>51.602365966049</x:v>
+        <x:v>107.367222875425</x:v>
       </x:c>
       <x:c r="G2" s="42" t="str">
-        <x:v>40.362769548562</x:v>
+        <x:v>85.712832480791</x:v>
       </x:c>
       <x:c r="H2" s="42" t="str">
-        <x:v>11.239596417487</x:v>
+        <x:v>21.654390394634</x:v>
       </x:c>
       <x:c r="I2" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6127,7 +6506,7 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="36" t="str">
         <x:v>III</x:v>
@@ -6136,19 +6515,19 @@
         <x:v>1.250000</x:v>
       </x:c>
       <x:c r="D3" s="42" t="str">
-        <x:v>-21.669458368756</x:v>
+        <x:v>-52.784771448006</x:v>
       </x:c>
       <x:c r="E3" s="42" t="str">
-        <x:v>-29.811523391510</x:v>
+        <x:v>-171.325848518761</x:v>
       </x:c>
       <x:c r="F3" s="42" t="str">
-        <x:v>-8.142065022754</x:v>
+        <x:v>-118.541077070755</x:v>
       </x:c>
       <x:c r="G3" s="42" t="str">
-        <x:v>22.919458368756</x:v>
+        <x:v>54.034771448006</x:v>
       </x:c>
       <x:c r="H3" s="42" t="str">
-        <x:v>31.061523391510</x:v>
+        <x:v>172.575848518761</x:v>
       </x:c>
       <x:c r="I3" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6162,7 +6541,7 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="36" t="str">
         <x:v>IV</x:v>
@@ -6171,19 +6550,19 @@
         <x:v>3.830000</x:v>
       </x:c>
       <x:c r="D4" s="42" t="str">
-        <x:v>14.926647908813</x:v>
+        <x:v>38.666296487481</x:v>
       </x:c>
       <x:c r="E4" s="42" t="str">
-        <x:v>0.256599145141</x:v>
+        <x:v>-64.481456672543</x:v>
       </x:c>
       <x:c r="F4" s="42" t="str">
-        <x:v>-14.670048763672</x:v>
+        <x:v>-103.147753160024</x:v>
       </x:c>
       <x:c r="G4" s="42" t="str">
-        <x:v>11.096647908813</x:v>
+        <x:v>34.836296487481</x:v>
       </x:c>
       <x:c r="H4" s="42" t="str">
-        <x:v>3.573400854859</x:v>
+        <x:v>68.311456672543</x:v>
       </x:c>
       <x:c r="I4" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6197,7 +6576,7 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="36" t="str">
         <x:v>VI</x:v>
@@ -6206,19 +6585,19 @@
         <x:v>1.780000</x:v>
       </x:c>
       <x:c r="D5" s="42" t="str">
-        <x:v>-57.367276074495</x:v>
+        <x:v>-119.951876462899</x:v>
       </x:c>
       <x:c r="E5" s="42" t="str">
-        <x:v>-28.460677817350</x:v>
+        <x:v>-55.475838468692</x:v>
       </x:c>
       <x:c r="F5" s="42" t="str">
-        <x:v>28.906598257145</x:v>
+        <x:v>64.476037994207</x:v>
       </x:c>
       <x:c r="G5" s="42" t="str">
-        <x:v>59.147276074495</x:v>
+        <x:v>121.731876462899</x:v>
       </x:c>
       <x:c r="H5" s="42" t="str">
-        <x:v>30.240677817350</x:v>
+        <x:v>57.255838468692</x:v>
       </x:c>
       <x:c r="I5" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6232,7 +6611,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="36" t="str">
         <x:v>VII</x:v>
@@ -6241,19 +6620,19 @@
         <x:v>4.990000</x:v>
       </x:c>
       <x:c r="D6" s="42" t="str">
-        <x:v>-299.975204903283</x:v>
+        <x:v>-491.873083815613</x:v>
       </x:c>
       <x:c r="E6" s="42" t="str">
-        <x:v>-151.947965741842</x:v>
+        <x:v>-259.196245399110</x:v>
       </x:c>
       <x:c r="F6" s="42" t="str">
-        <x:v>148.027239161441</x:v>
+        <x:v>232.676838416503</x:v>
       </x:c>
       <x:c r="G6" s="42" t="str">
-        <x:v>304.965204903283</x:v>
+        <x:v>496.863083815613</x:v>
       </x:c>
       <x:c r="H6" s="42" t="str">
-        <x:v>156.937965741842</x:v>
+        <x:v>264.186245399110</x:v>
       </x:c>
       <x:c r="I6" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6267,7 +6646,7 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="36" t="str">
         <x:v>VIII</x:v>
@@ -6276,19 +6655,19 @@
         <x:v>4.230000</x:v>
       </x:c>
       <x:c r="D7" s="42" t="str">
-        <x:v>-121.493623038083</x:v>
+        <x:v>-227.181421040355</x:v>
       </x:c>
       <x:c r="E7" s="42" t="str">
-        <x:v>-77.417542603032</x:v>
+        <x:v>-252.839445286494</x:v>
       </x:c>
       <x:c r="F7" s="42" t="str">
-        <x:v>44.076080435051</x:v>
+        <x:v>-25.658024246139</x:v>
       </x:c>
       <x:c r="G7" s="42" t="str">
-        <x:v>125.723623038083</x:v>
+        <x:v>231.411421040355</x:v>
       </x:c>
       <x:c r="H7" s="42" t="str">
-        <x:v>81.647542603032</x:v>
+        <x:v>257.069445286494</x:v>
       </x:c>
       <x:c r="I7" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6302,7 +6681,7 @@
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
         <x:v>IX</x:v>
@@ -6311,19 +6690,19 @@
         <x:v>0.600000</x:v>
       </x:c>
       <x:c r="D8" s="42" t="str">
-        <x:v>-14.811033266160</x:v>
+        <x:v>-36.269951925783</x:v>
       </x:c>
       <x:c r="E8" s="42" t="str">
-        <x:v>-24.470250890265</x:v>
+        <x:v>-146.178117427308</x:v>
       </x:c>
       <x:c r="F8" s="42" t="str">
-        <x:v>-9.659217624105</x:v>
+        <x:v>-109.908165501525</x:v>
       </x:c>
       <x:c r="G8" s="42" t="str">
-        <x:v>15.411033266160</x:v>
+        <x:v>36.869951925783</x:v>
       </x:c>
       <x:c r="H8" s="42" t="str">
-        <x:v>25.070250890265</x:v>
+        <x:v>146.778117427308</x:v>
       </x:c>
       <x:c r="I8" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6337,7 +6716,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="36" t="str">
         <x:v>XI</x:v>
@@ -6346,19 +6725,19 @@
         <x:v>0.160000</x:v>
       </x:c>
       <x:c r="D9" s="42" t="str">
-        <x:v>-165.236809268426</x:v>
+        <x:v>-299.258518836626</x:v>
       </x:c>
       <x:c r="E9" s="42" t="str">
-        <x:v>-84.549975905731</x:v>
+        <x:v>-224.393887966522</x:v>
       </x:c>
       <x:c r="F9" s="42" t="str">
-        <x:v>80.686833362695</x:v>
+        <x:v>74.864630870104</x:v>
       </x:c>
       <x:c r="G9" s="42" t="str">
-        <x:v>165.396809268426</x:v>
+        <x:v>299.418518836626</x:v>
       </x:c>
       <x:c r="H9" s="42" t="str">
-        <x:v>84.709975905731</x:v>
+        <x:v>224.553887966522</x:v>
       </x:c>
       <x:c r="I9" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6372,7 +6751,7 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B10" s="36" t="str">
         <x:v>XIII</x:v>
@@ -6381,19 +6760,19 @@
         <x:v>2.120000</x:v>
       </x:c>
       <x:c r="D10" s="42" t="str">
-        <x:v>6.872357662713</x:v>
+        <x:v>16.464730608559</x:v>
       </x:c>
       <x:c r="E10" s="42" t="str">
-        <x:v>0.922244833924</x:v>
+        <x:v>-64.059726187434</x:v>
       </x:c>
       <x:c r="F10" s="42" t="str">
-        <x:v>-5.950112828789</x:v>
+        <x:v>-80.524456795993</x:v>
       </x:c>
       <x:c r="G10" s="42" t="str">
-        <x:v>4.752357662713</x:v>
+        <x:v>14.344730608559</x:v>
       </x:c>
       <x:c r="H10" s="42" t="str">
-        <x:v>1.197755166076</x:v>
+        <x:v>66.179726187434</x:v>
       </x:c>
       <x:c r="I10" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6407,7 +6786,7 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B11" s="36" t="str">
         <x:v>XIV</x:v>
@@ -6416,19 +6795,19 @@
         <x:v>1.700000</x:v>
       </x:c>
       <x:c r="D11" s="42" t="str">
-        <x:v>-199.607041791688</x:v>
+        <x:v>-351.956576532881</x:v>
       </x:c>
       <x:c r="E11" s="42" t="str">
-        <x:v>-99.557194036284</x:v>
+        <x:v>-178.832658863162</x:v>
       </x:c>
       <x:c r="F11" s="42" t="str">
-        <x:v>100.049847755404</x:v>
+        <x:v>173.123917669719</x:v>
       </x:c>
       <x:c r="G11" s="42" t="str">
-        <x:v>201.307041791688</x:v>
+        <x:v>353.656576532881</x:v>
       </x:c>
       <x:c r="H11" s="42" t="str">
-        <x:v>101.257194036284</x:v>
+        <x:v>180.532658863162</x:v>
       </x:c>
       <x:c r="I11" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6442,7 +6821,7 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B12" s="36" t="str">
         <x:v>XV</x:v>
@@ -6451,19 +6830,19 @@
         <x:v>1.740000</x:v>
       </x:c>
       <x:c r="D12" s="42" t="str">
-        <x:v>-58.045564075785</x:v>
+        <x:v>-121.156628176656</x:v>
       </x:c>
       <x:c r="E12" s="42" t="str">
-        <x:v>-28.664951204286</x:v>
+        <x:v>-55.925167433801</x:v>
       </x:c>
       <x:c r="F12" s="42" t="str">
-        <x:v>29.380612871499</x:v>
+        <x:v>65.231460742855</x:v>
       </x:c>
       <x:c r="G12" s="42" t="str">
-        <x:v>59.785564075785</x:v>
+        <x:v>122.896628176656</x:v>
       </x:c>
       <x:c r="H12" s="42" t="str">
-        <x:v>30.404951204286</x:v>
+        <x:v>57.665167433801</x:v>
       </x:c>
       <x:c r="I12" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6477,7 +6856,7 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B13" s="36" t="str">
         <x:v>XVII</x:v>
@@ -6486,19 +6865,19 @@
         <x:v>1.750000</x:v>
       </x:c>
       <x:c r="D13" s="42" t="str">
-        <x:v>-51.558720983607</x:v>
+        <x:v>-112.486904450047</x:v>
       </x:c>
       <x:c r="E13" s="42" t="str">
-        <x:v>-25.438330429983</x:v>
+        <x:v>-52.285059233270</x:v>
       </x:c>
       <x:c r="F13" s="42" t="str">
-        <x:v>26.120390553624</x:v>
+        <x:v>60.201845216777</x:v>
       </x:c>
       <x:c r="G13" s="42" t="str">
-        <x:v>53.308720983607</x:v>
+        <x:v>114.236904450047</x:v>
       </x:c>
       <x:c r="H13" s="42" t="str">
-        <x:v>27.188330429983</x:v>
+        <x:v>54.035059233270</x:v>
       </x:c>
       <x:c r="I13" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6512,7 +6891,7 @@
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B14" s="36" t="str">
         <x:v>II</x:v>
@@ -6521,19 +6900,19 @@
         <x:v>0.310000</x:v>
       </x:c>
       <x:c r="D14" s="42" t="str">
-        <x:v>-9.052128552229</x:v>
+        <x:v>-40.052769548562</x:v>
       </x:c>
       <x:c r="E14" s="42" t="str">
-        <x:v>-0.279988209907</x:v>
+        <x:v>11.549596417487</x:v>
       </x:c>
       <x:c r="F14" s="42" t="str">
-        <x:v>8.772140342322</x:v>
+        <x:v>51.602365966049</x:v>
       </x:c>
       <x:c r="G14" s="42" t="str">
-        <x:v>9.362128552229</x:v>
+        <x:v>40.362769548562</x:v>
       </x:c>
       <x:c r="H14" s="42" t="str">
-        <x:v>0.589988209907</x:v>
+        <x:v>11.239596417487</x:v>
       </x:c>
       <x:c r="I14" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6547,7 +6926,7 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="36" t="str">
         <x:v>III</x:v>
@@ -6556,19 +6935,19 @@
         <x:v>1.250000</x:v>
       </x:c>
       <x:c r="D15" s="42" t="str">
-        <x:v>-2.299617048110</x:v>
+        <x:v>-21.669458368756</x:v>
       </x:c>
       <x:c r="E15" s="42" t="str">
-        <x:v>-1.720202220170</x:v>
+        <x:v>-29.811523391510</x:v>
       </x:c>
       <x:c r="F15" s="42" t="str">
-        <x:v>0.579414827940</x:v>
+        <x:v>-8.142065022754</x:v>
       </x:c>
       <x:c r="G15" s="42" t="str">
-        <x:v>3.549617048110</x:v>
+        <x:v>22.919458368756</x:v>
       </x:c>
       <x:c r="H15" s="42" t="str">
-        <x:v>2.970202220170</x:v>
+        <x:v>31.061523391510</x:v>
       </x:c>
       <x:c r="I15" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6582,7 +6961,7 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B16" s="36" t="str">
         <x:v>IV</x:v>
@@ -6591,19 +6970,19 @@
         <x:v>3.830000</x:v>
       </x:c>
       <x:c r="D16" s="42" t="str">
-        <x:v>2.904340310370</x:v>
+        <x:v>14.926647908813</x:v>
       </x:c>
       <x:c r="E16" s="42" t="str">
-        <x:v>1.653583137544</x:v>
+        <x:v>0.256599145141</x:v>
       </x:c>
       <x:c r="F16" s="42" t="str">
-        <x:v>-1.250757172826</x:v>
+        <x:v>-14.670048763672</x:v>
       </x:c>
       <x:c r="G16" s="42" t="str">
-        <x:v>0.925659689630</x:v>
+        <x:v>11.096647908813</x:v>
       </x:c>
       <x:c r="H16" s="42" t="str">
-        <x:v>2.176416862456</x:v>
+        <x:v>3.573400854859</x:v>
       </x:c>
       <x:c r="I16" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6617,7 +6996,7 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B17" s="36" t="str">
         <x:v>VI</x:v>
@@ -6626,19 +7005,19 @@
         <x:v>1.780000</x:v>
       </x:c>
       <x:c r="D17" s="42" t="str">
-        <x:v>-12.321031303355</x:v>
+        <x:v>-57.367276074495</x:v>
       </x:c>
       <x:c r="E17" s="42" t="str">
-        <x:v>-5.912105883998</x:v>
+        <x:v>-28.460677817350</x:v>
       </x:c>
       <x:c r="F17" s="42" t="str">
-        <x:v>6.408925419357</x:v>
+        <x:v>28.906598257145</x:v>
       </x:c>
       <x:c r="G17" s="42" t="str">
-        <x:v>14.101031303355</x:v>
+        <x:v>59.147276074495</x:v>
       </x:c>
       <x:c r="H17" s="42" t="str">
-        <x:v>7.692105883998</x:v>
+        <x:v>30.240677817350</x:v>
       </x:c>
       <x:c r="I17" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6652,7 +7031,7 @@
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B18" s="36" t="str">
         <x:v>VII</x:v>
@@ -6661,19 +7040,19 @@
         <x:v>4.990000</x:v>
       </x:c>
       <x:c r="D18" s="42" t="str">
-        <x:v>-153.898129900577</x:v>
+        <x:v>-299.975204903283</x:v>
       </x:c>
       <x:c r="E18" s="42" t="str">
-        <x:v>-77.446667006181</x:v>
+        <x:v>-151.947965741842</x:v>
       </x:c>
       <x:c r="F18" s="42" t="str">
-        <x:v>76.451462894396</x:v>
+        <x:v>148.027239161441</x:v>
       </x:c>
       <x:c r="G18" s="42" t="str">
-        <x:v>158.888129900577</x:v>
+        <x:v>304.965204903283</x:v>
       </x:c>
       <x:c r="H18" s="42" t="str">
-        <x:v>82.436667006181</x:v>
+        <x:v>156.937965741842</x:v>
       </x:c>
       <x:c r="I18" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6687,7 +7066,7 @@
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="36" t="str">
         <x:v>VIII</x:v>
@@ -6696,19 +7075,19 @@
         <x:v>4.230000</x:v>
       </x:c>
       <x:c r="D19" s="42" t="str">
-        <x:v>-38.486266197120</x:v>
+        <x:v>-121.493623038083</x:v>
       </x:c>
       <x:c r="E19" s="42" t="str">
-        <x:v>-19.706722185486</x:v>
+        <x:v>-77.417542603032</x:v>
       </x:c>
       <x:c r="F19" s="42" t="str">
-        <x:v>18.779544011634</x:v>
+        <x:v>44.076080435051</x:v>
       </x:c>
       <x:c r="G19" s="42" t="str">
-        <x:v>42.716266197120</x:v>
+        <x:v>125.723623038083</x:v>
       </x:c>
       <x:c r="H19" s="42" t="str">
-        <x:v>23.936722185486</x:v>
+        <x:v>81.647542603032</x:v>
       </x:c>
       <x:c r="I19" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6722,7 +7101,7 @@
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B20" s="36" t="str">
         <x:v>IX</x:v>
@@ -6731,19 +7110,19 @@
         <x:v>0.600000</x:v>
       </x:c>
       <x:c r="D20" s="42" t="str">
-        <x:v>-2.461004071112</x:v>
+        <x:v>-14.811033266160</x:v>
       </x:c>
       <x:c r="E20" s="42" t="str">
-        <x:v>-2.774771626398</x:v>
+        <x:v>-24.470250890265</x:v>
       </x:c>
       <x:c r="F20" s="42" t="str">
-        <x:v>-0.313767555286</x:v>
+        <x:v>-9.659217624105</x:v>
       </x:c>
       <x:c r="G20" s="42" t="str">
-        <x:v>3.061004071112</x:v>
+        <x:v>15.411033266160</x:v>
       </x:c>
       <x:c r="H20" s="42" t="str">
-        <x:v>3.374771626398</x:v>
+        <x:v>25.070250890265</x:v>
       </x:c>
       <x:c r="I20" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6757,7 +7136,7 @@
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B21" s="36" t="str">
         <x:v>XI</x:v>
@@ -6766,19 +7145,19 @@
         <x:v>0.160000</x:v>
       </x:c>
       <x:c r="D21" s="42" t="str">
-        <x:v>-62.523175264048</x:v>
+        <x:v>-165.236809268426</x:v>
       </x:c>
       <x:c r="E21" s="42" t="str">
-        <x:v>-31.168750655955</x:v>
+        <x:v>-84.549975905731</x:v>
       </x:c>
       <x:c r="F21" s="42" t="str">
-        <x:v>31.354424608093</x:v>
+        <x:v>80.686833362695</x:v>
       </x:c>
       <x:c r="G21" s="42" t="str">
-        <x:v>62.683175264048</x:v>
+        <x:v>165.396809268426</x:v>
       </x:c>
       <x:c r="H21" s="42" t="str">
-        <x:v>31.328750655955</x:v>
+        <x:v>84.709975905731</x:v>
       </x:c>
       <x:c r="I21" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6792,7 +7171,7 @@
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B22" s="36" t="str">
         <x:v>XIII</x:v>
@@ -6801,19 +7180,19 @@
         <x:v>2.120000</x:v>
       </x:c>
       <x:c r="D22" s="42" t="str">
-        <x:v>0.926723486584</x:v>
+        <x:v>6.872357662713</x:v>
       </x:c>
       <x:c r="E22" s="42" t="str">
-        <x:v>0.442953962487</x:v>
+        <x:v>0.922244833924</x:v>
       </x:c>
       <x:c r="F22" s="42" t="str">
-        <x:v>-0.483769524097</x:v>
+        <x:v>-5.950112828789</x:v>
       </x:c>
       <x:c r="G22" s="42" t="str">
-        <x:v>1.193276513416</x:v>
+        <x:v>4.752357662713</x:v>
       </x:c>
       <x:c r="H22" s="42" t="str">
-        <x:v>1.677046037513</x:v>
+        <x:v>1.197755166076</x:v>
       </x:c>
       <x:c r="I22" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6827,7 +7206,7 @@
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B23" s="36" t="str">
         <x:v>XIV</x:v>
@@ -6836,19 +7215,19 @@
         <x:v>1.700000</x:v>
       </x:c>
       <x:c r="D23" s="42" t="str">
-        <x:v>-83.899718986935</x:v>
+        <x:v>-199.607041791688</x:v>
       </x:c>
       <x:c r="E23" s="42" t="str">
-        <x:v>-41.779791859131</x:v>
+        <x:v>-99.557194036284</x:v>
       </x:c>
       <x:c r="F23" s="42" t="str">
-        <x:v>42.119927127804</x:v>
+        <x:v>100.049847755404</x:v>
       </x:c>
       <x:c r="G23" s="42" t="str">
-        <x:v>85.599718986935</x:v>
+        <x:v>201.307041791688</x:v>
       </x:c>
       <x:c r="H23" s="42" t="str">
-        <x:v>43.479791859131</x:v>
+        <x:v>101.257194036284</x:v>
       </x:c>
       <x:c r="I23" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6862,7 +7241,7 @@
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B24" s="36" t="str">
         <x:v>XV</x:v>
@@ -6871,19 +7250,19 @@
         <x:v>1.740000</x:v>
       </x:c>
       <x:c r="D24" s="42" t="str">
-        <x:v>-12.545503073689</x:v>
+        <x:v>-58.045564075785</x:v>
       </x:c>
       <x:c r="E24" s="42" t="str">
-        <x:v>-5.934441749535</x:v>
+        <x:v>-28.664951204286</x:v>
       </x:c>
       <x:c r="F24" s="42" t="str">
-        <x:v>6.611061324154</x:v>
+        <x:v>29.380612871499</x:v>
       </x:c>
       <x:c r="G24" s="42" t="str">
-        <x:v>14.285503073689</x:v>
+        <x:v>59.785564075785</x:v>
       </x:c>
       <x:c r="H24" s="42" t="str">
-        <x:v>7.674441749535</x:v>
+        <x:v>30.404951204286</x:v>
       </x:c>
       <x:c r="I24" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6897,7 +7276,7 @@
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B25" s="36" t="str">
         <x:v>XVII</x:v>
@@ -6906,19 +7285,19 @@
         <x:v>1.750000</x:v>
       </x:c>
       <x:c r="D25" s="42" t="str">
-        <x:v>-10.466391957817</x:v>
+        <x:v>-51.558720983607</x:v>
       </x:c>
       <x:c r="E25" s="42" t="str">
-        <x:v>-4.880577524129</x:v>
+        <x:v>-25.438330429983</x:v>
       </x:c>
       <x:c r="F25" s="42" t="str">
-        <x:v>5.585814433688</x:v>
+        <x:v>26.120390553624</x:v>
       </x:c>
       <x:c r="G25" s="42" t="str">
-        <x:v>12.216391957817</x:v>
+        <x:v>53.308720983607</x:v>
       </x:c>
       <x:c r="H25" s="42" t="str">
-        <x:v>6.630577524129</x:v>
+        <x:v>27.188330429983</x:v>
       </x:c>
       <x:c r="I25" s="36" t="str">
         <x:v>0.1</x:v>
@@ -6930,8 +7309,428 @@
         <x:v>true</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B26" s="36" t="str">
+        <x:v>II</x:v>
+      </x:c>
+      <x:c r="C26" s="36" t="str">
+        <x:v>0.310000</x:v>
+      </x:c>
+      <x:c r="D26" s="42" t="str">
+        <x:v>-9.052128552229</x:v>
+      </x:c>
+      <x:c r="E26" s="42" t="str">
+        <x:v>-0.279988209907</x:v>
+      </x:c>
+      <x:c r="F26" s="42" t="str">
+        <x:v>8.772140342322</x:v>
+      </x:c>
+      <x:c r="G26" s="42" t="str">
+        <x:v>9.362128552229</x:v>
+      </x:c>
+      <x:c r="H26" s="42" t="str">
+        <x:v>0.589988209907</x:v>
+      </x:c>
+      <x:c r="I26" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J26" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K26" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B27" s="36" t="str">
+        <x:v>III</x:v>
+      </x:c>
+      <x:c r="C27" s="36" t="str">
+        <x:v>1.250000</x:v>
+      </x:c>
+      <x:c r="D27" s="42" t="str">
+        <x:v>-2.299617048110</x:v>
+      </x:c>
+      <x:c r="E27" s="42" t="str">
+        <x:v>-1.720202220170</x:v>
+      </x:c>
+      <x:c r="F27" s="42" t="str">
+        <x:v>0.579414827940</x:v>
+      </x:c>
+      <x:c r="G27" s="42" t="str">
+        <x:v>3.549617048110</x:v>
+      </x:c>
+      <x:c r="H27" s="42" t="str">
+        <x:v>2.970202220170</x:v>
+      </x:c>
+      <x:c r="I27" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J27" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K27" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B28" s="36" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="C28" s="36" t="str">
+        <x:v>3.830000</x:v>
+      </x:c>
+      <x:c r="D28" s="42" t="str">
+        <x:v>2.904340310370</x:v>
+      </x:c>
+      <x:c r="E28" s="42" t="str">
+        <x:v>1.653583137544</x:v>
+      </x:c>
+      <x:c r="F28" s="42" t="str">
+        <x:v>-1.250757172826</x:v>
+      </x:c>
+      <x:c r="G28" s="42" t="str">
+        <x:v>0.925659689630</x:v>
+      </x:c>
+      <x:c r="H28" s="42" t="str">
+        <x:v>2.176416862456</x:v>
+      </x:c>
+      <x:c r="I28" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J28" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K28" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B29" s="36" t="str">
+        <x:v>VI</x:v>
+      </x:c>
+      <x:c r="C29" s="36" t="str">
+        <x:v>1.780000</x:v>
+      </x:c>
+      <x:c r="D29" s="42" t="str">
+        <x:v>-12.321031303355</x:v>
+      </x:c>
+      <x:c r="E29" s="42" t="str">
+        <x:v>-5.912105883998</x:v>
+      </x:c>
+      <x:c r="F29" s="42" t="str">
+        <x:v>6.408925419357</x:v>
+      </x:c>
+      <x:c r="G29" s="42" t="str">
+        <x:v>14.101031303355</x:v>
+      </x:c>
+      <x:c r="H29" s="42" t="str">
+        <x:v>7.692105883998</x:v>
+      </x:c>
+      <x:c r="I29" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J29" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K29" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B30" s="36" t="str">
+        <x:v>VII</x:v>
+      </x:c>
+      <x:c r="C30" s="36" t="str">
+        <x:v>4.990000</x:v>
+      </x:c>
+      <x:c r="D30" s="42" t="str">
+        <x:v>-153.898129900577</x:v>
+      </x:c>
+      <x:c r="E30" s="42" t="str">
+        <x:v>-77.446667006181</x:v>
+      </x:c>
+      <x:c r="F30" s="42" t="str">
+        <x:v>76.451462894396</x:v>
+      </x:c>
+      <x:c r="G30" s="42" t="str">
+        <x:v>158.888129900577</x:v>
+      </x:c>
+      <x:c r="H30" s="42" t="str">
+        <x:v>82.436667006181</x:v>
+      </x:c>
+      <x:c r="I30" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J30" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K30" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B31" s="36" t="str">
+        <x:v>VIII</x:v>
+      </x:c>
+      <x:c r="C31" s="36" t="str">
+        <x:v>4.230000</x:v>
+      </x:c>
+      <x:c r="D31" s="42" t="str">
+        <x:v>-38.486266197120</x:v>
+      </x:c>
+      <x:c r="E31" s="42" t="str">
+        <x:v>-19.706722185486</x:v>
+      </x:c>
+      <x:c r="F31" s="42" t="str">
+        <x:v>18.779544011634</x:v>
+      </x:c>
+      <x:c r="G31" s="42" t="str">
+        <x:v>42.716266197120</x:v>
+      </x:c>
+      <x:c r="H31" s="42" t="str">
+        <x:v>23.936722185486</x:v>
+      </x:c>
+      <x:c r="I31" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J31" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K31" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B32" s="36" t="str">
+        <x:v>IX</x:v>
+      </x:c>
+      <x:c r="C32" s="36" t="str">
+        <x:v>0.600000</x:v>
+      </x:c>
+      <x:c r="D32" s="42" t="str">
+        <x:v>-2.461004071112</x:v>
+      </x:c>
+      <x:c r="E32" s="42" t="str">
+        <x:v>-2.774771626398</x:v>
+      </x:c>
+      <x:c r="F32" s="42" t="str">
+        <x:v>-0.313767555286</x:v>
+      </x:c>
+      <x:c r="G32" s="42" t="str">
+        <x:v>3.061004071112</x:v>
+      </x:c>
+      <x:c r="H32" s="42" t="str">
+        <x:v>3.374771626398</x:v>
+      </x:c>
+      <x:c r="I32" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J32" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K32" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B33" s="36" t="str">
+        <x:v>XI</x:v>
+      </x:c>
+      <x:c r="C33" s="36" t="str">
+        <x:v>0.160000</x:v>
+      </x:c>
+      <x:c r="D33" s="42" t="str">
+        <x:v>-62.523175264048</x:v>
+      </x:c>
+      <x:c r="E33" s="42" t="str">
+        <x:v>-31.168750655955</x:v>
+      </x:c>
+      <x:c r="F33" s="42" t="str">
+        <x:v>31.354424608093</x:v>
+      </x:c>
+      <x:c r="G33" s="42" t="str">
+        <x:v>62.683175264048</x:v>
+      </x:c>
+      <x:c r="H33" s="42" t="str">
+        <x:v>31.328750655955</x:v>
+      </x:c>
+      <x:c r="I33" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J33" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K33" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B34" s="36" t="str">
+        <x:v>XIII</x:v>
+      </x:c>
+      <x:c r="C34" s="36" t="str">
+        <x:v>2.120000</x:v>
+      </x:c>
+      <x:c r="D34" s="42" t="str">
+        <x:v>0.926723486584</x:v>
+      </x:c>
+      <x:c r="E34" s="42" t="str">
+        <x:v>0.442953962487</x:v>
+      </x:c>
+      <x:c r="F34" s="42" t="str">
+        <x:v>-0.483769524097</x:v>
+      </x:c>
+      <x:c r="G34" s="42" t="str">
+        <x:v>1.193276513416</x:v>
+      </x:c>
+      <x:c r="H34" s="42" t="str">
+        <x:v>1.677046037513</x:v>
+      </x:c>
+      <x:c r="I34" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J34" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K34" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B35" s="36" t="str">
+        <x:v>XIV</x:v>
+      </x:c>
+      <x:c r="C35" s="36" t="str">
+        <x:v>1.700000</x:v>
+      </x:c>
+      <x:c r="D35" s="42" t="str">
+        <x:v>-83.899718986935</x:v>
+      </x:c>
+      <x:c r="E35" s="42" t="str">
+        <x:v>-41.779791859131</x:v>
+      </x:c>
+      <x:c r="F35" s="42" t="str">
+        <x:v>42.119927127804</x:v>
+      </x:c>
+      <x:c r="G35" s="42" t="str">
+        <x:v>85.599718986935</x:v>
+      </x:c>
+      <x:c r="H35" s="42" t="str">
+        <x:v>43.479791859131</x:v>
+      </x:c>
+      <x:c r="I35" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J35" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K35" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B36" s="36" t="str">
+        <x:v>XV</x:v>
+      </x:c>
+      <x:c r="C36" s="36" t="str">
+        <x:v>1.740000</x:v>
+      </x:c>
+      <x:c r="D36" s="42" t="str">
+        <x:v>-12.545503073689</x:v>
+      </x:c>
+      <x:c r="E36" s="42" t="str">
+        <x:v>-5.934441749535</x:v>
+      </x:c>
+      <x:c r="F36" s="42" t="str">
+        <x:v>6.611061324154</x:v>
+      </x:c>
+      <x:c r="G36" s="42" t="str">
+        <x:v>14.285503073689</x:v>
+      </x:c>
+      <x:c r="H36" s="42" t="str">
+        <x:v>7.674441749535</x:v>
+      </x:c>
+      <x:c r="I36" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J36" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K36" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B37" s="36" t="str">
+        <x:v>XVII</x:v>
+      </x:c>
+      <x:c r="C37" s="36" t="str">
+        <x:v>1.750000</x:v>
+      </x:c>
+      <x:c r="D37" s="42" t="str">
+        <x:v>-10.466391957817</x:v>
+      </x:c>
+      <x:c r="E37" s="42" t="str">
+        <x:v>-4.880577524129</x:v>
+      </x:c>
+      <x:c r="F37" s="42" t="str">
+        <x:v>5.585814433688</x:v>
+      </x:c>
+      <x:c r="G37" s="42" t="str">
+        <x:v>12.216391957817</x:v>
+      </x:c>
+      <x:c r="H37" s="42" t="str">
+        <x:v>6.630577524129</x:v>
+      </x:c>
+      <x:c r="I37" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="J37" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="K37" s="36" t="str">
+        <x:v>true</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="F2:F25">
+  <x:conditionalFormatting sqref="F2:F37">
     <x:cfRule type="colorScale" priority="1">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -10796,19 +11595,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C76" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D76" s="42" t="str">
-        <x:v>-0.111024864121</x:v>
+        <x:v>0.420415546280</x:v>
       </x:c>
       <x:c r="E76" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F76" s="42" t="str">
-        <x:v>-1.811024864121</x:v>
+        <x:v>0.260415546280</x:v>
       </x:c>
       <x:c r="G76" s="42" t="str">
-        <x:v>1.811024864121</x:v>
+        <x:v>0.260415546280</x:v>
       </x:c>
       <x:c r="H76" s="36" t="str">
         <x:v>PASS</x:v>
@@ -10822,19 +11621,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C77" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D77" s="42" t="str">
-        <x:v>0.635864765327</x:v>
+        <x:v>-0.111024864121</x:v>
       </x:c>
       <x:c r="E77" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F77" s="42" t="str">
-        <x:v>-1.104135234673</x:v>
+        <x:v>-1.811024864121</x:v>
       </x:c>
       <x:c r="G77" s="42" t="str">
-        <x:v>1.104135234673</x:v>
+        <x:v>1.811024864121</x:v>
       </x:c>
       <x:c r="H77" s="36" t="str">
         <x:v>PASS</x:v>
@@ -10848,19 +11647,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C78" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D78" s="42" t="str">
-        <x:v>0.672285685199</x:v>
+        <x:v>0.635864765327</x:v>
       </x:c>
       <x:c r="E78" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F78" s="42" t="str">
-        <x:v>-1.077714314801</x:v>
+        <x:v>-1.104135234673</x:v>
       </x:c>
       <x:c r="G78" s="42" t="str">
-        <x:v>1.077714314801</x:v>
+        <x:v>1.104135234673</x:v>
       </x:c>
       <x:c r="H78" s="36" t="str">
         <x:v>PASS</x:v>
@@ -10871,22 +11670,22 @@
         <x:v>CP2K-native pbc provider</x:v>
       </x:c>
       <x:c r="B79" s="36" t="str">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C79" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D79" s="42" t="str">
-        <x:v>-0.441453685894</x:v>
+        <x:v>0.672285685199</x:v>
       </x:c>
       <x:c r="E79" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F79" s="42" t="str">
-        <x:v>-5.431453685894</x:v>
+        <x:v>-1.077714314801</x:v>
       </x:c>
       <x:c r="G79" s="42" t="str">
-        <x:v>5.431453685894</x:v>
+        <x:v>1.077714314801</x:v>
       </x:c>
       <x:c r="H79" s="36" t="str">
         <x:v>PASS</x:v>
@@ -10900,19 +11699,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C80" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D80" s="42" t="str">
-        <x:v>1.810235969010</x:v>
+        <x:v>-0.441453685894</x:v>
       </x:c>
       <x:c r="E80" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F80" s="42" t="str">
-        <x:v>-2.419764030990</x:v>
+        <x:v>-5.431453685894</x:v>
       </x:c>
       <x:c r="G80" s="42" t="str">
-        <x:v>2.419764030990</x:v>
+        <x:v>5.431453685894</x:v>
       </x:c>
       <x:c r="H80" s="36" t="str">
         <x:v>PASS</x:v>
@@ -10926,21 +11725,47 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C81" s="36" t="str">
+        <x:v>VIII</x:v>
+      </x:c>
+      <x:c r="D81" s="42" t="str">
+        <x:v>1.810235969010</x:v>
+      </x:c>
+      <x:c r="E81" s="42" t="str">
+        <x:v>4.230000</x:v>
+      </x:c>
+      <x:c r="F81" s="42" t="str">
+        <x:v>-2.419764030990</x:v>
+      </x:c>
+      <x:c r="G81" s="42" t="str">
+        <x:v>2.419764030990</x:v>
+      </x:c>
+      <x:c r="H81" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="15" hidden="0" customHeight="1">
+      <x:c r="A82" s="36" t="str">
+        <x:v>CP2K-native pbc provider</x:v>
+      </x:c>
+      <x:c r="B82" s="36" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C82" s="36" t="str">
         <x:v>XIV</x:v>
       </x:c>
-      <x:c r="D81" s="42" t="str">
+      <x:c r="D82" s="42" t="str">
         <x:v>0.090455358961</x:v>
       </x:c>
-      <x:c r="E81" s="42" t="str">
+      <x:c r="E82" s="42" t="str">
         <x:v>1.700000</x:v>
       </x:c>
-      <x:c r="F81" s="42" t="str">
+      <x:c r="F82" s="42" t="str">
         <x:v>-1.609544641039</x:v>
       </x:c>
-      <x:c r="G81" s="42" t="str">
+      <x:c r="G82" s="42" t="str">
         <x:v>1.609544641039</x:v>
       </x:c>
-      <x:c r="H81" s="36" t="str">
+      <x:c r="H82" s="36" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
@@ -11015,7 +11840,7 @@
     </x:row>
     <x:row r="2" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A2" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="36" t="str">
         <x:v>Ih</x:v>
@@ -11024,16 +11849,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="36" t="str">
-        <x:v>-7340.672803582856432</x:v>
+        <x:v>-918.186577848805996</x:v>
       </x:c>
       <x:c r="E2" s="36" t="str">
-        <x:v>-917.584100447857054</x:v>
+        <x:v>-918.186577848805996</x:v>
       </x:c>
       <x:c r="F2" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G2" s="40" t="str">
-        <x:v>cc6ec119078ecd4769f50893aa7cd6128390cab0eb6f069d58d9972b0a1904b7</x:v>
+        <x:v>9aa350879d43ac7445bef16ad619abbdc73a6d8f19a29ff329bf5e6b1113c9a5</x:v>
       </x:c>
       <x:c r="H2" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11045,13 +11870,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K2" s="40" t="str">
-        <x:v>749d6063e20b5033943b7bf3d3ca55f97b625b2e621626e80ca65619a4261242</x:v>
+        <x:v>bc3729dcf9c02d7f8e2f04163a407fb546383ef85398d19b303799556771a5d7</x:v>
       </x:c>
       <x:c r="L2" s="40" t="str">
-        <x:v>19aba161f02ae7e25782bdd8defba0eec7d4bfdbcb1ab628af8c6dc403dbe881</x:v>
+        <x:v>b9a83be5c4ee6571f22c6b05f874cefc110b78eaf65b0283be3846faef028d39</x:v>
       </x:c>
       <x:c r="M2" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/Ih/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/Ih/result.json</x:v>
       </x:c>
       <x:c r="N2" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11059,7 +11884,7 @@
     </x:row>
     <x:row r="3" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A3" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="36" t="str">
         <x:v>II</x:v>
@@ -11068,16 +11893,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="36" t="str">
-        <x:v>-7340.250498723466990</x:v>
+        <x:v>-918.086188315030199</x:v>
       </x:c>
       <x:c r="E3" s="36" t="str">
-        <x:v>-917.531312340433374</x:v>
+        <x:v>-918.086188315030199</x:v>
       </x:c>
       <x:c r="F3" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G3" s="40" t="str">
-        <x:v>bb00e41511d4b1e4cec22e3de12ab94f4556cc0795c62a93f47bcf856947f88a</x:v>
+        <x:v>df58c1793e42fde72ca4b180ca8a064e9970b5cafb0375af132555c7ce6014ae</x:v>
       </x:c>
       <x:c r="H3" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11089,13 +11914,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K3" s="40" t="str">
-        <x:v>1585e0309ce639820ab8b153d3f6dd19f42fc9a1da7ad80a96173efef3ac6155</x:v>
+        <x:v>d32b6cbb080e28cd0ba9a15e397b0b5561fe6d45219a716025d2136d8ce3b324</x:v>
       </x:c>
       <x:c r="L3" s="40" t="str">
-        <x:v>2828276ebf4d0a050e11f37f5ce82a2b7ba987634e900d8c6a8a9fb0c6a3c540</x:v>
+        <x:v>b6b895c66e8b6bb619f7d35d334aa94c3421096665275a70de7c8f7424cb3099</x:v>
       </x:c>
       <x:c r="M3" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/II/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/II/result.json</x:v>
       </x:c>
       <x:c r="N3" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11103,7 +11928,7 @@
     </x:row>
     <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A4" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="36" t="str">
         <x:v>III</x:v>
@@ -11112,16 +11937,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D4" s="36" t="str">
-        <x:v>-7341.762846103735683</x:v>
+        <x:v>-918.969632681992834</x:v>
       </x:c>
       <x:c r="E4" s="36" t="str">
-        <x:v>-917.720355762966960</x:v>
+        <x:v>-918.969632681992834</x:v>
       </x:c>
       <x:c r="F4" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G4" s="40" t="str">
-        <x:v>b4fb7f7d4314640b30726af13be2ca0345cc1540c21136a11c4f3ddd5c476952</x:v>
+        <x:v>e02513be90d29d54c9a3b7b9d550a5b24f68d7cfa3ac49fceb6395c86a1c6352</x:v>
       </x:c>
       <x:c r="H4" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11133,13 +11958,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K4" s="40" t="str">
-        <x:v>0f0a1e5e67e212364bce5dce4df0b085e241ae1f5fcc3d350f056167976c0fa1</x:v>
+        <x:v>54eb52826351753d21df4c9966b9b8b289a3d91e29a5111e37a44cac585b4b42</x:v>
       </x:c>
       <x:c r="L4" s="40" t="str">
-        <x:v>ca0ca35b91cec751737872a2f9e57c5bfa2279fa762f8d191f0670364701479e</x:v>
+        <x:v>afc50a771612099458eb0b2bbe576462da3f9241d152f47f4d903c97ed678174</x:v>
       </x:c>
       <x:c r="M4" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/III/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/III/result.json</x:v>
       </x:c>
       <x:c r="N4" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11147,7 +11972,7 @@
     </x:row>
     <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A5" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="36" t="str">
         <x:v>IV</x:v>
@@ -11156,16 +11981,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="36" t="str">
-        <x:v>-9787.551228228514447</x:v>
+        <x:v>-1224.641725501611973</x:v>
       </x:c>
       <x:c r="E5" s="36" t="str">
-        <x:v>-1223.443903528564306</x:v>
+        <x:v>-1224.641725501611973</x:v>
       </x:c>
       <x:c r="F5" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G5" s="40" t="str">
-        <x:v>8ee3eca6ffdcce22ebba5414c22666ba6bb796a17c97016cb36339ebf1f7144e</x:v>
+        <x:v>87e98760385cf3674274809f5c0cf286d82d498ca32ed6ae628ab9788a8cfa4e</x:v>
       </x:c>
       <x:c r="H5" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11177,13 +12002,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K5" s="40" t="str">
-        <x:v>fac4327e8741119ee86ac0e7b7ea8f805661268db93dcaf33fd1acf176dcd434</x:v>
+        <x:v>33dca44ea2ebc93deaf0fb0fe586cf85f5949b796d60f5b5fd810bb5c718bdf6</x:v>
       </x:c>
       <x:c r="L5" s="40" t="str">
-        <x:v>11fd44ab82017bde57a87b5d4331cf0977fbf5d5b029b7c23a530134addf9d38</x:v>
+        <x:v>862d561ac5eb82f383abd37a50e06f9ade227c0b1c8fb7d71d4ff76d95e1e144</x:v>
       </x:c>
       <x:c r="M5" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/IV/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/IV/result.json</x:v>
       </x:c>
       <x:c r="N5" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11191,7 +12016,7 @@
     </x:row>
     <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="36" t="str">
         <x:v>VI</x:v>
@@ -11200,16 +12025,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="36" t="str">
-        <x:v>-6118.094544293921899</x:v>
+        <x:v>-765.366777850274957</x:v>
       </x:c>
       <x:c r="E6" s="36" t="str">
-        <x:v>-764.761818036740237</x:v>
+        <x:v>-765.366777850274957</x:v>
       </x:c>
       <x:c r="F6" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G6" s="40" t="str">
-        <x:v>d99062f4ddc7012617728ead977427ccfe556383ed12f9d9fa619662e9f1288b</x:v>
+        <x:v>bdbf876e7a1c12bc1c198fbbee3d47fd501037ed8e81c5458d4d4ba259d30ba2</x:v>
       </x:c>
       <x:c r="H6" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11221,13 +12046,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K6" s="40" t="str">
-        <x:v>73f06bc0cf30b027789b2233371261ccfa00e2cd52583d4540462b934655773f</x:v>
+        <x:v>b4cbe4efeaf6d2ec5927c46440c72199185885dde2e454af719945db23d9ac32</x:v>
       </x:c>
       <x:c r="L6" s="40" t="str">
-        <x:v>bd1ffe9cbab33487568da822ccac732b8acb9d1aa6481e3d218b5dfbea9da405</x:v>
+        <x:v>cdfc95fbed41632ef3db6a0d645b4fad9a5fe23c8b5a0659fc81977bfa58bfb4</x:v>
       </x:c>
       <x:c r="M6" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/VI/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/VI/result.json</x:v>
       </x:c>
       <x:c r="N6" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11235,7 +12060,7 @@
     </x:row>
     <x:row r="7" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A7" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="36" t="str">
         <x:v>VII</x:v>
@@ -11244,16 +12069,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="36" t="str">
-        <x:v>-7346.228700255577678</x:v>
+        <x:v>-919.371249481594873</x:v>
       </x:c>
       <x:c r="E7" s="36" t="str">
-        <x:v>-918.278587531947210</x:v>
+        <x:v>-919.371249481594873</x:v>
       </x:c>
       <x:c r="F7" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G7" s="40" t="str">
-        <x:v>4de281e3ab3632f443b22f99162e80a3a327c0b8124489c015d4b68fa62d1d91</x:v>
+        <x:v>b45fed8bcdd9050ca302bec8828e752859c700a23f60fcdec9229ad410e889fa</x:v>
       </x:c>
       <x:c r="H7" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11265,13 +12090,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K7" s="40" t="str">
-        <x:v>6315900ad724a8454646e2e5d7bd939e20d8f96a5f91299c9e7b2066b6d4756b</x:v>
+        <x:v>5b28dbc9521f903d9f984c970eaeeb6ad61e942bbf1ccab0533ffe90d9d7e597</x:v>
       </x:c>
       <x:c r="L7" s="40" t="str">
-        <x:v>049191e481ba7c550437dfa8109547993b3f5e2c6c3ad6a2fe17714338775a42</x:v>
+        <x:v>19d4ce5c13e3d290cc045e5f4172aceac8cbcc40d6863d65223068133b388ec2</x:v>
       </x:c>
       <x:c r="M7" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/VII/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/VII/result.json</x:v>
       </x:c>
       <x:c r="N7" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11279,7 +12104,7 @@
     </x:row>
     <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A8" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
         <x:v>VIII</x:v>
@@ -11288,16 +12113,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="36" t="str">
-        <x:v>-4895.669023276129337</x:v>
+        <x:v>-612.894796902710937</x:v>
       </x:c>
       <x:c r="E8" s="36" t="str">
-        <x:v>-611.958627909516167</x:v>
+        <x:v>-612.894796902710937</x:v>
       </x:c>
       <x:c r="F8" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G8" s="40" t="str">
-        <x:v>665dd43c54024db79d58c834bb4aa59727e405c1139b7e575dc73054d816a3d3</x:v>
+        <x:v>aaec8cece8b97380b3bfedc019f0e268fa1e00f019d7f12de02790879244e453</x:v>
       </x:c>
       <x:c r="H8" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11309,13 +12134,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K8" s="40" t="str">
-        <x:v>431da8381a1a096a120a8785f443e130bf7a448ab544ec3ba5e1c15d30426780</x:v>
+        <x:v>2af24a0c51daf621685d9572593f00acc0cd87c87ed9588990ae14bb4568e2e0</x:v>
       </x:c>
       <x:c r="L8" s="40" t="str">
-        <x:v>c217d49f9ed386839fab6a42cb7e7b425695818aa73ee955d5b4feed5de50cfc</x:v>
+        <x:v>30f4f436e65e72481da25f7251dfb07bac593d648946f403e7ec16031cfe1191</x:v>
       </x:c>
       <x:c r="M8" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/VIII/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/VIII/result.json</x:v>
       </x:c>
       <x:c r="N8" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11323,7 +12148,7 @@
     </x:row>
     <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="36" t="str">
         <x:v>IX</x:v>
@@ -11332,16 +12157,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="36" t="str">
-        <x:v>-7341.567545311303547</x:v>
+        <x:v>-918.854693502965802</x:v>
       </x:c>
       <x:c r="E9" s="36" t="str">
-        <x:v>-917.695943163912943</x:v>
+        <x:v>-918.854693502965802</x:v>
       </x:c>
       <x:c r="F9" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G9" s="40" t="str">
-        <x:v>ec345cbd2b7c34ea3f8f9f891c8486e4ac07e77e63517cb17b7ea17ca27df959</x:v>
+        <x:v>1ff6d5c95fcdf733d13ba53e53335411da5f0f16ad0bc9349b9215ae6d08ade3</x:v>
       </x:c>
       <x:c r="H9" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11353,13 +12178,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K9" s="40" t="str">
-        <x:v>02fb609bf9378960d55c2f9b5e5b5c2de4b022902aedafe644e73e0b408a712f</x:v>
+        <x:v>e9744f213c3f6ec0aaf98bc40cdef58ff3c6aed6daf964e10fc49bf4355cdf56</x:v>
       </x:c>
       <x:c r="L9" s="40" t="str">
-        <x:v>a4f36ea7ce09cf326ab5836851de01f8df22c7641d2d775c51f0c74513ff2054</x:v>
+        <x:v>25b9b44c3f35bffaf856ea68a49d93ff5d33680aff30ec8601101f284d136aec</x:v>
       </x:c>
       <x:c r="M9" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/IX/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/IX/result.json</x:v>
       </x:c>
       <x:c r="N9" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11367,7 +12192,7 @@
     </x:row>
     <x:row r="10" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A10" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B10" s="36" t="str">
         <x:v>XI</x:v>
@@ -11376,16 +12201,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D10" s="36" t="str">
-        <x:v>-4895.842885700069019</x:v>
+        <x:v>-612.808122177969835</x:v>
       </x:c>
       <x:c r="E10" s="36" t="str">
-        <x:v>-611.980360712508627</x:v>
+        <x:v>-612.808122177969835</x:v>
       </x:c>
       <x:c r="F10" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G10" s="40" t="str">
-        <x:v>89ce70f57ad4a49e4dcdf3d151a2981304d866190279ec84d516d9001890f737</x:v>
+        <x:v>1d8179172ae08b30df8afcab7afe059423aba0a965490649110cfc45df5d1956</x:v>
       </x:c>
       <x:c r="H10" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11397,13 +12222,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K10" s="40" t="str">
-        <x:v>9e40c7d2e505f009b2fede2023f09202f61031da6e211b54885d2f444fda3e65</x:v>
+        <x:v>dc062856e93b6e05bbcf35543388380a99a08f60f820ea0bf10bac4c3174a4ae</x:v>
       </x:c>
       <x:c r="L10" s="40" t="str">
-        <x:v>d899ae30870a775cb05fbc963f5711a02d2e7ed5f844cb0997e726cc0aaf2ce3</x:v>
+        <x:v>6f66997c2b7ea46783a747799762f4a7d49eef24f95f153ce63cc2b1b866b489</x:v>
       </x:c>
       <x:c r="M10" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/XI/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/XI/result.json</x:v>
       </x:c>
       <x:c r="N10" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11411,7 +12236,7 @@
     </x:row>
     <x:row r="11" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A11" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B11" s="36" t="str">
         <x:v>XIII</x:v>
@@ -11420,16 +12245,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D11" s="36" t="str">
-        <x:v>-17128.157858443981240</x:v>
+        <x:v>-2143.118522025381480</x:v>
       </x:c>
       <x:c r="E11" s="36" t="str">
-        <x:v>-2141.019732305497655</x:v>
+        <x:v>-2143.118522025381480</x:v>
       </x:c>
       <x:c r="F11" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G11" s="40" t="str">
-        <x:v>082bd77882b5a9bf57f9ca50ee6a4e5049b969c8b59c6eef2c593517ed8e0d23</x:v>
+        <x:v>e312c0cda85b25ceeb4d8e022c270ab642d9b9033ad4309efe1dc9b707695a2c</x:v>
       </x:c>
       <x:c r="H11" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11441,13 +12266,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K11" s="40" t="str">
-        <x:v>a3b852b7efff597bc8334e7d7873fb8f7d81ccf638728e9a0db0f6eeb2de8134</x:v>
+        <x:v>0e542eec3eca8c595fb89ba524b38be76c24d567c26e20a4c67a6f83dc746d34</x:v>
       </x:c>
       <x:c r="L11" s="40" t="str">
-        <x:v>345869fe0367a8b8d3ae51e20b6e19a33b5c2bd5a1e7cd7fc73e3fdf989a66a0</x:v>
+        <x:v>4b5ee7c515b2eeecfe36e6085b6198aa24ba07c4d2f60942149f0c624756e236</x:v>
       </x:c>
       <x:c r="M11" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/XIII/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/XIII/result.json</x:v>
       </x:c>
       <x:c r="N11" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11455,7 +12280,7 @@
     </x:row>
     <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A12" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B12" s="36" t="str">
         <x:v>XIV</x:v>
@@ -11464,16 +12289,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D12" s="36" t="str">
-        <x:v>-7344.313059511200663</x:v>
+        <x:v>-919.003942998695265</x:v>
       </x:c>
       <x:c r="E12" s="36" t="str">
-        <x:v>-918.039132438900083</x:v>
+        <x:v>-919.003942998695265</x:v>
       </x:c>
       <x:c r="F12" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G12" s="40" t="str">
-        <x:v>2e836349250b157878fd3f1683d921713e8f3757a542b6c0db439e45e39c7623</x:v>
+        <x:v>31a08202cdca25ce13ed9fb538367ff86fbe4558821ab34a7149d6e185a03a8c</x:v>
       </x:c>
       <x:c r="H12" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11485,13 +12310,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K12" s="40" t="str">
-        <x:v>55239c2d1be59876cc4756a3653c23ddd201284ceee08401cb16d4b85ef74bdb</x:v>
+        <x:v>50c01c883877a45dd01d4b71739693166ca3d106a05a6430e68f92728c161f3a</x:v>
       </x:c>
       <x:c r="L12" s="40" t="str">
-        <x:v>6bcdad038104cc366714d297ef3b13a723ddb09d23a0f5c5d31e07cb4755cdf0</x:v>
+        <x:v>d4e6b3f4d89aa733f27ea752e5b69fd7cca90df4b62cd599acebd54afae125c6</x:v>
       </x:c>
       <x:c r="M12" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/XIV/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/XIV/result.json</x:v>
       </x:c>
       <x:c r="N12" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11499,7 +12324,7 @@
     </x:row>
     <x:row r="13" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A13" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B13" s="36" t="str">
         <x:v>XV</x:v>
@@ -11508,16 +12333,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D13" s="36" t="str">
-        <x:v>-6118.100768583846730</x:v>
+        <x:v>-765.368489253919165</x:v>
       </x:c>
       <x:c r="E13" s="36" t="str">
-        <x:v>-764.762596072980841</x:v>
+        <x:v>-765.368489253919165</x:v>
       </x:c>
       <x:c r="F13" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G13" s="40" t="str">
-        <x:v>f69c74d09a7612876d5c85043287a99221062a22e8467f5e01bb511d4ac4ce31</x:v>
+        <x:v>8e03a362df5eba3f6a59021584b678bf7963501283e55ed40d83afcbe9c0962d</x:v>
       </x:c>
       <x:c r="H13" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11529,13 +12354,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K13" s="40" t="str">
-        <x:v>083decac894c4469dd80bbd847a50b964aef017c254deac1feb821ef37e3241a</x:v>
+        <x:v>cf4763e972603b5bdb5fe93caf36b5465e12c72f2972a37294483e7cf548be45</x:v>
       </x:c>
       <x:c r="L13" s="40" t="str">
-        <x:v>2237318935a3039634386fbbec6baf5557d677ef31a26898b7c3ef70f74e93e8</x:v>
+        <x:v>8446d303643b00c4a5fa657af6830b4cd9be9ce04f459fb5d64836ab52e19122</x:v>
       </x:c>
       <x:c r="M13" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/XV/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/XV/result.json</x:v>
       </x:c>
       <x:c r="N13" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11543,7 +12368,7 @@
     </x:row>
     <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A14" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="36" t="str">
         <x:v>XVII</x:v>
@@ -11552,16 +12377,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D14" s="36" t="str">
-        <x:v>-3670.801471312778631</x:v>
+        <x:v>-459.212774888400929</x:v>
       </x:c>
       <x:c r="E14" s="36" t="str">
-        <x:v>-458.850183914097329</x:v>
+        <x:v>-459.212774888400929</x:v>
       </x:c>
       <x:c r="F14" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G14" s="40" t="str">
-        <x:v>17446bfc858d189bb9e48745c7e14b470ba2b72bc56e7db50afa2864a101b8c7</x:v>
+        <x:v>19f9494c99dffcb5bfcd7d4c7dccf35fd4be806648b426c0f1816a05c7228681</x:v>
       </x:c>
       <x:c r="H14" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11573,13 +12398,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K14" s="40" t="str">
-        <x:v>6730aa099e286ba542e96fa997d5a589f7024ccdaa6340ecf54625eede2cdf90</x:v>
+        <x:v>1ae7eb4e3fd3221510823d866265dbef4f3cc953361a1277119bfadea7240198</x:v>
       </x:c>
       <x:c r="L14" s="40" t="str">
-        <x:v>87325e1be1e4e04c18bbaf3422d3aa4621531f067cb0af7326bacce5225fac04</x:v>
+        <x:v>1965373954638eed246a34dae5fa47a7f26d2694d619c2c07c395f8e0bac28db</x:v>
       </x:c>
       <x:c r="M14" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k222/XVII/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k111/XVII/result.json</x:v>
       </x:c>
       <x:c r="N14" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11587,7 +12412,7 @@
     </x:row>
     <x:row r="15" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A15" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="36" t="str">
         <x:v>Ih</x:v>
@@ -11596,16 +12421,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D15" s="36" t="str">
-        <x:v>-24772.174455952565040</x:v>
+        <x:v>-7340.672803582856432</x:v>
       </x:c>
       <x:c r="E15" s="36" t="str">
-        <x:v>-917.487942813057998</x:v>
+        <x:v>-917.584100447857054</x:v>
       </x:c>
       <x:c r="F15" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G15" s="40" t="str">
-        <x:v>390e6e2f86de77f0cb13c88f92ee287058d834466e56977c66c145bd4f14ba14</x:v>
+        <x:v>cc6ec119078ecd4769f50893aa7cd6128390cab0eb6f069d58d9972b0a1904b7</x:v>
       </x:c>
       <x:c r="H15" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11617,13 +12442,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K15" s="40" t="str">
-        <x:v>0b73af206d417114a1bd8ab1927b0f658aede0e14fdd91fa336e3086a47d1a53</x:v>
+        <x:v>749d6063e20b5033943b7bf3d3ca55f97b625b2e621626e80ca65619a4261242</x:v>
       </x:c>
       <x:c r="L15" s="40" t="str">
-        <x:v>b5d9dc6f1ed0f5e371ef19d851947b69fe24cfe523744f4ee76324be341ccfd2</x:v>
+        <x:v>19aba161f02ae7e25782bdd8defba0eec7d4bfdbcb1ab628af8c6dc403dbe881</x:v>
       </x:c>
       <x:c r="M15" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/Ih/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/Ih/result.json</x:v>
       </x:c>
       <x:c r="N15" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11631,7 +12456,7 @@
     </x:row>
     <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A16" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B16" s="36" t="str">
         <x:v>II</x:v>
@@ -11640,16 +12465,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D16" s="36" t="str">
-        <x:v>-24772.209007920748263</x:v>
+        <x:v>-7340.250498723466990</x:v>
       </x:c>
       <x:c r="E16" s="36" t="str">
-        <x:v>-917.489222515583265</x:v>
+        <x:v>-917.531312340433374</x:v>
       </x:c>
       <x:c r="F16" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G16" s="40" t="str">
-        <x:v>9c6fc3c088893d7413933ffd4ae6adeeb30bac20c9275e3ca73ccfe590039ff0</x:v>
+        <x:v>bb00e41511d4b1e4cec22e3de12ab94f4556cc0795c62a93f47bcf856947f88a</x:v>
       </x:c>
       <x:c r="H16" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11661,13 +12486,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K16" s="40" t="str">
-        <x:v>784ce0060d9cf5dcfa7f5669ad546170cf6a9c85797f6077053b6e44b5835f5d</x:v>
+        <x:v>1585e0309ce639820ab8b153d3f6dd19f42fc9a1da7ad80a96173efef3ac6155</x:v>
       </x:c>
       <x:c r="L16" s="40" t="str">
-        <x:v>686232d069fd45f79b8341d9baea08121f6aabc2d4c7b87cd507d4cf723232b2</x:v>
+        <x:v>2828276ebf4d0a050e11f37f5ce82a2b7ba987634e900d8c6a8a9fb0c6a3c540</x:v>
       </x:c>
       <x:c r="M16" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/II/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/II/result.json</x:v>
       </x:c>
       <x:c r="N16" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11675,7 +12500,7 @@
     </x:row>
     <x:row r="17" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A17" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B17" s="36" t="str">
         <x:v>III</x:v>
@@ -11684,16 +12509,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D17" s="36" t="str">
-        <x:v>-24772.386737649714632</x:v>
+        <x:v>-7341.762846103735683</x:v>
       </x:c>
       <x:c r="E17" s="36" t="str">
-        <x:v>-917.495805098137566</x:v>
+        <x:v>-917.720355762966960</x:v>
       </x:c>
       <x:c r="F17" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G17" s="40" t="str">
-        <x:v>9bf8e1381f7d38b8042bcaee4d3c3112520b647ce612cc447efe6435e26c7732</x:v>
+        <x:v>b4fb7f7d4314640b30726af13be2ca0345cc1540c21136a11c4f3ddd5c476952</x:v>
       </x:c>
       <x:c r="H17" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11705,13 +12530,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K17" s="40" t="str">
-        <x:v>0142e8dcc9d168ac1a9d08123e8fe71b3fec78ee6f6133d20fdc14596e5c7cbd</x:v>
+        <x:v>0f0a1e5e67e212364bce5dce4df0b085e241ae1f5fcc3d350f056167976c0fa1</x:v>
       </x:c>
       <x:c r="L17" s="40" t="str">
-        <x:v>642c61b22bce433639b50114ac3e15ff68ac77c321e3c62d2f5d731b8d29b4e6</x:v>
+        <x:v>ca0ca35b91cec751737872a2f9e57c5bfa2279fa762f8d191f0670364701479e</x:v>
       </x:c>
       <x:c r="M17" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/III/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/III/result.json</x:v>
       </x:c>
       <x:c r="N17" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11719,7 +12544,7 @@
     </x:row>
     <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B18" s="36" t="str">
         <x:v>IV</x:v>
@@ -11728,16 +12553,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D18" s="36" t="str">
-        <x:v>-33029.293860518417205</x:v>
+        <x:v>-9787.551228228514447</x:v>
       </x:c>
       <x:c r="E18" s="36" t="str">
-        <x:v>-1223.307180019200587</x:v>
+        <x:v>-1223.443903528564306</x:v>
       </x:c>
       <x:c r="F18" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G18" s="40" t="str">
-        <x:v>1213f0675a27713d0093568cdbdc8b50e8159e4154e42b0a491d0f77e5cf96ab</x:v>
+        <x:v>8ee3eca6ffdcce22ebba5414c22666ba6bb796a17c97016cb36339ebf1f7144e</x:v>
       </x:c>
       <x:c r="H18" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11749,13 +12574,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K18" s="40" t="str">
-        <x:v>02a875b1ce4838020e682dc007d41941e1d805ca9c198201a9c8d6fe109467ad</x:v>
+        <x:v>fac4327e8741119ee86ac0e7b7ea8f805661268db93dcaf33fd1acf176dcd434</x:v>
       </x:c>
       <x:c r="L18" s="40" t="str">
-        <x:v>14782501f727c6773e6bb979bfe00db327047e1cd0c66d95ac3b29a0d10572e6</x:v>
+        <x:v>11fd44ab82017bde57a87b5d4331cf0977fbf5d5b029b7c23a530134addf9d38</x:v>
       </x:c>
       <x:c r="M18" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/IV/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/IV/result.json</x:v>
       </x:c>
       <x:c r="N18" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11763,7 +12588,7 @@
     </x:row>
     <x:row r="19" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A19" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="36" t="str">
         <x:v>VI</x:v>
@@ -11772,16 +12597,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D19" s="36" t="str">
-        <x:v>-20644.086699889830925</x:v>
+        <x:v>-6118.094544293921899</x:v>
       </x:c>
       <x:c r="E19" s="36" t="str">
-        <x:v>-764.595803699623389</x:v>
+        <x:v>-764.761818036740237</x:v>
       </x:c>
       <x:c r="F19" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G19" s="40" t="str">
-        <x:v>77dcb209d6002de61674716b9e4084d2620dd1de648b719926306b0d47ea25f8</x:v>
+        <x:v>d99062f4ddc7012617728ead977427ccfe556383ed12f9d9fa619662e9f1288b</x:v>
       </x:c>
       <x:c r="H19" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11793,13 +12618,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K19" s="40" t="str">
-        <x:v>9a36c9ebf69adfab87535842b04ccd6f02bcd36e8e5729f5e4059a6e347a0847</x:v>
+        <x:v>73f06bc0cf30b027789b2233371261ccfa00e2cd52583d4540462b934655773f</x:v>
       </x:c>
       <x:c r="L19" s="40" t="str">
-        <x:v>8085599e1a91241f95c67035c1794b6f1864c0f0f373ce827233ca80a6bc50d0</x:v>
+        <x:v>bd1ffe9cbab33487568da822ccac732b8acb9d1aa6481e3d218b5dfbea9da405</x:v>
       </x:c>
       <x:c r="M19" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/VI/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/VI/result.json</x:v>
       </x:c>
       <x:c r="N19" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11807,7 +12632,7 @@
     </x:row>
     <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A20" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B20" s="36" t="str">
         <x:v>VII</x:v>
@@ -11816,16 +12641,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D20" s="36" t="str">
-        <x:v>-24781.731768295205256</x:v>
+        <x:v>-7346.228700255577678</x:v>
       </x:c>
       <x:c r="E20" s="36" t="str">
-        <x:v>-917.841917344266903</x:v>
+        <x:v>-918.278587531947210</x:v>
       </x:c>
       <x:c r="F20" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G20" s="40" t="str">
-        <x:v>8e7314d0d1920535e14a86ae92013aa5f19e35f835533c4c5b5152186aa75235</x:v>
+        <x:v>4de281e3ab3632f443b22f99162e80a3a327c0b8124489c015d4b68fa62d1d91</x:v>
       </x:c>
       <x:c r="H20" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11837,13 +12662,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K20" s="40" t="str">
-        <x:v>f14ad261b44fcf03970644ef4d85d7c49ea702be264505ca46475f864e830c7c</x:v>
+        <x:v>6315900ad724a8454646e2e5d7bd939e20d8f96a5f91299c9e7b2066b6d4756b</x:v>
       </x:c>
       <x:c r="L20" s="40" t="str">
-        <x:v>b1f4f0feea1d160b61ae3c95fa68d4a0c1fe48000535cd44c3706326b689df84</x:v>
+        <x:v>049191e481ba7c550437dfa8109547993b3f5e2c6c3ad6a2fe17714338775a42</x:v>
       </x:c>
       <x:c r="M20" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/VII/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/VII/result.json</x:v>
       </x:c>
       <x:c r="N20" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11851,7 +12676,7 @@
     </x:row>
     <x:row r="21" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A21" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B21" s="36" t="str">
         <x:v>VIII</x:v>
@@ -11860,16 +12685,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D21" s="36" t="str">
-        <x:v>-16516.404243755045172</x:v>
+        <x:v>-4895.669023276129337</x:v>
       </x:c>
       <x:c r="E21" s="36" t="str">
-        <x:v>-611.718675694631315</x:v>
+        <x:v>-611.958627909516167</x:v>
       </x:c>
       <x:c r="F21" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G21" s="40" t="str">
-        <x:v>9bd1a82532940e5f98fb6e04cc291787e0ea73d9ab34ae89de69867e9bf21398</x:v>
+        <x:v>665dd43c54024db79d58c834bb4aa59727e405c1139b7e575dc73054d816a3d3</x:v>
       </x:c>
       <x:c r="H21" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11881,13 +12706,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K21" s="40" t="str">
-        <x:v>76d2112aa0b7898a8d192a28271620619da202b69f6f0216eb47f2814bf56eef</x:v>
+        <x:v>431da8381a1a096a120a8785f443e130bf7a448ab544ec3ba5e1c15d30426780</x:v>
       </x:c>
       <x:c r="L21" s="40" t="str">
-        <x:v>f3422098ad845a28ffe6f8981a7a8b665d4f2eed1672748ef2ef7fa328eeabcf</x:v>
+        <x:v>c217d49f9ed386839fab6a42cb7e7b425695818aa73ee955d5b4feed5de50cfc</x:v>
       </x:c>
       <x:c r="M21" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/VIII/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/VIII/result.json</x:v>
       </x:c>
       <x:c r="N21" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11895,7 +12720,7 @@
     </x:row>
     <x:row r="22" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A22" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B22" s="36" t="str">
         <x:v>IX</x:v>
@@ -11904,16 +12729,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D22" s="36" t="str">
-        <x:v>-24772.516876874447917</x:v>
+        <x:v>-7341.567545311303547</x:v>
       </x:c>
       <x:c r="E22" s="36" t="str">
-        <x:v>-917.500625069424018</x:v>
+        <x:v>-917.695943163912943</x:v>
       </x:c>
       <x:c r="F22" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G22" s="40" t="str">
-        <x:v>c65ee97797664282f7e987860a895bc4d30d33af8d190c41aa96ba78b0f984e5</x:v>
+        <x:v>ec345cbd2b7c34ea3f8f9f891c8486e4ac07e77e63517cb17b7ea17ca27df959</x:v>
       </x:c>
       <x:c r="H22" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11925,13 +12750,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K22" s="40" t="str">
-        <x:v>9d93b4c1b93403e1a86d719220529a9d39f053ed90bf259fce83ee86b308f17d</x:v>
+        <x:v>02fb609bf9378960d55c2f9b5e5b5c2de4b022902aedafe644e73e0b408a712f</x:v>
       </x:c>
       <x:c r="L22" s="40" t="str">
-        <x:v>26a1b0106e9faf6a69101dc82c5cdc561ce615c1f63e6482191799086ff2eea6</x:v>
+        <x:v>a4f36ea7ce09cf326ab5836851de01f8df22c7641d2d775c51f0c74513ff2054</x:v>
       </x:c>
       <x:c r="M22" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/IX/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/IX/result.json</x:v>
       </x:c>
       <x:c r="N22" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11939,7 +12764,7 @@
     </x:row>
     <x:row r="23" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A23" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B23" s="36" t="str">
         <x:v>XI</x:v>
@@ -11948,16 +12773,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D23" s="36" t="str">
-        <x:v>-16517.347225468845863</x:v>
+        <x:v>-4895.842885700069019</x:v>
       </x:c>
       <x:c r="E23" s="36" t="str">
-        <x:v>-611.753600943290621</x:v>
+        <x:v>-611.980360712508627</x:v>
       </x:c>
       <x:c r="F23" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G23" s="40" t="str">
-        <x:v>c7ebc2fbbb67b620ef93d11a03adfcb9e8f54c2604931ee36842b670d9caa4f5</x:v>
+        <x:v>89ce70f57ad4a49e4dcdf3d151a2981304d866190279ec84d516d9001890f737</x:v>
       </x:c>
       <x:c r="H23" s="36" t="str">
         <x:v>0.1</x:v>
@@ -11969,13 +12794,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K23" s="40" t="str">
-        <x:v>81f9f34536e4f82d987b2a0e6032a33c87bc6dc7de7b0384909d35d42ee4e999</x:v>
+        <x:v>9e40c7d2e505f009b2fede2023f09202f61031da6e211b54885d2f444fda3e65</x:v>
       </x:c>
       <x:c r="L23" s="40" t="str">
-        <x:v>593944fe2d6f5847859d2f11a7e3deb488bde00e60547f07c95868817d66b87e</x:v>
+        <x:v>d899ae30870a775cb05fbc963f5711a02d2e7ed5f844cb0997e726cc0aaf2ce3</x:v>
       </x:c>
       <x:c r="M23" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/XI/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/XI/result.json</x:v>
       </x:c>
       <x:c r="N23" s="36" t="str">
         <x:v>PASS</x:v>
@@ -11983,7 +12808,7 @@
     </x:row>
     <x:row r="24" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A24" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B24" s="36" t="str">
         <x:v>XIII</x:v>
@@ -11992,16 +12817,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D24" s="36" t="str">
-        <x:v>-57801.612850758501736</x:v>
+        <x:v>-17128.157858443981240</x:v>
       </x:c>
       <x:c r="E24" s="36" t="str">
-        <x:v>-2140.800475954018566</x:v>
+        <x:v>-2141.019732305497655</x:v>
       </x:c>
       <x:c r="F24" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G24" s="40" t="str">
-        <x:v>37b1d93ec726b6e50c401f66bd1c4eca2ff9ae6073a351aedeb1d03d21cc9fd4</x:v>
+        <x:v>082bd77882b5a9bf57f9ca50ee6a4e5049b969c8b59c6eef2c593517ed8e0d23</x:v>
       </x:c>
       <x:c r="H24" s="36" t="str">
         <x:v>0.1</x:v>
@@ -12013,13 +12838,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K24" s="40" t="str">
-        <x:v>1cf9308d274edeb118aba8b3a79ba471e5f9abb3e020d5795bdf945fb822e610</x:v>
+        <x:v>a3b852b7efff597bc8334e7d7873fb8f7d81ccf638728e9a0db0f6eeb2de8134</x:v>
       </x:c>
       <x:c r="L24" s="40" t="str">
-        <x:v>4c7e6011d522d99b4e7af6ac830580758663ceadae43261f7c4046fd9124dc5f</x:v>
+        <x:v>345869fe0367a8b8d3ae51e20b6e19a33b5c2bd5a1e7cd7fc73e3fdf989a66a0</x:v>
       </x:c>
       <x:c r="M24" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/XIII/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/XIII/result.json</x:v>
       </x:c>
       <x:c r="N24" s="36" t="str">
         <x:v>PASS</x:v>
@@ -12027,7 +12852,7 @@
     </x:row>
     <x:row r="25" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A25" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B25" s="36" t="str">
         <x:v>XIV</x:v>
@@ -12036,16 +12861,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D25" s="36" t="str">
-        <x:v>-24777.330294619918277</x:v>
+        <x:v>-7344.313059511200663</x:v>
       </x:c>
       <x:c r="E25" s="36" t="str">
-        <x:v>-917.678899800737668</x:v>
+        <x:v>-918.039132438900083</x:v>
       </x:c>
       <x:c r="F25" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G25" s="40" t="str">
-        <x:v>06ef5467deadd2e61959f6997effdac1b11a6d1ebe61c673d9197a79566363ab</x:v>
+        <x:v>2e836349250b157878fd3f1683d921713e8f3757a542b6c0db439e45e39c7623</x:v>
       </x:c>
       <x:c r="H25" s="36" t="str">
         <x:v>0.1</x:v>
@@ -12057,13 +12882,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K25" s="40" t="str">
-        <x:v>840c2306186c3186ccf9d181cf692ce3feac8d5af846af5663623cd713d4e62e</x:v>
+        <x:v>55239c2d1be59876cc4756a3653c23ddd201284ceee08401cb16d4b85ef74bdb</x:v>
       </x:c>
       <x:c r="L25" s="40" t="str">
-        <x:v>5711936e81a854f0528de07fd00589e85ab7052ebd9bea36e8fadc3097ce3e2f</x:v>
+        <x:v>6bcdad038104cc366714d297ef3b13a723ddb09d23a0f5c5d31e07cb4755cdf0</x:v>
       </x:c>
       <x:c r="M25" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/XIV/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/XIV/result.json</x:v>
       </x:c>
       <x:c r="N25" s="36" t="str">
         <x:v>PASS</x:v>
@@ -12071,7 +12896,7 @@
     </x:row>
     <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A26" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B26" s="36" t="str">
         <x:v>XV</x:v>
@@ -12080,16 +12905,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D26" s="36" t="str">
-        <x:v>-20644.088996855942241</x:v>
+        <x:v>-6118.100768583846730</x:v>
       </x:c>
       <x:c r="E26" s="36" t="str">
-        <x:v>-764.595888772442322</x:v>
+        <x:v>-764.762596072980841</x:v>
       </x:c>
       <x:c r="F26" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G26" s="40" t="str">
-        <x:v>ddcea98e071c52b4125a28a8b2329840e386ca491346213bb671b6025a523c89</x:v>
+        <x:v>f69c74d09a7612876d5c85043287a99221062a22e8467f5e01bb511d4ac4ce31</x:v>
       </x:c>
       <x:c r="H26" s="36" t="str">
         <x:v>0.1</x:v>
@@ -12101,13 +12926,13 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K26" s="40" t="str">
-        <x:v>5f69dcaba3edba31ab66c8d8fdceb85e89f32c4fd6538dc77819d35186a705e6</x:v>
+        <x:v>083decac894c4469dd80bbd847a50b964aef017c254deac1feb821ef37e3241a</x:v>
       </x:c>
       <x:c r="L26" s="40" t="str">
-        <x:v>f05423a7605041f4b509130b07c534c05a89eb9d3dec444ce37814ced0736598</x:v>
+        <x:v>2237318935a3039634386fbbec6baf5557d677ef31a26898b7c3ef70f74e93e8</x:v>
       </x:c>
       <x:c r="M26" s="40" t="str">
-        <x:v>raw/mstore_inorganic_cli/k333/XV/result.json</x:v>
+        <x:v>raw/mstore_inorganic_cli/k222/XV/result.json</x:v>
       </x:c>
       <x:c r="N26" s="36" t="str">
         <x:v>PASS</x:v>
@@ -12115,7 +12940,7 @@
     </x:row>
     <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A27" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B27" s="36" t="str">
         <x:v>XVII</x:v>
@@ -12124,16 +12949,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D27" s="36" t="str">
-        <x:v>-12386.388372012648688</x:v>
+        <x:v>-3670.801471312778631</x:v>
       </x:c>
       <x:c r="E27" s="36" t="str">
-        <x:v>-458.755124889357376</x:v>
+        <x:v>-458.850183914097329</x:v>
       </x:c>
       <x:c r="F27" s="40" t="str">
         <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
       </x:c>
       <x:c r="G27" s="40" t="str">
-        <x:v>89506fdd1b60dcacf9184a9fc61f1dab567cf4fa9ac8d14e49045147acf12f02</x:v>
+        <x:v>17446bfc858d189bb9e48745c7e14b470ba2b72bc56e7db50afa2864a101b8c7</x:v>
       </x:c>
       <x:c r="H27" s="36" t="str">
         <x:v>0.1</x:v>
@@ -12145,15 +12970,587 @@
         <x:v>1.9999999999999999e-06</x:v>
       </x:c>
       <x:c r="K27" s="40" t="str">
+        <x:v>6730aa099e286ba542e96fa997d5a589f7024ccdaa6340ecf54625eede2cdf90</x:v>
+      </x:c>
+      <x:c r="L27" s="40" t="str">
+        <x:v>87325e1be1e4e04c18bbaf3422d3aa4621531f067cb0af7326bacce5225fac04</x:v>
+      </x:c>
+      <x:c r="M27" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k222/XVII/result.json</x:v>
+      </x:c>
+      <x:c r="N27" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A28" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B28" s="36" t="str">
+        <x:v>Ih</x:v>
+      </x:c>
+      <x:c r="C28" s="36" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D28" s="36" t="str">
+        <x:v>-24772.174455952565040</x:v>
+      </x:c>
+      <x:c r="E28" s="36" t="str">
+        <x:v>-917.487942813057998</x:v>
+      </x:c>
+      <x:c r="F28" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G28" s="40" t="str">
+        <x:v>390e6e2f86de77f0cb13c88f92ee287058d834466e56977c66c145bd4f14ba14</x:v>
+      </x:c>
+      <x:c r="H28" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I28" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J28" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K28" s="40" t="str">
+        <x:v>0b73af206d417114a1bd8ab1927b0f658aede0e14fdd91fa336e3086a47d1a53</x:v>
+      </x:c>
+      <x:c r="L28" s="40" t="str">
+        <x:v>b5d9dc6f1ed0f5e371ef19d851947b69fe24cfe523744f4ee76324be341ccfd2</x:v>
+      </x:c>
+      <x:c r="M28" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/Ih/result.json</x:v>
+      </x:c>
+      <x:c r="N28" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A29" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B29" s="36" t="str">
+        <x:v>II</x:v>
+      </x:c>
+      <x:c r="C29" s="36" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D29" s="36" t="str">
+        <x:v>-24772.209007920748263</x:v>
+      </x:c>
+      <x:c r="E29" s="36" t="str">
+        <x:v>-917.489222515583265</x:v>
+      </x:c>
+      <x:c r="F29" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G29" s="40" t="str">
+        <x:v>9c6fc3c088893d7413933ffd4ae6adeeb30bac20c9275e3ca73ccfe590039ff0</x:v>
+      </x:c>
+      <x:c r="H29" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I29" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J29" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K29" s="40" t="str">
+        <x:v>784ce0060d9cf5dcfa7f5669ad546170cf6a9c85797f6077053b6e44b5835f5d</x:v>
+      </x:c>
+      <x:c r="L29" s="40" t="str">
+        <x:v>686232d069fd45f79b8341d9baea08121f6aabc2d4c7b87cd507d4cf723232b2</x:v>
+      </x:c>
+      <x:c r="M29" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/II/result.json</x:v>
+      </x:c>
+      <x:c r="N29" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A30" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B30" s="36" t="str">
+        <x:v>III</x:v>
+      </x:c>
+      <x:c r="C30" s="36" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D30" s="36" t="str">
+        <x:v>-24772.386737649714632</x:v>
+      </x:c>
+      <x:c r="E30" s="36" t="str">
+        <x:v>-917.495805098137566</x:v>
+      </x:c>
+      <x:c r="F30" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G30" s="40" t="str">
+        <x:v>9bf8e1381f7d38b8042bcaee4d3c3112520b647ce612cc447efe6435e26c7732</x:v>
+      </x:c>
+      <x:c r="H30" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I30" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J30" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K30" s="40" t="str">
+        <x:v>0142e8dcc9d168ac1a9d08123e8fe71b3fec78ee6f6133d20fdc14596e5c7cbd</x:v>
+      </x:c>
+      <x:c r="L30" s="40" t="str">
+        <x:v>642c61b22bce433639b50114ac3e15ff68ac77c321e3c62d2f5d731b8d29b4e6</x:v>
+      </x:c>
+      <x:c r="M30" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/III/result.json</x:v>
+      </x:c>
+      <x:c r="N30" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A31" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B31" s="36" t="str">
+        <x:v>IV</x:v>
+      </x:c>
+      <x:c r="C31" s="36" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D31" s="36" t="str">
+        <x:v>-33029.293860518417205</x:v>
+      </x:c>
+      <x:c r="E31" s="36" t="str">
+        <x:v>-1223.307180019200587</x:v>
+      </x:c>
+      <x:c r="F31" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G31" s="40" t="str">
+        <x:v>1213f0675a27713d0093568cdbdc8b50e8159e4154e42b0a491d0f77e5cf96ab</x:v>
+      </x:c>
+      <x:c r="H31" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I31" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J31" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K31" s="40" t="str">
+        <x:v>02a875b1ce4838020e682dc007d41941e1d805ca9c198201a9c8d6fe109467ad</x:v>
+      </x:c>
+      <x:c r="L31" s="40" t="str">
+        <x:v>14782501f727c6773e6bb979bfe00db327047e1cd0c66d95ac3b29a0d10572e6</x:v>
+      </x:c>
+      <x:c r="M31" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/IV/result.json</x:v>
+      </x:c>
+      <x:c r="N31" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A32" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B32" s="36" t="str">
+        <x:v>VI</x:v>
+      </x:c>
+      <x:c r="C32" s="36" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D32" s="36" t="str">
+        <x:v>-20644.086699889830925</x:v>
+      </x:c>
+      <x:c r="E32" s="36" t="str">
+        <x:v>-764.595803699623389</x:v>
+      </x:c>
+      <x:c r="F32" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G32" s="40" t="str">
+        <x:v>77dcb209d6002de61674716b9e4084d2620dd1de648b719926306b0d47ea25f8</x:v>
+      </x:c>
+      <x:c r="H32" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I32" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J32" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K32" s="40" t="str">
+        <x:v>9a36c9ebf69adfab87535842b04ccd6f02bcd36e8e5729f5e4059a6e347a0847</x:v>
+      </x:c>
+      <x:c r="L32" s="40" t="str">
+        <x:v>8085599e1a91241f95c67035c1794b6f1864c0f0f373ce827233ca80a6bc50d0</x:v>
+      </x:c>
+      <x:c r="M32" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/VI/result.json</x:v>
+      </x:c>
+      <x:c r="N32" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A33" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B33" s="36" t="str">
+        <x:v>VII</x:v>
+      </x:c>
+      <x:c r="C33" s="36" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D33" s="36" t="str">
+        <x:v>-24781.731768295205256</x:v>
+      </x:c>
+      <x:c r="E33" s="36" t="str">
+        <x:v>-917.841917344266903</x:v>
+      </x:c>
+      <x:c r="F33" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G33" s="40" t="str">
+        <x:v>8e7314d0d1920535e14a86ae92013aa5f19e35f835533c4c5b5152186aa75235</x:v>
+      </x:c>
+      <x:c r="H33" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I33" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J33" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K33" s="40" t="str">
+        <x:v>f14ad261b44fcf03970644ef4d85d7c49ea702be264505ca46475f864e830c7c</x:v>
+      </x:c>
+      <x:c r="L33" s="40" t="str">
+        <x:v>b1f4f0feea1d160b61ae3c95fa68d4a0c1fe48000535cd44c3706326b689df84</x:v>
+      </x:c>
+      <x:c r="M33" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/VII/result.json</x:v>
+      </x:c>
+      <x:c r="N33" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A34" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B34" s="36" t="str">
+        <x:v>VIII</x:v>
+      </x:c>
+      <x:c r="C34" s="36" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D34" s="36" t="str">
+        <x:v>-16516.404243755045172</x:v>
+      </x:c>
+      <x:c r="E34" s="36" t="str">
+        <x:v>-611.718675694631315</x:v>
+      </x:c>
+      <x:c r="F34" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G34" s="40" t="str">
+        <x:v>9bd1a82532940e5f98fb6e04cc291787e0ea73d9ab34ae89de69867e9bf21398</x:v>
+      </x:c>
+      <x:c r="H34" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I34" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J34" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K34" s="40" t="str">
+        <x:v>76d2112aa0b7898a8d192a28271620619da202b69f6f0216eb47f2814bf56eef</x:v>
+      </x:c>
+      <x:c r="L34" s="40" t="str">
+        <x:v>f3422098ad845a28ffe6f8981a7a8b665d4f2eed1672748ef2ef7fa328eeabcf</x:v>
+      </x:c>
+      <x:c r="M34" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/VIII/result.json</x:v>
+      </x:c>
+      <x:c r="N34" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A35" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B35" s="36" t="str">
+        <x:v>IX</x:v>
+      </x:c>
+      <x:c r="C35" s="36" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D35" s="36" t="str">
+        <x:v>-24772.516876874447917</x:v>
+      </x:c>
+      <x:c r="E35" s="36" t="str">
+        <x:v>-917.500625069424018</x:v>
+      </x:c>
+      <x:c r="F35" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G35" s="40" t="str">
+        <x:v>c65ee97797664282f7e987860a895bc4d30d33af8d190c41aa96ba78b0f984e5</x:v>
+      </x:c>
+      <x:c r="H35" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I35" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J35" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K35" s="40" t="str">
+        <x:v>9d93b4c1b93403e1a86d719220529a9d39f053ed90bf259fce83ee86b308f17d</x:v>
+      </x:c>
+      <x:c r="L35" s="40" t="str">
+        <x:v>26a1b0106e9faf6a69101dc82c5cdc561ce615c1f63e6482191799086ff2eea6</x:v>
+      </x:c>
+      <x:c r="M35" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/IX/result.json</x:v>
+      </x:c>
+      <x:c r="N35" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A36" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B36" s="36" t="str">
+        <x:v>XI</x:v>
+      </x:c>
+      <x:c r="C36" s="36" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D36" s="36" t="str">
+        <x:v>-16517.347225468845863</x:v>
+      </x:c>
+      <x:c r="E36" s="36" t="str">
+        <x:v>-611.753600943290621</x:v>
+      </x:c>
+      <x:c r="F36" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G36" s="40" t="str">
+        <x:v>c7ebc2fbbb67b620ef93d11a03adfcb9e8f54c2604931ee36842b670d9caa4f5</x:v>
+      </x:c>
+      <x:c r="H36" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I36" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J36" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K36" s="40" t="str">
+        <x:v>81f9f34536e4f82d987b2a0e6032a33c87bc6dc7de7b0384909d35d42ee4e999</x:v>
+      </x:c>
+      <x:c r="L36" s="40" t="str">
+        <x:v>593944fe2d6f5847859d2f11a7e3deb488bde00e60547f07c95868817d66b87e</x:v>
+      </x:c>
+      <x:c r="M36" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/XI/result.json</x:v>
+      </x:c>
+      <x:c r="N36" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A37" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B37" s="36" t="str">
+        <x:v>XIII</x:v>
+      </x:c>
+      <x:c r="C37" s="36" t="str">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D37" s="36" t="str">
+        <x:v>-57801.612850758501736</x:v>
+      </x:c>
+      <x:c r="E37" s="36" t="str">
+        <x:v>-2140.800475954018566</x:v>
+      </x:c>
+      <x:c r="F37" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G37" s="40" t="str">
+        <x:v>37b1d93ec726b6e50c401f66bd1c4eca2ff9ae6073a351aedeb1d03d21cc9fd4</x:v>
+      </x:c>
+      <x:c r="H37" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I37" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J37" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K37" s="40" t="str">
+        <x:v>1cf9308d274edeb118aba8b3a79ba471e5f9abb3e020d5795bdf945fb822e610</x:v>
+      </x:c>
+      <x:c r="L37" s="40" t="str">
+        <x:v>4c7e6011d522d99b4e7af6ac830580758663ceadae43261f7c4046fd9124dc5f</x:v>
+      </x:c>
+      <x:c r="M37" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/XIII/result.json</x:v>
+      </x:c>
+      <x:c r="N37" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A38" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B38" s="36" t="str">
+        <x:v>XIV</x:v>
+      </x:c>
+      <x:c r="C38" s="36" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D38" s="36" t="str">
+        <x:v>-24777.330294619918277</x:v>
+      </x:c>
+      <x:c r="E38" s="36" t="str">
+        <x:v>-917.678899800737668</x:v>
+      </x:c>
+      <x:c r="F38" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G38" s="40" t="str">
+        <x:v>06ef5467deadd2e61959f6997effdac1b11a6d1ebe61c673d9197a79566363ab</x:v>
+      </x:c>
+      <x:c r="H38" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I38" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J38" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K38" s="40" t="str">
+        <x:v>840c2306186c3186ccf9d181cf692ce3feac8d5af846af5663623cd713d4e62e</x:v>
+      </x:c>
+      <x:c r="L38" s="40" t="str">
+        <x:v>5711936e81a854f0528de07fd00589e85ab7052ebd9bea36e8fadc3097ce3e2f</x:v>
+      </x:c>
+      <x:c r="M38" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/XIV/result.json</x:v>
+      </x:c>
+      <x:c r="N38" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A39" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B39" s="36" t="str">
+        <x:v>XV</x:v>
+      </x:c>
+      <x:c r="C39" s="36" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D39" s="36" t="str">
+        <x:v>-20644.088996855942241</x:v>
+      </x:c>
+      <x:c r="E39" s="36" t="str">
+        <x:v>-764.595888772442322</x:v>
+      </x:c>
+      <x:c r="F39" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G39" s="40" t="str">
+        <x:v>ddcea98e071c52b4125a28a8b2329840e386ca491346213bb671b6025a523c89</x:v>
+      </x:c>
+      <x:c r="H39" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I39" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J39" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K39" s="40" t="str">
+        <x:v>5f69dcaba3edba31ab66c8d8fdceb85e89f32c4fd6538dc77819d35186a705e6</x:v>
+      </x:c>
+      <x:c r="L39" s="40" t="str">
+        <x:v>f05423a7605041f4b509130b07c534c05a89eb9d3dec444ce37814ced0736598</x:v>
+      </x:c>
+      <x:c r="M39" s="40" t="str">
+        <x:v>raw/mstore_inorganic_cli/k333/XV/result.json</x:v>
+      </x:c>
+      <x:c r="N39" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A40" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B40" s="36" t="str">
+        <x:v>XVII</x:v>
+      </x:c>
+      <x:c r="C40" s="36" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D40" s="36" t="str">
+        <x:v>-12386.388372012648688</x:v>
+      </x:c>
+      <x:c r="E40" s="36" t="str">
+        <x:v>-458.755124889357376</x:v>
+      </x:c>
+      <x:c r="F40" s="40" t="str">
+        <x:v>8df9fcc990f15600f0b99316602d1d6adfad43f85a2b0203ae14aad44ad4b1aa</x:v>
+      </x:c>
+      <x:c r="G40" s="40" t="str">
+        <x:v>89506fdd1b60dcacf9184a9fc61f1dab567cf4fa9ac8d14e49045147acf12f02</x:v>
+      </x:c>
+      <x:c r="H40" s="36" t="str">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="I40" s="36" t="str">
+        <x:v>9.9999999999999995e-08</x:v>
+      </x:c>
+      <x:c r="J40" s="36" t="str">
+        <x:v>1.9999999999999999e-06</x:v>
+      </x:c>
+      <x:c r="K40" s="40" t="str">
         <x:v>0ce1101199a0faa3af2e0faf2797504098347d0024dcdf7c0fd13f93ea56db90</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="str">
+      <x:c r="L40" s="40" t="str">
         <x:v>8f7e991d824536b8b089147e2196ca0746314c34a9f32845f639ce64c2f26c07</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="str">
+      <x:c r="M40" s="40" t="str">
         <x:v>raw/mstore_inorganic_cli/k333/XVII/result.json</x:v>
       </x:c>
-      <x:c r="N27" s="36" t="str">
+      <x:c r="N40" s="36" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>

--- a/DMC-ICE13/reproduction/seidler_dmc13_recalculation/comparison_workbook.xlsx
+++ b/DMC-ICE13/reproduction/seidler_dmc13_recalculation/comparison_workbook.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R143bfb9c0f194c1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch statistics" sheetId="2" r:id="Red175082568a434f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative energies" sheetId="3" r:id="R42a0f59b0a554140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch differences" sheetId="4" r:id="Rfef6cab5e87149a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absolute parity" sheetId="5" r:id="Rda6b4d1b66c04a20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Native meshes" sheetId="6" r:id="Rdfee209259314721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mstore absolute" sheetId="7" r:id="R2a51f1bdebd24f70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="8" r:id="R76beba646cb74d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb666662d441b48b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch statistics" sheetId="2" r:id="R9c366c3a849347a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative energies" sheetId="3" r:id="R990069d02d2d4e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch differences" sheetId="4" r:id="Re562defc59124850"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Absolute parity" sheetId="5" r:id="Rbeee38ce48434b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Native meshes" sheetId="6" r:id="Ree91b4f30a4e42ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mstore absolute" sheetId="7" r:id="Rffd01ef99f3f4a1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="8" r:id="Rbae01682e9314cdc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -524,7 +524,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0d786a217f1641c7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R13a613f211174a69"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1079,7 +1079,7 @@
     <x:mergeCell ref="A24:E24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1baf0f69a85426e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89d0416fc1d14cdb"/>
 </x:worksheet>
 </file>
 
@@ -3586,19 +3586,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C82" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D82" s="42" t="str">
-        <x:v>0.090455358961</x:v>
+        <x:v>0.508805411655</x:v>
       </x:c>
       <x:c r="E82" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F82" s="42" t="str">
-        <x:v>-1.609544641039</x:v>
+        <x:v>0.348805411655</x:v>
       </x:c>
       <x:c r="G82" s="42" t="str">
-        <x:v>1.609544641039</x:v>
+        <x:v>0.348805411655</x:v>
       </x:c>
       <x:c r="H82" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3606,25 +3606,25 @@
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="36" t="str">
-        <x:v>author pbc CLI</x:v>
+        <x:v>CP2K-native pbc provider</x:v>
       </x:c>
       <x:c r="B83" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C83" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D83" s="42" t="str">
-        <x:v>-40.056162616318</x:v>
+        <x:v>0.090455358961</x:v>
       </x:c>
       <x:c r="E83" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F83" s="42" t="str">
-        <x:v>-40.366162616318</x:v>
+        <x:v>-1.609544641039</x:v>
       </x:c>
       <x:c r="G83" s="42" t="str">
-        <x:v>40.366162616318</x:v>
+        <x:v>1.609544641039</x:v>
       </x:c>
       <x:c r="H83" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3638,19 +3638,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C84" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D84" s="42" t="str">
-        <x:v>-21.728016057439</x:v>
+        <x:v>-40.056162616318</x:v>
       </x:c>
       <x:c r="E84" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F84" s="42" t="str">
-        <x:v>-22.978016057439</x:v>
+        <x:v>-40.366162616318</x:v>
       </x:c>
       <x:c r="G84" s="42" t="str">
-        <x:v>22.978016057439</x:v>
+        <x:v>40.366162616318</x:v>
       </x:c>
       <x:c r="H84" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3664,19 +3664,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C85" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D85" s="42" t="str">
-        <x:v>14.909575775296</x:v>
+        <x:v>-21.728016057439</x:v>
       </x:c>
       <x:c r="E85" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F85" s="42" t="str">
-        <x:v>11.079575775296</x:v>
+        <x:v>-22.978016057439</x:v>
       </x:c>
       <x:c r="G85" s="42" t="str">
-        <x:v>11.079575775296</x:v>
+        <x:v>22.978016057439</x:v>
       </x:c>
       <x:c r="H85" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3690,19 +3690,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C86" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D86" s="42" t="str">
-        <x:v>-57.502753280215</x:v>
+        <x:v>14.909575775296</x:v>
       </x:c>
       <x:c r="E86" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F86" s="42" t="str">
-        <x:v>-59.282753280215</x:v>
+        <x:v>11.079575775296</x:v>
       </x:c>
       <x:c r="G86" s="42" t="str">
-        <x:v>59.282753280215</x:v>
+        <x:v>11.079575775296</x:v>
       </x:c>
       <x:c r="H86" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3716,19 +3716,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C87" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D87" s="42" t="str">
-        <x:v>-300.067320161804</x:v>
+        <x:v>-57.502753280215</x:v>
       </x:c>
       <x:c r="E87" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F87" s="42" t="str">
-        <x:v>-305.057320161804</x:v>
+        <x:v>-59.282753280215</x:v>
       </x:c>
       <x:c r="G87" s="42" t="str">
-        <x:v>305.057320161804</x:v>
+        <x:v>59.282753280215</x:v>
       </x:c>
       <x:c r="H87" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3742,19 +3742,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C88" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D88" s="42" t="str">
-        <x:v>-121.498882525679</x:v>
+        <x:v>-300.067320161804</x:v>
       </x:c>
       <x:c r="E88" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F88" s="42" t="str">
-        <x:v>-125.728882525679</x:v>
+        <x:v>-305.057320161804</x:v>
       </x:c>
       <x:c r="G88" s="42" t="str">
-        <x:v>125.728882525679</x:v>
+        <x:v>305.057320161804</x:v>
       </x:c>
       <x:c r="H88" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3768,19 +3768,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C89" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D89" s="42" t="str">
-        <x:v>-14.812836787859</x:v>
+        <x:v>-121.498882525679</x:v>
       </x:c>
       <x:c r="E89" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F89" s="42" t="str">
-        <x:v>-15.412836787859</x:v>
+        <x:v>-125.728882525679</x:v>
       </x:c>
       <x:c r="G89" s="42" t="str">
-        <x:v>15.412836787859</x:v>
+        <x:v>125.728882525679</x:v>
       </x:c>
       <x:c r="H89" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3794,19 +3794,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C90" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D90" s="42" t="str">
-        <x:v>-165.257377908596</x:v>
+        <x:v>-14.812836787859</x:v>
       </x:c>
       <x:c r="E90" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F90" s="42" t="str">
-        <x:v>-165.417377908596</x:v>
+        <x:v>-15.412836787859</x:v>
       </x:c>
       <x:c r="G90" s="42" t="str">
-        <x:v>165.417377908596</x:v>
+        <x:v>15.412836787859</x:v>
       </x:c>
       <x:c r="H90" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3820,19 +3820,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C91" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D91" s="42" t="str">
-        <x:v>6.868364020212</x:v>
+        <x:v>-165.257377908596</x:v>
       </x:c>
       <x:c r="E91" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F91" s="42" t="str">
-        <x:v>4.748364020212</x:v>
+        <x:v>-165.417377908596</x:v>
       </x:c>
       <x:c r="G91" s="42" t="str">
-        <x:v>4.748364020212</x:v>
+        <x:v>165.417377908596</x:v>
       </x:c>
       <x:c r="H91" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3846,19 +3846,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C92" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D92" s="42" t="str">
-        <x:v>-199.611684777200</x:v>
+        <x:v>6.868364020212</x:v>
       </x:c>
       <x:c r="E92" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F92" s="42" t="str">
-        <x:v>-201.311684777200</x:v>
+        <x:v>4.748364020212</x:v>
       </x:c>
       <x:c r="G92" s="42" t="str">
-        <x:v>201.311684777200</x:v>
+        <x:v>4.748364020212</x:v>
       </x:c>
       <x:c r="H92" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3872,19 +3872,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C93" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D93" s="42" t="str">
-        <x:v>-58.050293332028</x:v>
+        <x:v>-199.611684777200</x:v>
       </x:c>
       <x:c r="E93" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F93" s="42" t="str">
-        <x:v>-59.790293332028</x:v>
+        <x:v>-201.311684777200</x:v>
       </x:c>
       <x:c r="G93" s="42" t="str">
-        <x:v>59.790293332028</x:v>
+        <x:v>201.311684777200</x:v>
       </x:c>
       <x:c r="H93" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3898,19 +3898,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C94" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D94" s="42" t="str">
-        <x:v>-51.559121420866</x:v>
+        <x:v>-58.050293332028</x:v>
       </x:c>
       <x:c r="E94" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F94" s="42" t="str">
-        <x:v>-53.309121420866</x:v>
+        <x:v>-59.790293332028</x:v>
       </x:c>
       <x:c r="G94" s="42" t="str">
-        <x:v>53.309121420866</x:v>
+        <x:v>59.790293332028</x:v>
       </x:c>
       <x:c r="H94" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3921,22 +3921,22 @@
         <x:v>author pbc CLI</x:v>
       </x:c>
       <x:c r="B95" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C95" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D95" s="42" t="str">
-        <x:v>-9.054674468559</x:v>
+        <x:v>-51.559121420866</x:v>
       </x:c>
       <x:c r="E95" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F95" s="42" t="str">
-        <x:v>-9.364674468559</x:v>
+        <x:v>-53.309121420866</x:v>
       </x:c>
       <x:c r="G95" s="42" t="str">
-        <x:v>9.364674468559</x:v>
+        <x:v>53.309121420866</x:v>
       </x:c>
       <x:c r="H95" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3950,19 +3950,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C96" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D96" s="42" t="str">
-        <x:v>-2.341718734421</x:v>
+        <x:v>-9.054674468559</x:v>
       </x:c>
       <x:c r="E96" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F96" s="42" t="str">
-        <x:v>-3.591718734421</x:v>
+        <x:v>-9.364674468559</x:v>
       </x:c>
       <x:c r="G96" s="42" t="str">
-        <x:v>3.591718734421</x:v>
+        <x:v>9.364674468559</x:v>
       </x:c>
       <x:c r="H96" s="36" t="str">
         <x:v>PASS</x:v>
@@ -3976,19 +3976,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C97" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D97" s="42" t="str">
-        <x:v>2.892295286943</x:v>
+        <x:v>-2.341718734421</x:v>
       </x:c>
       <x:c r="E97" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F97" s="42" t="str">
-        <x:v>-0.937704713057</x:v>
+        <x:v>-3.591718734421</x:v>
       </x:c>
       <x:c r="G97" s="42" t="str">
-        <x:v>0.937704713057</x:v>
+        <x:v>3.591718734421</x:v>
       </x:c>
       <x:c r="H97" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4002,19 +4002,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C98" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D98" s="42" t="str">
-        <x:v>-12.421511801622</x:v>
+        <x:v>2.892295286943</x:v>
       </x:c>
       <x:c r="E98" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F98" s="42" t="str">
-        <x:v>-14.201511801622</x:v>
+        <x:v>-0.937704713057</x:v>
       </x:c>
       <x:c r="G98" s="42" t="str">
-        <x:v>14.201511801622</x:v>
+        <x:v>0.937704713057</x:v>
       </x:c>
       <x:c r="H98" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4028,19 +4028,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C99" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D99" s="42" t="str">
-        <x:v>-153.975297576434</x:v>
+        <x:v>-12.421511801622</x:v>
       </x:c>
       <x:c r="E99" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F99" s="42" t="str">
-        <x:v>-158.965297576434</x:v>
+        <x:v>-14.201511801622</x:v>
       </x:c>
       <x:c r="G99" s="42" t="str">
-        <x:v>158.965297576434</x:v>
+        <x:v>14.201511801622</x:v>
       </x:c>
       <x:c r="H99" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4054,19 +4054,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C100" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D100" s="42" t="str">
-        <x:v>-38.490190110106</x:v>
+        <x:v>-153.975297576434</x:v>
       </x:c>
       <x:c r="E100" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F100" s="42" t="str">
-        <x:v>-42.720190110106</x:v>
+        <x:v>-158.965297576434</x:v>
       </x:c>
       <x:c r="G100" s="42" t="str">
-        <x:v>42.720190110106</x:v>
+        <x:v>158.965297576434</x:v>
       </x:c>
       <x:c r="H100" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4080,19 +4080,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C101" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D101" s="42" t="str">
-        <x:v>-2.462552657305</x:v>
+        <x:v>-38.490190110106</x:v>
       </x:c>
       <x:c r="E101" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F101" s="42" t="str">
-        <x:v>-3.062552657305</x:v>
+        <x:v>-42.720190110106</x:v>
       </x:c>
       <x:c r="G101" s="42" t="str">
-        <x:v>3.062552657305</x:v>
+        <x:v>42.720190110106</x:v>
       </x:c>
       <x:c r="H101" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4106,19 +4106,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C102" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D102" s="42" t="str">
-        <x:v>-62.538655042867</x:v>
+        <x:v>-2.462552657305</x:v>
       </x:c>
       <x:c r="E102" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F102" s="42" t="str">
-        <x:v>-62.698655042867</x:v>
+        <x:v>-3.062552657305</x:v>
       </x:c>
       <x:c r="G102" s="42" t="str">
-        <x:v>62.698655042867</x:v>
+        <x:v>3.062552657305</x:v>
       </x:c>
       <x:c r="H102" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4132,19 +4132,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C103" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D103" s="42" t="str">
-        <x:v>0.923689537732</x:v>
+        <x:v>-62.538655042867</x:v>
       </x:c>
       <x:c r="E103" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F103" s="42" t="str">
-        <x:v>-1.196310462268</x:v>
+        <x:v>-62.698655042867</x:v>
       </x:c>
       <x:c r="G103" s="42" t="str">
-        <x:v>1.196310462268</x:v>
+        <x:v>62.698655042867</x:v>
       </x:c>
       <x:c r="H103" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4158,19 +4158,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C104" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D104" s="42" t="str">
-        <x:v>-83.903026598902</x:v>
+        <x:v>0.923689537732</x:v>
       </x:c>
       <x:c r="E104" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F104" s="42" t="str">
-        <x:v>-85.603026598902</x:v>
+        <x:v>-1.196310462268</x:v>
       </x:c>
       <x:c r="G104" s="42" t="str">
-        <x:v>85.603026598902</x:v>
+        <x:v>1.196310462268</x:v>
       </x:c>
       <x:c r="H104" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4184,19 +4184,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C105" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D105" s="42" t="str">
-        <x:v>-12.548998010281</x:v>
+        <x:v>-83.903026598902</x:v>
       </x:c>
       <x:c r="E105" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F105" s="42" t="str">
-        <x:v>-14.288998010281</x:v>
+        <x:v>-85.603026598902</x:v>
       </x:c>
       <x:c r="G105" s="42" t="str">
-        <x:v>14.288998010281</x:v>
+        <x:v>85.603026598902</x:v>
       </x:c>
       <x:c r="H105" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4210,19 +4210,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C106" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D106" s="42" t="str">
-        <x:v>-10.466416914384</x:v>
+        <x:v>-12.548998010281</x:v>
       </x:c>
       <x:c r="E106" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F106" s="42" t="str">
-        <x:v>-12.216416914384</x:v>
+        <x:v>-14.288998010281</x:v>
       </x:c>
       <x:c r="G106" s="42" t="str">
-        <x:v>12.216416914384</x:v>
+        <x:v>14.288998010281</x:v>
       </x:c>
       <x:c r="H106" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4230,25 +4230,25 @@
     </x:row>
     <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="36" t="str">
-        <x:v>current pbc CLI</x:v>
+        <x:v>author pbc CLI</x:v>
       </x:c>
       <x:c r="B107" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C107" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D107" s="42" t="str">
-        <x:v>-85.402832480791</x:v>
+        <x:v>-10.466416914384</x:v>
       </x:c>
       <x:c r="E107" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F107" s="42" t="str">
-        <x:v>-85.712832480791</x:v>
+        <x:v>-12.216416914384</x:v>
       </x:c>
       <x:c r="G107" s="42" t="str">
-        <x:v>85.712832480791</x:v>
+        <x:v>12.216416914384</x:v>
       </x:c>
       <x:c r="H107" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4262,19 +4262,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C108" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D108" s="42" t="str">
-        <x:v>-52.784771448006</x:v>
+        <x:v>-85.402832480791</x:v>
       </x:c>
       <x:c r="E108" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F108" s="42" t="str">
-        <x:v>-54.034771448006</x:v>
+        <x:v>-85.712832480791</x:v>
       </x:c>
       <x:c r="G108" s="42" t="str">
-        <x:v>54.034771448006</x:v>
+        <x:v>85.712832480791</x:v>
       </x:c>
       <x:c r="H108" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4288,19 +4288,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C109" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D109" s="42" t="str">
-        <x:v>38.666296487481</x:v>
+        <x:v>-52.784771448006</x:v>
       </x:c>
       <x:c r="E109" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F109" s="42" t="str">
-        <x:v>34.836296487481</x:v>
+        <x:v>-54.034771448006</x:v>
       </x:c>
       <x:c r="G109" s="42" t="str">
-        <x:v>34.836296487481</x:v>
+        <x:v>54.034771448006</x:v>
       </x:c>
       <x:c r="H109" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4314,19 +4314,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C110" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D110" s="42" t="str">
-        <x:v>-119.951876462899</x:v>
+        <x:v>38.666296487481</x:v>
       </x:c>
       <x:c r="E110" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F110" s="42" t="str">
-        <x:v>-121.731876462899</x:v>
+        <x:v>34.836296487481</x:v>
       </x:c>
       <x:c r="G110" s="42" t="str">
-        <x:v>121.731876462899</x:v>
+        <x:v>34.836296487481</x:v>
       </x:c>
       <x:c r="H110" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4340,19 +4340,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C111" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D111" s="42" t="str">
-        <x:v>-491.873083815613</x:v>
+        <x:v>-119.951876462899</x:v>
       </x:c>
       <x:c r="E111" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F111" s="42" t="str">
-        <x:v>-496.863083815613</x:v>
+        <x:v>-121.731876462899</x:v>
       </x:c>
       <x:c r="G111" s="42" t="str">
-        <x:v>496.863083815613</x:v>
+        <x:v>121.731876462899</x:v>
       </x:c>
       <x:c r="H111" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4366,19 +4366,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C112" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D112" s="42" t="str">
-        <x:v>-227.181421040355</x:v>
+        <x:v>-491.873083815613</x:v>
       </x:c>
       <x:c r="E112" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F112" s="42" t="str">
-        <x:v>-231.411421040355</x:v>
+        <x:v>-496.863083815613</x:v>
       </x:c>
       <x:c r="G112" s="42" t="str">
-        <x:v>231.411421040355</x:v>
+        <x:v>496.863083815613</x:v>
       </x:c>
       <x:c r="H112" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4392,19 +4392,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C113" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D113" s="42" t="str">
-        <x:v>-36.269951925783</x:v>
+        <x:v>-227.181421040355</x:v>
       </x:c>
       <x:c r="E113" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F113" s="42" t="str">
-        <x:v>-36.869951925783</x:v>
+        <x:v>-231.411421040355</x:v>
       </x:c>
       <x:c r="G113" s="42" t="str">
-        <x:v>36.869951925783</x:v>
+        <x:v>231.411421040355</x:v>
       </x:c>
       <x:c r="H113" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4418,19 +4418,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C114" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D114" s="42" t="str">
-        <x:v>-299.258518836626</x:v>
+        <x:v>-36.269951925783</x:v>
       </x:c>
       <x:c r="E114" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F114" s="42" t="str">
-        <x:v>-299.418518836626</x:v>
+        <x:v>-36.869951925783</x:v>
       </x:c>
       <x:c r="G114" s="42" t="str">
-        <x:v>299.418518836626</x:v>
+        <x:v>36.869951925783</x:v>
       </x:c>
       <x:c r="H114" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4444,19 +4444,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C115" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D115" s="42" t="str">
-        <x:v>16.464730608559</x:v>
+        <x:v>-299.258518836626</x:v>
       </x:c>
       <x:c r="E115" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F115" s="42" t="str">
-        <x:v>14.344730608559</x:v>
+        <x:v>-299.418518836626</x:v>
       </x:c>
       <x:c r="G115" s="42" t="str">
-        <x:v>14.344730608559</x:v>
+        <x:v>299.418518836626</x:v>
       </x:c>
       <x:c r="H115" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4470,19 +4470,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C116" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D116" s="42" t="str">
-        <x:v>-351.956576532881</x:v>
+        <x:v>16.464730608559</x:v>
       </x:c>
       <x:c r="E116" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F116" s="42" t="str">
-        <x:v>-353.656576532881</x:v>
+        <x:v>14.344730608559</x:v>
       </x:c>
       <x:c r="G116" s="42" t="str">
-        <x:v>353.656576532881</x:v>
+        <x:v>14.344730608559</x:v>
       </x:c>
       <x:c r="H116" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4496,19 +4496,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C117" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D117" s="42" t="str">
-        <x:v>-121.156628176656</x:v>
+        <x:v>-351.956576532881</x:v>
       </x:c>
       <x:c r="E117" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F117" s="42" t="str">
-        <x:v>-122.896628176656</x:v>
+        <x:v>-353.656576532881</x:v>
       </x:c>
       <x:c r="G117" s="42" t="str">
-        <x:v>122.896628176656</x:v>
+        <x:v>353.656576532881</x:v>
       </x:c>
       <x:c r="H117" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4522,19 +4522,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C118" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D118" s="42" t="str">
-        <x:v>-112.486904450047</x:v>
+        <x:v>-121.156628176656</x:v>
       </x:c>
       <x:c r="E118" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F118" s="42" t="str">
-        <x:v>-114.236904450047</x:v>
+        <x:v>-122.896628176656</x:v>
       </x:c>
       <x:c r="G118" s="42" t="str">
-        <x:v>114.236904450047</x:v>
+        <x:v>122.896628176656</x:v>
       </x:c>
       <x:c r="H118" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4545,22 +4545,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B119" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C119" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D119" s="42" t="str">
-        <x:v>-40.052769548562</x:v>
+        <x:v>-112.486904450047</x:v>
       </x:c>
       <x:c r="E119" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F119" s="42" t="str">
-        <x:v>-40.362769548562</x:v>
+        <x:v>-114.236904450047</x:v>
       </x:c>
       <x:c r="G119" s="42" t="str">
-        <x:v>40.362769548562</x:v>
+        <x:v>114.236904450047</x:v>
       </x:c>
       <x:c r="H119" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4574,19 +4574,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C120" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D120" s="42" t="str">
-        <x:v>-21.669458368756</x:v>
+        <x:v>-40.052769548562</x:v>
       </x:c>
       <x:c r="E120" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F120" s="42" t="str">
-        <x:v>-22.919458368756</x:v>
+        <x:v>-40.362769548562</x:v>
       </x:c>
       <x:c r="G120" s="42" t="str">
-        <x:v>22.919458368756</x:v>
+        <x:v>40.362769548562</x:v>
       </x:c>
       <x:c r="H120" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4600,19 +4600,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C121" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D121" s="42" t="str">
-        <x:v>14.926647908813</x:v>
+        <x:v>-21.669458368756</x:v>
       </x:c>
       <x:c r="E121" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F121" s="42" t="str">
-        <x:v>11.096647908813</x:v>
+        <x:v>-22.919458368756</x:v>
       </x:c>
       <x:c r="G121" s="42" t="str">
-        <x:v>11.096647908813</x:v>
+        <x:v>22.919458368756</x:v>
       </x:c>
       <x:c r="H121" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4626,19 +4626,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C122" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D122" s="42" t="str">
-        <x:v>-57.367276074495</x:v>
+        <x:v>14.926647908813</x:v>
       </x:c>
       <x:c r="E122" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F122" s="42" t="str">
-        <x:v>-59.147276074495</x:v>
+        <x:v>11.096647908813</x:v>
       </x:c>
       <x:c r="G122" s="42" t="str">
-        <x:v>59.147276074495</x:v>
+        <x:v>11.096647908813</x:v>
       </x:c>
       <x:c r="H122" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4652,19 +4652,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C123" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D123" s="42" t="str">
-        <x:v>-299.975204903283</x:v>
+        <x:v>-57.367276074495</x:v>
       </x:c>
       <x:c r="E123" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F123" s="42" t="str">
-        <x:v>-304.965204903283</x:v>
+        <x:v>-59.147276074495</x:v>
       </x:c>
       <x:c r="G123" s="42" t="str">
-        <x:v>304.965204903283</x:v>
+        <x:v>59.147276074495</x:v>
       </x:c>
       <x:c r="H123" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4678,19 +4678,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C124" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D124" s="42" t="str">
-        <x:v>-121.493623038083</x:v>
+        <x:v>-299.975204903283</x:v>
       </x:c>
       <x:c r="E124" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F124" s="42" t="str">
-        <x:v>-125.723623038083</x:v>
+        <x:v>-304.965204903283</x:v>
       </x:c>
       <x:c r="G124" s="42" t="str">
-        <x:v>125.723623038083</x:v>
+        <x:v>304.965204903283</x:v>
       </x:c>
       <x:c r="H124" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4704,19 +4704,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C125" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D125" s="42" t="str">
-        <x:v>-14.811033266160</x:v>
+        <x:v>-121.493623038083</x:v>
       </x:c>
       <x:c r="E125" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F125" s="42" t="str">
-        <x:v>-15.411033266160</x:v>
+        <x:v>-125.723623038083</x:v>
       </x:c>
       <x:c r="G125" s="42" t="str">
-        <x:v>15.411033266160</x:v>
+        <x:v>125.723623038083</x:v>
       </x:c>
       <x:c r="H125" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4730,19 +4730,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C126" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D126" s="42" t="str">
-        <x:v>-165.236809268426</x:v>
+        <x:v>-14.811033266160</x:v>
       </x:c>
       <x:c r="E126" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F126" s="42" t="str">
-        <x:v>-165.396809268426</x:v>
+        <x:v>-15.411033266160</x:v>
       </x:c>
       <x:c r="G126" s="42" t="str">
-        <x:v>165.396809268426</x:v>
+        <x:v>15.411033266160</x:v>
       </x:c>
       <x:c r="H126" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4756,19 +4756,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C127" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D127" s="42" t="str">
-        <x:v>6.872357662713</x:v>
+        <x:v>-165.236809268426</x:v>
       </x:c>
       <x:c r="E127" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F127" s="42" t="str">
-        <x:v>4.752357662713</x:v>
+        <x:v>-165.396809268426</x:v>
       </x:c>
       <x:c r="G127" s="42" t="str">
-        <x:v>4.752357662713</x:v>
+        <x:v>165.396809268426</x:v>
       </x:c>
       <x:c r="H127" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4782,19 +4782,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C128" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D128" s="42" t="str">
-        <x:v>-199.607041791688</x:v>
+        <x:v>6.872357662713</x:v>
       </x:c>
       <x:c r="E128" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F128" s="42" t="str">
-        <x:v>-201.307041791688</x:v>
+        <x:v>4.752357662713</x:v>
       </x:c>
       <x:c r="G128" s="42" t="str">
-        <x:v>201.307041791688</x:v>
+        <x:v>4.752357662713</x:v>
       </x:c>
       <x:c r="H128" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4808,19 +4808,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C129" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D129" s="42" t="str">
-        <x:v>-58.045564075785</x:v>
+        <x:v>-199.607041791688</x:v>
       </x:c>
       <x:c r="E129" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F129" s="42" t="str">
-        <x:v>-59.785564075785</x:v>
+        <x:v>-201.307041791688</x:v>
       </x:c>
       <x:c r="G129" s="42" t="str">
-        <x:v>59.785564075785</x:v>
+        <x:v>201.307041791688</x:v>
       </x:c>
       <x:c r="H129" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4834,19 +4834,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C130" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D130" s="42" t="str">
-        <x:v>-51.558720983607</x:v>
+        <x:v>-58.045564075785</x:v>
       </x:c>
       <x:c r="E130" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F130" s="42" t="str">
-        <x:v>-53.308720983607</x:v>
+        <x:v>-59.785564075785</x:v>
       </x:c>
       <x:c r="G130" s="42" t="str">
-        <x:v>53.308720983607</x:v>
+        <x:v>59.785564075785</x:v>
       </x:c>
       <x:c r="H130" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4857,22 +4857,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B131" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C131" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D131" s="42" t="str">
-        <x:v>-9.052128552229</x:v>
+        <x:v>-51.558720983607</x:v>
       </x:c>
       <x:c r="E131" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F131" s="42" t="str">
-        <x:v>-9.362128552229</x:v>
+        <x:v>-53.308720983607</x:v>
       </x:c>
       <x:c r="G131" s="42" t="str">
-        <x:v>9.362128552229</x:v>
+        <x:v>53.308720983607</x:v>
       </x:c>
       <x:c r="H131" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4886,19 +4886,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C132" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D132" s="42" t="str">
-        <x:v>-2.299617048110</x:v>
+        <x:v>-9.052128552229</x:v>
       </x:c>
       <x:c r="E132" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F132" s="42" t="str">
-        <x:v>-3.549617048110</x:v>
+        <x:v>-9.362128552229</x:v>
       </x:c>
       <x:c r="G132" s="42" t="str">
-        <x:v>3.549617048110</x:v>
+        <x:v>9.362128552229</x:v>
       </x:c>
       <x:c r="H132" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4912,19 +4912,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C133" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D133" s="42" t="str">
-        <x:v>2.904340310370</x:v>
+        <x:v>-2.299617048110</x:v>
       </x:c>
       <x:c r="E133" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F133" s="42" t="str">
-        <x:v>-0.925659689630</x:v>
+        <x:v>-3.549617048110</x:v>
       </x:c>
       <x:c r="G133" s="42" t="str">
-        <x:v>0.925659689630</x:v>
+        <x:v>3.549617048110</x:v>
       </x:c>
       <x:c r="H133" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4938,19 +4938,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C134" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D134" s="42" t="str">
-        <x:v>-12.321031303355</x:v>
+        <x:v>2.904340310370</x:v>
       </x:c>
       <x:c r="E134" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F134" s="42" t="str">
-        <x:v>-14.101031303355</x:v>
+        <x:v>-0.925659689630</x:v>
       </x:c>
       <x:c r="G134" s="42" t="str">
-        <x:v>14.101031303355</x:v>
+        <x:v>0.925659689630</x:v>
       </x:c>
       <x:c r="H134" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4964,19 +4964,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C135" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D135" s="42" t="str">
-        <x:v>-153.898129900577</x:v>
+        <x:v>-12.321031303355</x:v>
       </x:c>
       <x:c r="E135" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F135" s="42" t="str">
-        <x:v>-158.888129900577</x:v>
+        <x:v>-14.101031303355</x:v>
       </x:c>
       <x:c r="G135" s="42" t="str">
-        <x:v>158.888129900577</x:v>
+        <x:v>14.101031303355</x:v>
       </x:c>
       <x:c r="H135" s="36" t="str">
         <x:v>PASS</x:v>
@@ -4990,19 +4990,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C136" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D136" s="42" t="str">
-        <x:v>-38.486266197120</x:v>
+        <x:v>-153.898129900577</x:v>
       </x:c>
       <x:c r="E136" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F136" s="42" t="str">
-        <x:v>-42.716266197120</x:v>
+        <x:v>-158.888129900577</x:v>
       </x:c>
       <x:c r="G136" s="42" t="str">
-        <x:v>42.716266197120</x:v>
+        <x:v>158.888129900577</x:v>
       </x:c>
       <x:c r="H136" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5016,19 +5016,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C137" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D137" s="42" t="str">
-        <x:v>-2.461004071112</x:v>
+        <x:v>-38.486266197120</x:v>
       </x:c>
       <x:c r="E137" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F137" s="42" t="str">
-        <x:v>-3.061004071112</x:v>
+        <x:v>-42.716266197120</x:v>
       </x:c>
       <x:c r="G137" s="42" t="str">
-        <x:v>3.061004071112</x:v>
+        <x:v>42.716266197120</x:v>
       </x:c>
       <x:c r="H137" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5042,19 +5042,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C138" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D138" s="42" t="str">
-        <x:v>-62.523175264048</x:v>
+        <x:v>-2.461004071112</x:v>
       </x:c>
       <x:c r="E138" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F138" s="42" t="str">
-        <x:v>-62.683175264048</x:v>
+        <x:v>-3.061004071112</x:v>
       </x:c>
       <x:c r="G138" s="42" t="str">
-        <x:v>62.683175264048</x:v>
+        <x:v>3.061004071112</x:v>
       </x:c>
       <x:c r="H138" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5068,19 +5068,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C139" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D139" s="42" t="str">
-        <x:v>0.926723486584</x:v>
+        <x:v>-62.523175264048</x:v>
       </x:c>
       <x:c r="E139" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F139" s="42" t="str">
-        <x:v>-1.193276513416</x:v>
+        <x:v>-62.683175264048</x:v>
       </x:c>
       <x:c r="G139" s="42" t="str">
-        <x:v>1.193276513416</x:v>
+        <x:v>62.683175264048</x:v>
       </x:c>
       <x:c r="H139" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5094,19 +5094,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C140" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D140" s="42" t="str">
-        <x:v>-83.899718986935</x:v>
+        <x:v>0.926723486584</x:v>
       </x:c>
       <x:c r="E140" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F140" s="42" t="str">
-        <x:v>-85.599718986935</x:v>
+        <x:v>-1.193276513416</x:v>
       </x:c>
       <x:c r="G140" s="42" t="str">
-        <x:v>85.599718986935</x:v>
+        <x:v>1.193276513416</x:v>
       </x:c>
       <x:c r="H140" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5120,19 +5120,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C141" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D141" s="42" t="str">
-        <x:v>-12.545503073689</x:v>
+        <x:v>-83.899718986935</x:v>
       </x:c>
       <x:c r="E141" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F141" s="42" t="str">
-        <x:v>-14.285503073689</x:v>
+        <x:v>-85.599718986935</x:v>
       </x:c>
       <x:c r="G141" s="42" t="str">
-        <x:v>14.285503073689</x:v>
+        <x:v>85.599718986935</x:v>
       </x:c>
       <x:c r="H141" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5146,19 +5146,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C142" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D142" s="42" t="str">
-        <x:v>-10.466391957817</x:v>
+        <x:v>-12.545503073689</x:v>
       </x:c>
       <x:c r="E142" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F142" s="42" t="str">
-        <x:v>-12.216391957817</x:v>
+        <x:v>-14.285503073689</x:v>
       </x:c>
       <x:c r="G142" s="42" t="str">
-        <x:v>12.216391957817</x:v>
+        <x:v>14.285503073689</x:v>
       </x:c>
       <x:c r="H142" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5169,22 +5169,22 @@
         <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B143" s="36" t="str">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C143" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D143" s="42" t="str">
-        <x:v>-2.513150603252</x:v>
+        <x:v>-10.466391957817</x:v>
       </x:c>
       <x:c r="E143" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F143" s="42" t="str">
-        <x:v>-2.823150603252</x:v>
+        <x:v>-12.216391957817</x:v>
       </x:c>
       <x:c r="G143" s="42" t="str">
-        <x:v>2.823150603252</x:v>
+        <x:v>12.216391957817</x:v>
       </x:c>
       <x:c r="H143" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5198,19 +5198,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C144" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D144" s="42" t="str">
-        <x:v>1.264029937698</x:v>
+        <x:v>-2.513150603252</x:v>
       </x:c>
       <x:c r="E144" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F144" s="42" t="str">
-        <x:v>0.014029937698</x:v>
+        <x:v>-2.823150603252</x:v>
       </x:c>
       <x:c r="G144" s="42" t="str">
-        <x:v>0.014029937698</x:v>
+        <x:v>2.823150603252</x:v>
       </x:c>
       <x:c r="H144" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5224,19 +5224,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C145" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D145" s="42" t="str">
-        <x:v>1.405712159485</x:v>
+        <x:v>1.264029937698</x:v>
       </x:c>
       <x:c r="E145" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F145" s="42" t="str">
-        <x:v>-2.424287840515</x:v>
+        <x:v>0.014029937698</x:v>
       </x:c>
       <x:c r="G145" s="42" t="str">
-        <x:v>2.424287840515</x:v>
+        <x:v>0.014029937698</x:v>
       </x:c>
       <x:c r="H145" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5250,19 +5250,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C146" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D146" s="42" t="str">
-        <x:v>-1.048061577331</x:v>
+        <x:v>1.405712159485</x:v>
       </x:c>
       <x:c r="E146" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F146" s="42" t="str">
-        <x:v>-2.828061577331</x:v>
+        <x:v>-2.424287840515</x:v>
       </x:c>
       <x:c r="G146" s="42" t="str">
-        <x:v>2.828061577331</x:v>
+        <x:v>2.424287840515</x:v>
       </x:c>
       <x:c r="H146" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5276,19 +5276,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C147" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D147" s="42" t="str">
-        <x:v>-63.955235096392</x:v>
+        <x:v>-1.048061577331</x:v>
       </x:c>
       <x:c r="E147" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F147" s="42" t="str">
-        <x:v>-68.945235096392</x:v>
+        <x:v>-2.828061577331</x:v>
       </x:c>
       <x:c r="G147" s="42" t="str">
-        <x:v>68.945235096392</x:v>
+        <x:v>2.828061577331</x:v>
       </x:c>
       <x:c r="H147" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5302,19 +5302,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C148" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D148" s="42" t="str">
-        <x:v>-6.163484047291</x:v>
+        <x:v>-63.955235096392</x:v>
       </x:c>
       <x:c r="E148" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F148" s="42" t="str">
-        <x:v>-10.393484047291</x:v>
+        <x:v>-68.945235096392</x:v>
       </x:c>
       <x:c r="G148" s="42" t="str">
-        <x:v>10.393484047291</x:v>
+        <x:v>68.945235096392</x:v>
       </x:c>
       <x:c r="H148" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5328,19 +5328,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C149" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D149" s="42" t="str">
-        <x:v>-0.372876272237</x:v>
+        <x:v>-6.163484047291</x:v>
       </x:c>
       <x:c r="E149" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F149" s="42" t="str">
-        <x:v>-0.972876272237</x:v>
+        <x:v>-10.393484047291</x:v>
       </x:c>
       <x:c r="G149" s="42" t="str">
-        <x:v>0.972876272237</x:v>
+        <x:v>10.393484047291</x:v>
       </x:c>
       <x:c r="H149" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5354,19 +5354,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C150" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D150" s="42" t="str">
-        <x:v>-14.875013200229</x:v>
+        <x:v>-0.372876272237</x:v>
       </x:c>
       <x:c r="E150" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F150" s="42" t="str">
-        <x:v>-15.035013200229</x:v>
+        <x:v>-0.972876272237</x:v>
       </x:c>
       <x:c r="G150" s="42" t="str">
-        <x:v>15.035013200229</x:v>
+        <x:v>0.972876272237</x:v>
       </x:c>
       <x:c r="H150" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5380,19 +5380,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C151" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D151" s="42" t="str">
-        <x:v>0.123061371006</x:v>
+        <x:v>-14.875013200229</x:v>
       </x:c>
       <x:c r="E151" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F151" s="42" t="str">
-        <x:v>-1.996938628994</x:v>
+        <x:v>-15.035013200229</x:v>
       </x:c>
       <x:c r="G151" s="42" t="str">
-        <x:v>1.996938628994</x:v>
+        <x:v>15.035013200229</x:v>
       </x:c>
       <x:c r="H151" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5406,19 +5406,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C152" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D152" s="42" t="str">
-        <x:v>-23.938106879109</x:v>
+        <x:v>0.123061371006</x:v>
       </x:c>
       <x:c r="E152" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F152" s="42" t="str">
-        <x:v>-25.638106879109</x:v>
+        <x:v>-1.996938628994</x:v>
       </x:c>
       <x:c r="G152" s="42" t="str">
-        <x:v>25.638106879109</x:v>
+        <x:v>1.996938628994</x:v>
       </x:c>
       <x:c r="H152" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5432,19 +5432,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C153" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D153" s="42" t="str">
-        <x:v>-1.097393985422</x:v>
+        <x:v>-23.938106879109</x:v>
       </x:c>
       <x:c r="E153" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F153" s="42" t="str">
-        <x:v>-2.837393985422</x:v>
+        <x:v>-25.638106879109</x:v>
       </x:c>
       <x:c r="G153" s="42" t="str">
-        <x:v>2.837393985422</x:v>
+        <x:v>25.638106879109</x:v>
       </x:c>
       <x:c r="H153" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5458,19 +5458,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C154" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D154" s="42" t="str">
-        <x:v>-0.727230275074</x:v>
+        <x:v>-1.097393985422</x:v>
       </x:c>
       <x:c r="E154" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F154" s="42" t="str">
-        <x:v>-2.477230275074</x:v>
+        <x:v>-2.837393985422</x:v>
       </x:c>
       <x:c r="G154" s="42" t="str">
-        <x:v>2.477230275074</x:v>
+        <x:v>2.837393985422</x:v>
       </x:c>
       <x:c r="H154" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5478,25 +5478,25 @@
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
       <x:c r="A155" s="36" t="str">
-        <x:v>historical mstore-inorganic CLI</x:v>
+        <x:v>current pbc CLI</x:v>
       </x:c>
       <x:c r="B155" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C155" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D155" s="42" t="str">
-        <x:v>21.964390394634</x:v>
+        <x:v>-0.727230275074</x:v>
       </x:c>
       <x:c r="E155" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F155" s="42" t="str">
-        <x:v>21.654390394634</x:v>
+        <x:v>-2.477230275074</x:v>
       </x:c>
       <x:c r="G155" s="42" t="str">
-        <x:v>21.654390394634</x:v>
+        <x:v>2.477230275074</x:v>
       </x:c>
       <x:c r="H155" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5510,19 +5510,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C156" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D156" s="42" t="str">
-        <x:v>-171.325848518761</x:v>
+        <x:v>21.964390394634</x:v>
       </x:c>
       <x:c r="E156" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F156" s="42" t="str">
-        <x:v>-172.575848518761</x:v>
+        <x:v>21.654390394634</x:v>
       </x:c>
       <x:c r="G156" s="42" t="str">
-        <x:v>172.575848518761</x:v>
+        <x:v>21.654390394634</x:v>
       </x:c>
       <x:c r="H156" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5536,19 +5536,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C157" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D157" s="42" t="str">
-        <x:v>-64.481456672543</x:v>
+        <x:v>-171.325848518761</x:v>
       </x:c>
       <x:c r="E157" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F157" s="42" t="str">
-        <x:v>-68.311456672543</x:v>
+        <x:v>-172.575848518761</x:v>
       </x:c>
       <x:c r="G157" s="42" t="str">
-        <x:v>68.311456672543</x:v>
+        <x:v>172.575848518761</x:v>
       </x:c>
       <x:c r="H157" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5562,19 +5562,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C158" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D158" s="42" t="str">
-        <x:v>-55.475838468692</x:v>
+        <x:v>-64.481456672543</x:v>
       </x:c>
       <x:c r="E158" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F158" s="42" t="str">
-        <x:v>-57.255838468692</x:v>
+        <x:v>-68.311456672543</x:v>
       </x:c>
       <x:c r="G158" s="42" t="str">
-        <x:v>57.255838468692</x:v>
+        <x:v>68.311456672543</x:v>
       </x:c>
       <x:c r="H158" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5588,19 +5588,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C159" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D159" s="42" t="str">
-        <x:v>-259.196245399110</x:v>
+        <x:v>-55.475838468692</x:v>
       </x:c>
       <x:c r="E159" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F159" s="42" t="str">
-        <x:v>-264.186245399110</x:v>
+        <x:v>-57.255838468692</x:v>
       </x:c>
       <x:c r="G159" s="42" t="str">
-        <x:v>264.186245399110</x:v>
+        <x:v>57.255838468692</x:v>
       </x:c>
       <x:c r="H159" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5614,19 +5614,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C160" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D160" s="42" t="str">
-        <x:v>-252.839445286494</x:v>
+        <x:v>-259.196245399110</x:v>
       </x:c>
       <x:c r="E160" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F160" s="42" t="str">
-        <x:v>-257.069445286494</x:v>
+        <x:v>-264.186245399110</x:v>
       </x:c>
       <x:c r="G160" s="42" t="str">
-        <x:v>257.069445286494</x:v>
+        <x:v>264.186245399110</x:v>
       </x:c>
       <x:c r="H160" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5640,19 +5640,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C161" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D161" s="42" t="str">
-        <x:v>-146.178117427308</x:v>
+        <x:v>-252.839445286494</x:v>
       </x:c>
       <x:c r="E161" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F161" s="42" t="str">
-        <x:v>-146.778117427308</x:v>
+        <x:v>-257.069445286494</x:v>
       </x:c>
       <x:c r="G161" s="42" t="str">
-        <x:v>146.778117427308</x:v>
+        <x:v>257.069445286494</x:v>
       </x:c>
       <x:c r="H161" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5666,19 +5666,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C162" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D162" s="42" t="str">
-        <x:v>-224.393887966522</x:v>
+        <x:v>-146.178117427308</x:v>
       </x:c>
       <x:c r="E162" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F162" s="42" t="str">
-        <x:v>-224.553887966522</x:v>
+        <x:v>-146.778117427308</x:v>
       </x:c>
       <x:c r="G162" s="42" t="str">
-        <x:v>224.553887966522</x:v>
+        <x:v>146.778117427308</x:v>
       </x:c>
       <x:c r="H162" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5692,19 +5692,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C163" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D163" s="42" t="str">
-        <x:v>-64.059726187434</x:v>
+        <x:v>-224.393887966522</x:v>
       </x:c>
       <x:c r="E163" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F163" s="42" t="str">
-        <x:v>-66.179726187434</x:v>
+        <x:v>-224.553887966522</x:v>
       </x:c>
       <x:c r="G163" s="42" t="str">
-        <x:v>66.179726187434</x:v>
+        <x:v>224.553887966522</x:v>
       </x:c>
       <x:c r="H163" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5718,19 +5718,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C164" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D164" s="42" t="str">
-        <x:v>-178.832658863162</x:v>
+        <x:v>-64.059726187434</x:v>
       </x:c>
       <x:c r="E164" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F164" s="42" t="str">
-        <x:v>-180.532658863162</x:v>
+        <x:v>-66.179726187434</x:v>
       </x:c>
       <x:c r="G164" s="42" t="str">
-        <x:v>180.532658863162</x:v>
+        <x:v>66.179726187434</x:v>
       </x:c>
       <x:c r="H164" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5744,19 +5744,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C165" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D165" s="42" t="str">
-        <x:v>-55.925167433801</x:v>
+        <x:v>-178.832658863162</x:v>
       </x:c>
       <x:c r="E165" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F165" s="42" t="str">
-        <x:v>-57.665167433801</x:v>
+        <x:v>-180.532658863162</x:v>
       </x:c>
       <x:c r="G165" s="42" t="str">
-        <x:v>57.665167433801</x:v>
+        <x:v>180.532658863162</x:v>
       </x:c>
       <x:c r="H165" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5770,19 +5770,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C166" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D166" s="42" t="str">
-        <x:v>-52.285059233270</x:v>
+        <x:v>-55.925167433801</x:v>
       </x:c>
       <x:c r="E166" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F166" s="42" t="str">
-        <x:v>-54.035059233270</x:v>
+        <x:v>-57.665167433801</x:v>
       </x:c>
       <x:c r="G166" s="42" t="str">
-        <x:v>54.035059233270</x:v>
+        <x:v>57.665167433801</x:v>
       </x:c>
       <x:c r="H166" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5793,22 +5793,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B167" s="36" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C167" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D167" s="42" t="str">
-        <x:v>11.549596417487</x:v>
+        <x:v>-52.285059233270</x:v>
       </x:c>
       <x:c r="E167" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F167" s="42" t="str">
-        <x:v>11.239596417487</x:v>
+        <x:v>-54.035059233270</x:v>
       </x:c>
       <x:c r="G167" s="42" t="str">
-        <x:v>11.239596417487</x:v>
+        <x:v>54.035059233270</x:v>
       </x:c>
       <x:c r="H167" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5822,19 +5822,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C168" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D168" s="42" t="str">
-        <x:v>-29.811523391510</x:v>
+        <x:v>11.549596417487</x:v>
       </x:c>
       <x:c r="E168" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F168" s="42" t="str">
-        <x:v>-31.061523391510</x:v>
+        <x:v>11.239596417487</x:v>
       </x:c>
       <x:c r="G168" s="42" t="str">
-        <x:v>31.061523391510</x:v>
+        <x:v>11.239596417487</x:v>
       </x:c>
       <x:c r="H168" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5848,19 +5848,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C169" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D169" s="42" t="str">
-        <x:v>0.256599145141</x:v>
+        <x:v>-29.811523391510</x:v>
       </x:c>
       <x:c r="E169" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F169" s="42" t="str">
-        <x:v>-3.573400854859</x:v>
+        <x:v>-31.061523391510</x:v>
       </x:c>
       <x:c r="G169" s="42" t="str">
-        <x:v>3.573400854859</x:v>
+        <x:v>31.061523391510</x:v>
       </x:c>
       <x:c r="H169" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5874,19 +5874,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C170" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D170" s="42" t="str">
-        <x:v>-28.460677817350</x:v>
+        <x:v>0.256599145141</x:v>
       </x:c>
       <x:c r="E170" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F170" s="42" t="str">
-        <x:v>-30.240677817350</x:v>
+        <x:v>-3.573400854859</x:v>
       </x:c>
       <x:c r="G170" s="42" t="str">
-        <x:v>30.240677817350</x:v>
+        <x:v>3.573400854859</x:v>
       </x:c>
       <x:c r="H170" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5900,19 +5900,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C171" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D171" s="42" t="str">
-        <x:v>-151.947965741842</x:v>
+        <x:v>-28.460677817350</x:v>
       </x:c>
       <x:c r="E171" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F171" s="42" t="str">
-        <x:v>-156.937965741842</x:v>
+        <x:v>-30.240677817350</x:v>
       </x:c>
       <x:c r="G171" s="42" t="str">
-        <x:v>156.937965741842</x:v>
+        <x:v>30.240677817350</x:v>
       </x:c>
       <x:c r="H171" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5926,19 +5926,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C172" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D172" s="42" t="str">
-        <x:v>-77.417542603032</x:v>
+        <x:v>-151.947965741842</x:v>
       </x:c>
       <x:c r="E172" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F172" s="42" t="str">
-        <x:v>-81.647542603032</x:v>
+        <x:v>-156.937965741842</x:v>
       </x:c>
       <x:c r="G172" s="42" t="str">
-        <x:v>81.647542603032</x:v>
+        <x:v>156.937965741842</x:v>
       </x:c>
       <x:c r="H172" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5952,19 +5952,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C173" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D173" s="42" t="str">
-        <x:v>-24.470250890265</x:v>
+        <x:v>-77.417542603032</x:v>
       </x:c>
       <x:c r="E173" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F173" s="42" t="str">
-        <x:v>-25.070250890265</x:v>
+        <x:v>-81.647542603032</x:v>
       </x:c>
       <x:c r="G173" s="42" t="str">
-        <x:v>25.070250890265</x:v>
+        <x:v>81.647542603032</x:v>
       </x:c>
       <x:c r="H173" s="36" t="str">
         <x:v>PASS</x:v>
@@ -5978,19 +5978,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C174" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D174" s="42" t="str">
-        <x:v>-84.549975905731</x:v>
+        <x:v>-24.470250890265</x:v>
       </x:c>
       <x:c r="E174" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F174" s="42" t="str">
-        <x:v>-84.709975905731</x:v>
+        <x:v>-25.070250890265</x:v>
       </x:c>
       <x:c r="G174" s="42" t="str">
-        <x:v>84.709975905731</x:v>
+        <x:v>25.070250890265</x:v>
       </x:c>
       <x:c r="H174" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6004,19 +6004,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C175" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D175" s="42" t="str">
-        <x:v>0.922244833924</x:v>
+        <x:v>-84.549975905731</x:v>
       </x:c>
       <x:c r="E175" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F175" s="42" t="str">
-        <x:v>-1.197755166076</x:v>
+        <x:v>-84.709975905731</x:v>
       </x:c>
       <x:c r="G175" s="42" t="str">
-        <x:v>1.197755166076</x:v>
+        <x:v>84.709975905731</x:v>
       </x:c>
       <x:c r="H175" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6030,19 +6030,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C176" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D176" s="42" t="str">
-        <x:v>-99.557194036284</x:v>
+        <x:v>0.922244833924</x:v>
       </x:c>
       <x:c r="E176" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F176" s="42" t="str">
-        <x:v>-101.257194036284</x:v>
+        <x:v>-1.197755166076</x:v>
       </x:c>
       <x:c r="G176" s="42" t="str">
-        <x:v>101.257194036284</x:v>
+        <x:v>1.197755166076</x:v>
       </x:c>
       <x:c r="H176" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6056,19 +6056,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C177" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D177" s="42" t="str">
-        <x:v>-28.664951204286</x:v>
+        <x:v>-99.557194036284</x:v>
       </x:c>
       <x:c r="E177" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F177" s="42" t="str">
-        <x:v>-30.404951204286</x:v>
+        <x:v>-101.257194036284</x:v>
       </x:c>
       <x:c r="G177" s="42" t="str">
-        <x:v>30.404951204286</x:v>
+        <x:v>101.257194036284</x:v>
       </x:c>
       <x:c r="H177" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6082,19 +6082,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C178" s="36" t="str">
-        <x:v>XVII</x:v>
+        <x:v>XV</x:v>
       </x:c>
       <x:c r="D178" s="42" t="str">
-        <x:v>-25.438330429983</x:v>
+        <x:v>-28.664951204286</x:v>
       </x:c>
       <x:c r="E178" s="42" t="str">
-        <x:v>1.750000</x:v>
+        <x:v>1.740000</x:v>
       </x:c>
       <x:c r="F178" s="42" t="str">
-        <x:v>-27.188330429983</x:v>
+        <x:v>-30.404951204286</x:v>
       </x:c>
       <x:c r="G178" s="42" t="str">
-        <x:v>27.188330429983</x:v>
+        <x:v>30.404951204286</x:v>
       </x:c>
       <x:c r="H178" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6105,22 +6105,22 @@
         <x:v>historical mstore-inorganic CLI</x:v>
       </x:c>
       <x:c r="B179" s="36" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C179" s="36" t="str">
-        <x:v>II</x:v>
+        <x:v>XVII</x:v>
       </x:c>
       <x:c r="D179" s="42" t="str">
-        <x:v>-0.279988209907</x:v>
+        <x:v>-25.438330429983</x:v>
       </x:c>
       <x:c r="E179" s="42" t="str">
-        <x:v>0.310000</x:v>
+        <x:v>1.750000</x:v>
       </x:c>
       <x:c r="F179" s="42" t="str">
-        <x:v>-0.589988209907</x:v>
+        <x:v>-27.188330429983</x:v>
       </x:c>
       <x:c r="G179" s="42" t="str">
-        <x:v>0.589988209907</x:v>
+        <x:v>27.188330429983</x:v>
       </x:c>
       <x:c r="H179" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6134,19 +6134,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C180" s="36" t="str">
-        <x:v>III</x:v>
+        <x:v>II</x:v>
       </x:c>
       <x:c r="D180" s="42" t="str">
-        <x:v>-1.720202220170</x:v>
+        <x:v>-0.279988209907</x:v>
       </x:c>
       <x:c r="E180" s="42" t="str">
-        <x:v>1.250000</x:v>
+        <x:v>0.310000</x:v>
       </x:c>
       <x:c r="F180" s="42" t="str">
-        <x:v>-2.970202220170</x:v>
+        <x:v>-0.589988209907</x:v>
       </x:c>
       <x:c r="G180" s="42" t="str">
-        <x:v>2.970202220170</x:v>
+        <x:v>0.589988209907</x:v>
       </x:c>
       <x:c r="H180" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6160,19 +6160,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C181" s="36" t="str">
-        <x:v>IV</x:v>
+        <x:v>III</x:v>
       </x:c>
       <x:c r="D181" s="42" t="str">
-        <x:v>1.653583137544</x:v>
+        <x:v>-1.720202220170</x:v>
       </x:c>
       <x:c r="E181" s="42" t="str">
-        <x:v>3.830000</x:v>
+        <x:v>1.250000</x:v>
       </x:c>
       <x:c r="F181" s="42" t="str">
-        <x:v>-2.176416862456</x:v>
+        <x:v>-2.970202220170</x:v>
       </x:c>
       <x:c r="G181" s="42" t="str">
-        <x:v>2.176416862456</x:v>
+        <x:v>2.970202220170</x:v>
       </x:c>
       <x:c r="H181" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6186,19 +6186,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C182" s="36" t="str">
-        <x:v>VI</x:v>
+        <x:v>IV</x:v>
       </x:c>
       <x:c r="D182" s="42" t="str">
-        <x:v>-5.912105883998</x:v>
+        <x:v>1.653583137544</x:v>
       </x:c>
       <x:c r="E182" s="42" t="str">
-        <x:v>1.780000</x:v>
+        <x:v>3.830000</x:v>
       </x:c>
       <x:c r="F182" s="42" t="str">
-        <x:v>-7.692105883998</x:v>
+        <x:v>-2.176416862456</x:v>
       </x:c>
       <x:c r="G182" s="42" t="str">
-        <x:v>7.692105883998</x:v>
+        <x:v>2.176416862456</x:v>
       </x:c>
       <x:c r="H182" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6212,19 +6212,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C183" s="36" t="str">
-        <x:v>VII</x:v>
+        <x:v>VI</x:v>
       </x:c>
       <x:c r="D183" s="42" t="str">
-        <x:v>-77.446667006181</x:v>
+        <x:v>-5.912105883998</x:v>
       </x:c>
       <x:c r="E183" s="42" t="str">
-        <x:v>4.990000</x:v>
+        <x:v>1.780000</x:v>
       </x:c>
       <x:c r="F183" s="42" t="str">
-        <x:v>-82.436667006181</x:v>
+        <x:v>-7.692105883998</x:v>
       </x:c>
       <x:c r="G183" s="42" t="str">
-        <x:v>82.436667006181</x:v>
+        <x:v>7.692105883998</x:v>
       </x:c>
       <x:c r="H183" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6238,19 +6238,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C184" s="36" t="str">
-        <x:v>VIII</x:v>
+        <x:v>VII</x:v>
       </x:c>
       <x:c r="D184" s="42" t="str">
-        <x:v>-19.706722185486</x:v>
+        <x:v>-77.446667006181</x:v>
       </x:c>
       <x:c r="E184" s="42" t="str">
-        <x:v>4.230000</x:v>
+        <x:v>4.990000</x:v>
       </x:c>
       <x:c r="F184" s="42" t="str">
-        <x:v>-23.936722185486</x:v>
+        <x:v>-82.436667006181</x:v>
       </x:c>
       <x:c r="G184" s="42" t="str">
-        <x:v>23.936722185486</x:v>
+        <x:v>82.436667006181</x:v>
       </x:c>
       <x:c r="H184" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6264,19 +6264,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C185" s="36" t="str">
-        <x:v>IX</x:v>
+        <x:v>VIII</x:v>
       </x:c>
       <x:c r="D185" s="42" t="str">
-        <x:v>-2.774771626398</x:v>
+        <x:v>-19.706722185486</x:v>
       </x:c>
       <x:c r="E185" s="42" t="str">
-        <x:v>0.600000</x:v>
+        <x:v>4.230000</x:v>
       </x:c>
       <x:c r="F185" s="42" t="str">
-        <x:v>-3.374771626398</x:v>
+        <x:v>-23.936722185486</x:v>
       </x:c>
       <x:c r="G185" s="42" t="str">
-        <x:v>3.374771626398</x:v>
+        <x:v>23.936722185486</x:v>
       </x:c>
       <x:c r="H185" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6290,19 +6290,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C186" s="36" t="str">
-        <x:v>XI</x:v>
+        <x:v>IX</x:v>
       </x:c>
       <x:c r="D186" s="42" t="str">
-        <x:v>-31.168750655955</x:v>
+        <x:v>-2.774771626398</x:v>
       </x:c>
       <x:c r="E186" s="42" t="str">
-        <x:v>0.160000</x:v>
+        <x:v>0.600000</x:v>
       </x:c>
       <x:c r="F186" s="42" t="str">
-        <x:v>-31.328750655955</x:v>
+        <x:v>-3.374771626398</x:v>
       </x:c>
       <x:c r="G186" s="42" t="str">
-        <x:v>31.328750655955</x:v>
+        <x:v>3.374771626398</x:v>
       </x:c>
       <x:c r="H186" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6316,19 +6316,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C187" s="36" t="str">
-        <x:v>XIII</x:v>
+        <x:v>XI</x:v>
       </x:c>
       <x:c r="D187" s="42" t="str">
-        <x:v>0.442953962487</x:v>
+        <x:v>-31.168750655955</x:v>
       </x:c>
       <x:c r="E187" s="42" t="str">
-        <x:v>2.120000</x:v>
+        <x:v>0.160000</x:v>
       </x:c>
       <x:c r="F187" s="42" t="str">
-        <x:v>-1.677046037513</x:v>
+        <x:v>-31.328750655955</x:v>
       </x:c>
       <x:c r="G187" s="42" t="str">
-        <x:v>1.677046037513</x:v>
+        <x:v>31.328750655955</x:v>
       </x:c>
       <x:c r="H187" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6342,19 +6342,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C188" s="36" t="str">
-        <x:v>XIV</x:v>
+        <x:v>XIII</x:v>
       </x:c>
       <x:c r="D188" s="42" t="str">
-        <x:v>-41.779791859131</x:v>
+        <x:v>0.442953962487</x:v>
       </x:c>
       <x:c r="E188" s="42" t="str">
-        <x:v>1.700000</x:v>
+        <x:v>2.120000</x:v>
       </x:c>
       <x:c r="F188" s="42" t="str">
-        <x:v>-43.479791859131</x:v>
+        <x:v>-1.677046037513</x:v>
       </x:c>
       <x:c r="G188" s="42" t="str">
-        <x:v>43.479791859131</x:v>
+        <x:v>1.677046037513</x:v>
       </x:c>
       <x:c r="H188" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6368,19 +6368,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C189" s="36" t="str">
-        <x:v>XV</x:v>
+        <x:v>XIV</x:v>
       </x:c>
       <x:c r="D189" s="42" t="str">
-        <x:v>-5.934441749535</x:v>
+        <x:v>-41.779791859131</x:v>
       </x:c>
       <x:c r="E189" s="42" t="str">
-        <x:v>1.740000</x:v>
+        <x:v>1.700000</x:v>
       </x:c>
       <x:c r="F189" s="42" t="str">
-        <x:v>-7.674441749535</x:v>
+        <x:v>-43.479791859131</x:v>
       </x:c>
       <x:c r="G189" s="42" t="str">
-        <x:v>7.674441749535</x:v>
+        <x:v>43.479791859131</x:v>
       </x:c>
       <x:c r="H189" s="36" t="str">
         <x:v>PASS</x:v>
@@ -6394,21 +6394,47 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C190" s="36" t="str">
+        <x:v>XV</x:v>
+      </x:c>
+      <x:c r="D190" s="42" t="str">
+        <x:v>-5.934441749535</x:v>
+      </x:c>
+      <x:c r="E190" s="42" t="str">
+        <x:v>1.740000</x:v>
+      </x:c>
+      <x:c r="F190" s="42" t="str">
+        <x:v>-7.674441749535</x:v>
+      </x:c>
+      <x:c r="G190" s="42" t="str">
+        <x:v>7.674441749535</x:v>
+      </x:c>
+      <x:c r="H190" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" ht="15" hidden="0" customHeight="1">
+      <x:c r="A191" s="36" t="str">
+        <x:v>historical mstore-inorganic CLI</x:v>
+      </x:c>
+      <x:c r="B191" s="36" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C191" s="36" t="str">
         <x:v>XVII</x:v>
       </x:c>
-      <x:c r="D190" s="42" t="str">
+      <x:c r="D191" s="42" t="str">
         <x:v>-4.880577524129</x:v>
       </x:c>
-      <x:c r="E190" s="42" t="str">
+      <x:c r="E191" s="42" t="str">
         <x:v>1.750000</x:v>
       </x:c>
-      <x:c r="F190" s="42" t="str">
+      <x:c r="F191" s="42" t="str">
         <x:v>-6.630577524129</x:v>
       </x:c>
-      <x:c r="G190" s="42" t="str">
+      <x:c r="G191" s="42" t="str">
         <x:v>6.630577524129</x:v>
       </x:c>
-      <x:c r="H190" s="36" t="str">
+      <x:c r="H191" s="36" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
@@ -11751,21 +11777,47 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C82" s="36" t="str">
+        <x:v>XI</x:v>
+      </x:c>
+      <x:c r="D82" s="42" t="str">
+        <x:v>0.508805411655</x:v>
+      </x:c>
+      <x:c r="E82" s="42" t="str">
+        <x:v>0.160000</x:v>
+      </x:c>
+      <x:c r="F82" s="42" t="str">
+        <x:v>0.348805411655</x:v>
+      </x:c>
+      <x:c r="G82" s="42" t="str">
+        <x:v>0.348805411655</x:v>
+      </x:c>
+      <x:c r="H82" s="36" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="15" hidden="0" customHeight="1">
+      <x:c r="A83" s="36" t="str">
+        <x:v>CP2K-native pbc provider</x:v>
+      </x:c>
+      <x:c r="B83" s="36" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C83" s="36" t="str">
         <x:v>XIV</x:v>
       </x:c>
-      <x:c r="D82" s="42" t="str">
+      <x:c r="D83" s="42" t="str">
         <x:v>0.090455358961</x:v>
       </x:c>
-      <x:c r="E82" s="42" t="str">
+      <x:c r="E83" s="42" t="str">
         <x:v>1.700000</x:v>
       </x:c>
-      <x:c r="F82" s="42" t="str">
+      <x:c r="F83" s="42" t="str">
         <x:v>-1.609544641039</x:v>
       </x:c>
-      <x:c r="G82" s="42" t="str">
+      <x:c r="G83" s="42" t="str">
         <x:v>1.609544641039</x:v>
       </x:c>
-      <x:c r="H82" s="36" t="str">
+      <x:c r="H83" s="36" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
